--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11143,6 +11143,9240 @@
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128103784</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>626608</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7217437</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128103745</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>626149</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7217977</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128103836</v>
+      </c>
+      <c r="B99" t="n">
+        <v>90906</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>900</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gröntagging</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Kavinia alboviridis</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Morgan) Gilb. &amp; Budington</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>626328</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7217861</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128103850</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>626593</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7217442</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128103701</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91349</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>626222</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7218014</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128103757</v>
+      </c>
+      <c r="B102" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>626239</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7218007</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128103728</v>
+      </c>
+      <c r="B103" t="n">
+        <v>80161</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>626453</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7217719</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128103703</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91349</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>626128</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7218027</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128103812</v>
+      </c>
+      <c r="B105" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>626319</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7217868</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128103719</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>626269</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7217921</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128103806</v>
+      </c>
+      <c r="B107" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>626574</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7217449</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128103830</v>
+      </c>
+      <c r="B108" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>626295</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7217850</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128103794</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>626239</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7217951</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128103826</v>
+      </c>
+      <c r="B110" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>626206</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7218045</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128103716</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>626454</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7217736</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128103870</v>
+      </c>
+      <c r="B112" t="n">
+        <v>78007</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>626270</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7217834</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128103754</v>
+      </c>
+      <c r="B113" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>626325</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7217934</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128103744</v>
+      </c>
+      <c r="B114" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>626454</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7217736</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128103765</v>
+      </c>
+      <c r="B115" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>626320</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7217923</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128103871</v>
+      </c>
+      <c r="B116" t="n">
+        <v>92633</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>626144</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7217996</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128103831</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>626373</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7217883</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128103717</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>626217</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7217965</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128103733</v>
+      </c>
+      <c r="B119" t="n">
+        <v>98488</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>626571</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7217492</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128103828</v>
+      </c>
+      <c r="B120" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>626202</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7217956</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128103853</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>626328</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7217861</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128103866</v>
+      </c>
+      <c r="B122" t="n">
+        <v>80167</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>626282</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7217980</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128103782</v>
+      </c>
+      <c r="B123" t="n">
+        <v>80168</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>626380</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7217892</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128103756</v>
+      </c>
+      <c r="B124" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>626277</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7217976</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128103772</v>
+      </c>
+      <c r="B125" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>626347</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7217886</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128103746</v>
+      </c>
+      <c r="B126" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>626290</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7217851</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128103740</v>
+      </c>
+      <c r="B127" t="n">
+        <v>91645</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>658</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>626128</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7218027</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128103824</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>626300</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7217895</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128103721</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>626306</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7217910</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128103842</v>
+      </c>
+      <c r="B130" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>626317</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7217935</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128103811</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>626311</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7217865</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128103696</v>
+      </c>
+      <c r="B132" t="n">
+        <v>91634</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>71</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>626167</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7217957</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128103787</v>
+      </c>
+      <c r="B133" t="n">
+        <v>91721</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Kristallticka</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Skeletocutis stellae</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Pilát) Jean Keller</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>626280</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7217822</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128103827</v>
+      </c>
+      <c r="B134" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>626128</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7218027</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128103781</v>
+      </c>
+      <c r="B135" t="n">
+        <v>80168</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>626239</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7218007</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128103867</v>
+      </c>
+      <c r="B136" t="n">
+        <v>80167</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>626346</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7217883</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128103856</v>
+      </c>
+      <c r="B137" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>626323</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7217908</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128103810</v>
+      </c>
+      <c r="B138" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>626290</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7217851</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128103773</v>
+      </c>
+      <c r="B139" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>626370</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7217900</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128103835</v>
+      </c>
+      <c r="B140" t="n">
+        <v>90906</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>900</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Gröntagging</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Kavinia alboviridis</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Morgan) Gilb. &amp; Budington</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>626354</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7217769</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128103837</v>
+      </c>
+      <c r="B141" t="n">
+        <v>105505</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>626194</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7218055</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128103769</v>
+      </c>
+      <c r="B142" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>626248</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7218007</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128103743</v>
+      </c>
+      <c r="B143" t="n">
+        <v>92631</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>626130</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7218000</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128103857</v>
+      </c>
+      <c r="B144" t="n">
+        <v>91610</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>65</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>626178</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7217957</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128103843</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>626276</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7217891</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128103863</v>
+      </c>
+      <c r="B146" t="n">
+        <v>80167</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>626248</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7218007</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128103753</v>
+      </c>
+      <c r="B147" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>626465</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7217693</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128103839</v>
+      </c>
+      <c r="B148" t="n">
+        <v>91367</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>626215</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7218028</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128103763</v>
+      </c>
+      <c r="B149" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>626343</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7217927</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>128103829</v>
+      </c>
+      <c r="B150" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>626217</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7217956</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>128103704</v>
+      </c>
+      <c r="B151" t="n">
+        <v>91349</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>626182</v>
+      </c>
+      <c r="R151" t="n">
+        <v>7218029</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>128103807</v>
+      </c>
+      <c r="B152" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>626532</v>
+      </c>
+      <c r="R152" t="n">
+        <v>7217568</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>128103735</v>
+      </c>
+      <c r="B153" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>626159</v>
+      </c>
+      <c r="R153" t="n">
+        <v>7217940</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>128103699</v>
+      </c>
+      <c r="B154" t="n">
+        <v>91634</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>71</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>626262</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7217920</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>128103737</v>
+      </c>
+      <c r="B155" t="n">
+        <v>92643</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>626278</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7217843</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>128103694</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>626150</v>
+      </c>
+      <c r="R156" t="n">
+        <v>7217973</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>128103767</v>
+      </c>
+      <c r="B157" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>626268</v>
+      </c>
+      <c r="R157" t="n">
+        <v>7217982</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>128103858</v>
+      </c>
+      <c r="B158" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>626413</v>
+      </c>
+      <c r="R158" t="n">
+        <v>7217701</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>128103851</v>
+      </c>
+      <c r="B159" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>626264</v>
+      </c>
+      <c r="R159" t="n">
+        <v>7217994</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>128103808</v>
+      </c>
+      <c r="B160" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>626216</v>
+      </c>
+      <c r="R160" t="n">
+        <v>7217940</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>128103770</v>
+      </c>
+      <c r="B161" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>626249</v>
+      </c>
+      <c r="R161" t="n">
+        <v>7218009</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>128103774</v>
+      </c>
+      <c r="B162" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>626377</v>
+      </c>
+      <c r="R162" t="n">
+        <v>7217880</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>128103768</v>
+      </c>
+      <c r="B163" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>626272</v>
+      </c>
+      <c r="R163" t="n">
+        <v>7217987</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>128103786</v>
+      </c>
+      <c r="B164" t="n">
+        <v>91822</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>626319</v>
+      </c>
+      <c r="R164" t="n">
+        <v>7217868</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>128103783</v>
+      </c>
+      <c r="B165" t="n">
+        <v>91732</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>298</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Laxgröppa</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Byssomerulius albostramineus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Torrend) Hjortstam</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>626271</v>
+      </c>
+      <c r="R165" t="n">
+        <v>7217852</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>128103823</v>
+      </c>
+      <c r="B166" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>626337</v>
+      </c>
+      <c r="R166" t="n">
+        <v>7217840</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>128103813</v>
+      </c>
+      <c r="B167" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>626370</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7217900</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>128103736</v>
+      </c>
+      <c r="B168" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>626194</v>
+      </c>
+      <c r="R168" t="n">
+        <v>7217951</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>128103766</v>
+      </c>
+      <c r="B169" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>626308</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7217938</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>128103785</v>
+      </c>
+      <c r="B170" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>626322</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7217855</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>128103809</v>
+      </c>
+      <c r="B171" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>626232</v>
+      </c>
+      <c r="R171" t="n">
+        <v>7217960</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>128103825</v>
+      </c>
+      <c r="B172" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>626215</v>
+      </c>
+      <c r="R172" t="n">
+        <v>7218004</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>128103793</v>
+      </c>
+      <c r="B173" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>626317</v>
+      </c>
+      <c r="R173" t="n">
+        <v>7217867</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>128103844</v>
+      </c>
+      <c r="B174" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>626263</v>
+      </c>
+      <c r="R174" t="n">
+        <v>7217877</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>128103852</v>
+      </c>
+      <c r="B175" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>626320</v>
+      </c>
+      <c r="R175" t="n">
+        <v>7217901</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>128103792</v>
+      </c>
+      <c r="B176" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>626297</v>
+      </c>
+      <c r="R176" t="n">
+        <v>7217856</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>128103692</v>
+      </c>
+      <c r="B177" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>626320</v>
+      </c>
+      <c r="R177" t="n">
+        <v>7217864</v>
+      </c>
+      <c r="S177" t="n">
+        <v>10</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>128103758</v>
+      </c>
+      <c r="B178" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>626196</v>
+      </c>
+      <c r="R178" t="n">
+        <v>7218053</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>128103727</v>
+      </c>
+      <c r="B179" t="n">
+        <v>80161</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>626546</v>
+      </c>
+      <c r="R179" t="n">
+        <v>7217566</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>128103845</v>
+      </c>
+      <c r="B180" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>626363</v>
+      </c>
+      <c r="R180" t="n">
+        <v>7217905</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>128103734</v>
+      </c>
+      <c r="B181" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>626084</v>
+      </c>
+      <c r="R181" t="n">
+        <v>7218019</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>128103729</v>
+      </c>
+      <c r="B182" t="n">
+        <v>91299</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>112</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>626278</v>
+      </c>
+      <c r="R182" t="n">
+        <v>7217843</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>128103759</v>
+      </c>
+      <c r="B183" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>626350</v>
+      </c>
+      <c r="R183" t="n">
+        <v>7217852</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>128103695</v>
+      </c>
+      <c r="B184" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>626290</v>
+      </c>
+      <c r="R184" t="n">
+        <v>7217851</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>128103700</v>
+      </c>
+      <c r="B185" t="n">
+        <v>91634</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>71</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>626271</v>
+      </c>
+      <c r="R185" t="n">
+        <v>7217852</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>128103859</v>
+      </c>
+      <c r="B186" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>626133</v>
+      </c>
+      <c r="R186" t="n">
+        <v>7217998</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>128103761</v>
+      </c>
+      <c r="B187" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>626398</v>
+      </c>
+      <c r="R187" t="n">
+        <v>7217759</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>128103791</v>
+      </c>
+      <c r="B188" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>626290</v>
+      </c>
+      <c r="R188" t="n">
+        <v>7217851</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>128103739</v>
+      </c>
+      <c r="B189" t="n">
+        <v>80133</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>626582</v>
+      </c>
+      <c r="R189" t="n">
+        <v>7217455</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>128103822</v>
+      </c>
+      <c r="B190" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Burmyrhobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>626528</v>
+      </c>
+      <c r="R190" t="n">
+        <v>7217613</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103784</v>
+        <v>128103836</v>
       </c>
       <c r="B97" t="n">
-        <v>57776</v>
+        <v>90907</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>900</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626608</v>
+        <v>626328</v>
       </c>
       <c r="R97" t="n">
-        <v>7217437</v>
+        <v>7217861</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103745</v>
+        <v>128103784</v>
       </c>
       <c r="B98" t="n">
-        <v>78788</v>
+        <v>57776</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626149</v>
+        <v>626608</v>
       </c>
       <c r="R98" t="n">
-        <v>7217977</v>
+        <v>7217437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,7 +11321,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11340,10 +11339,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>90906</v>
+        <v>78788</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11351,21 +11350,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11375,10 +11374,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R99" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11419,6 +11418,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>128103701</v>
       </c>
       <c r="B101" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>128103703</v>
       </c>
       <c r="B104" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11927,45 +11927,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103812</v>
+        <v>128103719</v>
       </c>
       <c r="B105" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626319</v>
+        <v>626269</v>
       </c>
       <c r="R105" t="n">
-        <v>7217868</v>
+        <v>7217921</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11998,6 +12006,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12024,53 +12037,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103719</v>
+        <v>128103812</v>
       </c>
       <c r="B106" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626269</v>
+        <v>626319</v>
       </c>
       <c r="R106" t="n">
-        <v>7217921</v>
+        <v>7217868</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12103,11 +12108,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12137,7 +12137,7 @@
         <v>128103806</v>
       </c>
       <c r="B107" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12231,32 +12231,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128103830</v>
+        <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>98467</v>
+        <v>78787</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>626295</v>
+        <v>626239</v>
       </c>
       <c r="R108" t="n">
-        <v>7217850</v>
+        <v>7217951</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12328,32 +12328,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128103794</v>
+        <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>78787</v>
+        <v>98468</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>626239</v>
+        <v>626295</v>
       </c>
       <c r="R109" t="n">
-        <v>7217951</v>
+        <v>7217850</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12428,7 +12428,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103870</v>
+        <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78007</v>
+        <v>78788</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626270</v>
+        <v>626454</v>
       </c>
       <c r="R112" t="n">
-        <v>7217834</v>
+        <v>7217736</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12711,6 +12711,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12729,10 +12730,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103754</v>
+        <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>80132</v>
+        <v>78007</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12740,21 +12741,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12764,10 +12765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626325</v>
+        <v>626270</v>
       </c>
       <c r="R113" t="n">
-        <v>7217934</v>
+        <v>7217834</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12826,10 +12827,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103744</v>
+        <v>128103754</v>
       </c>
       <c r="B114" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12837,21 +12838,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12861,10 +12862,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626454</v>
+        <v>626325</v>
       </c>
       <c r="R114" t="n">
-        <v>7217736</v>
+        <v>7217934</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12905,7 +12906,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103871</v>
+        <v>128103866</v>
       </c>
       <c r="B116" t="n">
-        <v>92633</v>
+        <v>80167</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626144</v>
+        <v>626282</v>
       </c>
       <c r="R116" t="n">
-        <v>7217996</v>
+        <v>7217980</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,45 +13118,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103831</v>
+        <v>128103717</v>
       </c>
       <c r="B117" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626373</v>
+        <v>626217</v>
       </c>
       <c r="R117" t="n">
-        <v>7217883</v>
+        <v>7217965</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13189,6 +13197,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13215,53 +13228,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103717</v>
+        <v>128103831</v>
       </c>
       <c r="B118" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626217</v>
+        <v>626373</v>
       </c>
       <c r="R118" t="n">
-        <v>7217965</v>
+        <v>7217883</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13294,11 +13299,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13325,32 +13325,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103733</v>
+        <v>128103828</v>
       </c>
       <c r="B119" t="n">
-        <v>98488</v>
+        <v>98468</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626571</v>
+        <v>626202</v>
       </c>
       <c r="R119" t="n">
-        <v>7217492</v>
+        <v>7217956</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103828</v>
+        <v>128103871</v>
       </c>
       <c r="B120" t="n">
-        <v>98467</v>
+        <v>92634</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626202</v>
+        <v>626144</v>
       </c>
       <c r="R120" t="n">
-        <v>7217956</v>
+        <v>7217996</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13616,10 +13616,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103866</v>
+        <v>128103733</v>
       </c>
       <c r="B122" t="n">
-        <v>80167</v>
+        <v>98489</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13627,21 +13627,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13651,10 +13651,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626282</v>
+        <v>626571</v>
       </c>
       <c r="R122" t="n">
-        <v>7217980</v>
+        <v>7217492</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13713,45 +13713,53 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103782</v>
+        <v>128103721</v>
       </c>
       <c r="B123" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626380</v>
+        <v>626306</v>
       </c>
       <c r="R123" t="n">
-        <v>7217892</v>
+        <v>7217910</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13784,6 +13792,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13810,10 +13823,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103756</v>
+        <v>128103746</v>
       </c>
       <c r="B124" t="n">
-        <v>80132</v>
+        <v>78788</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,21 +13834,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13845,10 +13858,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626277</v>
+        <v>626290</v>
       </c>
       <c r="R124" t="n">
-        <v>7217976</v>
+        <v>7217851</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,6 +13902,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13907,32 +13921,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103772</v>
+        <v>128103824</v>
       </c>
       <c r="B125" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626347</v>
+        <v>626300</v>
       </c>
       <c r="R125" t="n">
-        <v>7217886</v>
+        <v>7217895</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14004,32 +14018,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103746</v>
+        <v>128103782</v>
       </c>
       <c r="B126" t="n">
-        <v>78788</v>
+        <v>80168</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14039,10 +14053,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626290</v>
+        <v>626380</v>
       </c>
       <c r="R126" t="n">
-        <v>7217851</v>
+        <v>7217892</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14083,7 +14097,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14102,10 +14115,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103740</v>
+        <v>128103756</v>
       </c>
       <c r="B127" t="n">
-        <v>91645</v>
+        <v>80132</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14113,21 +14126,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14137,10 +14150,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626128</v>
+        <v>626277</v>
       </c>
       <c r="R127" t="n">
-        <v>7218027</v>
+        <v>7217976</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14199,32 +14212,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103824</v>
+        <v>128103772</v>
       </c>
       <c r="B128" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14234,10 +14247,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626300</v>
+        <v>626347</v>
       </c>
       <c r="R128" t="n">
-        <v>7217895</v>
+        <v>7217886</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14296,10 +14309,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103721</v>
+        <v>128103842</v>
       </c>
       <c r="B129" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14307,42 +14320,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626306</v>
+        <v>626317</v>
       </c>
       <c r="R129" t="n">
-        <v>7217910</v>
+        <v>7217935</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14375,11 +14380,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14406,10 +14406,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103842</v>
+        <v>128103740</v>
       </c>
       <c r="B130" t="n">
-        <v>79029</v>
+        <v>91646</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14417,21 +14417,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14441,10 +14441,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626317</v>
+        <v>626128</v>
       </c>
       <c r="R130" t="n">
-        <v>7217935</v>
+        <v>7218027</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14503,32 +14503,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103811</v>
+        <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>98467</v>
+        <v>91635</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>71</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14538,10 +14538,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626311</v>
+        <v>626167</v>
       </c>
       <c r="R131" t="n">
-        <v>7217865</v>
+        <v>7217957</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14600,32 +14600,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103696</v>
+        <v>128103781</v>
       </c>
       <c r="B132" t="n">
-        <v>91634</v>
+        <v>80168</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>71</v>
+        <v>6464</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626167</v>
+        <v>626239</v>
       </c>
       <c r="R132" t="n">
-        <v>7217957</v>
+        <v>7218007</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14697,48 +14697,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103787</v>
+        <v>128103867</v>
       </c>
       <c r="B133" t="n">
-        <v>91721</v>
+        <v>80167</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1505</v>
+        <v>6463</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626280</v>
+        <v>626346</v>
       </c>
       <c r="R133" t="n">
-        <v>7217822</v>
+        <v>7217883</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14779,7 +14776,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14798,45 +14794,53 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103827</v>
+        <v>128103856</v>
       </c>
       <c r="B134" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626128</v>
+        <v>626323</v>
       </c>
       <c r="R134" t="n">
-        <v>7218027</v>
+        <v>7217908</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14869,6 +14873,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,32 +14904,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103781</v>
+        <v>128103811</v>
       </c>
       <c r="B135" t="n">
-        <v>80168</v>
+        <v>98468</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14930,10 +14939,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626239</v>
+        <v>626311</v>
       </c>
       <c r="R135" t="n">
-        <v>7218007</v>
+        <v>7217865</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14992,32 +15001,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103867</v>
+        <v>128103827</v>
       </c>
       <c r="B136" t="n">
-        <v>80167</v>
+        <v>98468</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15027,10 +15036,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626346</v>
+        <v>626128</v>
       </c>
       <c r="R136" t="n">
-        <v>7217883</v>
+        <v>7218027</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15089,42 +15098,37 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103856</v>
+        <v>128103787</v>
       </c>
       <c r="B137" t="n">
-        <v>57672</v>
+        <v>91722</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1505</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -15132,10 +15136,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626323</v>
+        <v>626280</v>
       </c>
       <c r="R137" t="n">
-        <v>7217908</v>
+        <v>7217822</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15170,17 +15174,13 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15199,32 +15199,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103810</v>
+        <v>128103773</v>
       </c>
       <c r="B138" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626290</v>
+        <v>626370</v>
       </c>
       <c r="R138" t="n">
-        <v>7217851</v>
+        <v>7217900</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,7 +15296,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B139" t="n">
         <v>80132</v>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R139" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15396,7 +15396,7 @@
         <v>128103835</v>
       </c>
       <c r="B140" t="n">
-        <v>90906</v>
+        <v>90907</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>128103837</v>
       </c>
       <c r="B141" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103769</v>
+        <v>128103810</v>
       </c>
       <c r="B142" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626248</v>
+        <v>626290</v>
       </c>
       <c r="R142" t="n">
-        <v>7218007</v>
+        <v>7217851</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103743</v>
+        <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>92631</v>
+        <v>91611</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626130</v>
+        <v>626178</v>
       </c>
       <c r="R143" t="n">
-        <v>7218000</v>
+        <v>7217957</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,32 +15781,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103857</v>
+        <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>91610</v>
+        <v>92632</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626178</v>
+        <v>626130</v>
       </c>
       <c r="R144" t="n">
-        <v>7217957</v>
+        <v>7218000</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,27 +15878,27 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103843</v>
+        <v>128103863</v>
       </c>
       <c r="B145" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626276</v>
+        <v>626248</v>
       </c>
       <c r="R145" t="n">
-        <v>7217891</v>
+        <v>7218007</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15975,27 +15975,27 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103863</v>
+        <v>128103843</v>
       </c>
       <c r="B146" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626248</v>
+        <v>626276</v>
       </c>
       <c r="R146" t="n">
-        <v>7218007</v>
+        <v>7217891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103753</v>
+        <v>128103704</v>
       </c>
       <c r="B147" t="n">
-        <v>80132</v>
+        <v>91350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,21 +16083,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626465</v>
+        <v>626182</v>
       </c>
       <c r="R147" t="n">
-        <v>7217693</v>
+        <v>7218029</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,32 +16169,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103839</v>
+        <v>128103829</v>
       </c>
       <c r="B148" t="n">
-        <v>91367</v>
+        <v>98468</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626215</v>
+        <v>626217</v>
       </c>
       <c r="R148" t="n">
-        <v>7218028</v>
+        <v>7217956</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,32 +16266,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103763</v>
+        <v>128103807</v>
       </c>
       <c r="B149" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626343</v>
+        <v>626532</v>
       </c>
       <c r="R149" t="n">
-        <v>7217927</v>
+        <v>7217568</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,32 +16363,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103829</v>
+        <v>128103753</v>
       </c>
       <c r="B150" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626217</v>
+        <v>626465</v>
       </c>
       <c r="R150" t="n">
-        <v>7217956</v>
+        <v>7217693</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103704</v>
+        <v>128103763</v>
       </c>
       <c r="B151" t="n">
-        <v>91349</v>
+        <v>80132</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,21 +16471,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16495,10 +16495,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626182</v>
+        <v>626343</v>
       </c>
       <c r="R151" t="n">
-        <v>7218029</v>
+        <v>7217927</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16557,32 +16557,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103807</v>
+        <v>128103839</v>
       </c>
       <c r="B152" t="n">
-        <v>98467</v>
+        <v>91368</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16592,10 +16592,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626532</v>
+        <v>626215</v>
       </c>
       <c r="R152" t="n">
-        <v>7217568</v>
+        <v>7218028</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16767,7 +16767,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91634</v>
+        <v>91635</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16861,32 +16861,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128103737</v>
+        <v>128103694</v>
       </c>
       <c r="B155" t="n">
-        <v>92643</v>
+        <v>79647</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626278</v>
+        <v>626150</v>
       </c>
       <c r="R155" t="n">
-        <v>7217843</v>
+        <v>7217973</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103694</v>
+        <v>128103737</v>
       </c>
       <c r="B156" t="n">
-        <v>79647</v>
+        <v>92644</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626150</v>
+        <v>626278</v>
       </c>
       <c r="R156" t="n">
-        <v>7217973</v>
+        <v>7217843</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80132</v>
+        <v>92640</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92639</v>
+        <v>80132</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17249,10 +17249,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103851</v>
+        <v>128103770</v>
       </c>
       <c r="B159" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17260,21 +17260,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626264</v>
+        <v>626249</v>
       </c>
       <c r="R159" t="n">
-        <v>7217994</v>
+        <v>7218009</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17346,32 +17346,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103808</v>
+        <v>128103774</v>
       </c>
       <c r="B160" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626216</v>
+        <v>626377</v>
       </c>
       <c r="R160" t="n">
-        <v>7217940</v>
+        <v>7217880</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103770</v>
+        <v>128103768</v>
       </c>
       <c r="B161" t="n">
         <v>80132</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626249</v>
+        <v>626272</v>
       </c>
       <c r="R161" t="n">
-        <v>7218009</v>
+        <v>7217987</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,10 +17540,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103774</v>
+        <v>128103851</v>
       </c>
       <c r="B162" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17551,21 +17551,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626377</v>
+        <v>626264</v>
       </c>
       <c r="R162" t="n">
-        <v>7217880</v>
+        <v>7217994</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17637,32 +17637,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103768</v>
+        <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626272</v>
+        <v>626216</v>
       </c>
       <c r="R163" t="n">
-        <v>7217987</v>
+        <v>7217940</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103786</v>
+        <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91822</v>
+        <v>91733</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5467</v>
+        <v>298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626319</v>
+        <v>626271</v>
       </c>
       <c r="R164" t="n">
-        <v>7217868</v>
+        <v>7217852</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,32 +17831,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103783</v>
+        <v>128103766</v>
       </c>
       <c r="B165" t="n">
-        <v>91732</v>
+        <v>80132</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>298</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626271</v>
+        <v>626308</v>
       </c>
       <c r="R165" t="n">
-        <v>7217852</v>
+        <v>7217938</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,32 +17928,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103823</v>
+        <v>128103786</v>
       </c>
       <c r="B166" t="n">
-        <v>98467</v>
+        <v>91823</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626337</v>
+        <v>626319</v>
       </c>
       <c r="R166" t="n">
-        <v>7217840</v>
+        <v>7217868</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18025,45 +18025,53 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103813</v>
+        <v>128103736</v>
       </c>
       <c r="B167" t="n">
-        <v>98467</v>
+        <v>57669</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626370</v>
+        <v>626194</v>
       </c>
       <c r="R167" t="n">
-        <v>7217900</v>
+        <v>7217951</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18096,6 +18104,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18122,53 +18135,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103736</v>
+        <v>128103823</v>
       </c>
       <c r="B168" t="n">
-        <v>57669</v>
+        <v>98468</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626194</v>
+        <v>626337</v>
       </c>
       <c r="R168" t="n">
-        <v>7217951</v>
+        <v>7217840</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18201,11 +18206,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18232,32 +18232,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103766</v>
+        <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626308</v>
+        <v>626370</v>
       </c>
       <c r="R169" t="n">
-        <v>7217938</v>
+        <v>7217900</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18429,7 +18429,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18523,32 +18523,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103825</v>
+        <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>98467</v>
+        <v>78787</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626215</v>
+        <v>626317</v>
       </c>
       <c r="R172" t="n">
-        <v>7218004</v>
+        <v>7217867</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,10 +18620,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103793</v>
+        <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18631,21 +18631,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626317</v>
+        <v>626263</v>
       </c>
       <c r="R173" t="n">
-        <v>7217867</v>
+        <v>7217877</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,7 +18717,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103844</v>
+        <v>128103852</v>
       </c>
       <c r="B174" t="n">
         <v>79029</v>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626263</v>
+        <v>626320</v>
       </c>
       <c r="R174" t="n">
-        <v>7217877</v>
+        <v>7217901</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18814,10 +18814,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103852</v>
+        <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18825,21 +18825,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626320</v>
+        <v>626297</v>
       </c>
       <c r="R175" t="n">
-        <v>7217901</v>
+        <v>7217856</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18911,32 +18911,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103792</v>
+        <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>78787</v>
+        <v>98468</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626297</v>
+        <v>626215</v>
       </c>
       <c r="R176" t="n">
-        <v>7217856</v>
+        <v>7218004</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19008,32 +19008,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128103692</v>
+        <v>128103758</v>
       </c>
       <c r="B177" t="n">
-        <v>91314</v>
+        <v>80132</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19043,10 +19043,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>626320</v>
+        <v>626196</v>
       </c>
       <c r="R177" t="n">
-        <v>7217864</v>
+        <v>7218053</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,32 +19105,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128103758</v>
+        <v>128103692</v>
       </c>
       <c r="B178" t="n">
-        <v>80132</v>
+        <v>91315</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19140,10 +19140,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>626196</v>
+        <v>626320</v>
       </c>
       <c r="R178" t="n">
-        <v>7218053</v>
+        <v>7217864</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103727</v>
+        <v>128103845</v>
       </c>
       <c r="B179" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626546</v>
+        <v>626363</v>
       </c>
       <c r="R179" t="n">
-        <v>7217566</v>
+        <v>7217905</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19299,10 +19299,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103845</v>
+        <v>128103729</v>
       </c>
       <c r="B180" t="n">
-        <v>79029</v>
+        <v>91300</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19310,21 +19310,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626363</v>
+        <v>626278</v>
       </c>
       <c r="R180" t="n">
-        <v>7217905</v>
+        <v>7217843</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19396,53 +19396,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103734</v>
+        <v>128103727</v>
       </c>
       <c r="B181" t="n">
-        <v>57669</v>
+        <v>80161</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626084</v>
+        <v>626546</v>
       </c>
       <c r="R181" t="n">
-        <v>7218019</v>
+        <v>7217566</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19475,11 +19467,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19506,10 +19493,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128103729</v>
+        <v>128103734</v>
       </c>
       <c r="B182" t="n">
-        <v>91299</v>
+        <v>57669</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19517,34 +19504,42 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>626278</v>
+        <v>626084</v>
       </c>
       <c r="R182" t="n">
-        <v>7217843</v>
+        <v>7218019</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19577,6 +19572,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19603,10 +19603,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103759</v>
+        <v>128103739</v>
       </c>
       <c r="B183" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19614,21 +19614,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626350</v>
+        <v>626582</v>
       </c>
       <c r="R183" t="n">
-        <v>7217852</v>
+        <v>7217455</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,32 +19700,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103695</v>
+        <v>128103700</v>
       </c>
       <c r="B184" t="n">
-        <v>79647</v>
+        <v>91635</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626290</v>
+        <v>626271</v>
       </c>
       <c r="R184" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,32 +19797,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103700</v>
+        <v>128103859</v>
       </c>
       <c r="B185" t="n">
-        <v>91634</v>
+        <v>92640</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626271</v>
+        <v>626133</v>
       </c>
       <c r="R185" t="n">
-        <v>7217852</v>
+        <v>7217998</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,32 +19894,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103859</v>
+        <v>128103759</v>
       </c>
       <c r="B186" t="n">
-        <v>92639</v>
+        <v>80132</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626133</v>
+        <v>626350</v>
       </c>
       <c r="R186" t="n">
-        <v>7217998</v>
+        <v>7217852</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,10 +19991,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103761</v>
+        <v>128103695</v>
       </c>
       <c r="B187" t="n">
-        <v>80132</v>
+        <v>79647</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20002,21 +20002,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626398</v>
+        <v>626290</v>
       </c>
       <c r="R187" t="n">
-        <v>7217759</v>
+        <v>7217851</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,10 +20088,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103791</v>
+        <v>128103761</v>
       </c>
       <c r="B188" t="n">
-        <v>78787</v>
+        <v>80132</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20099,21 +20099,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626290</v>
+        <v>626398</v>
       </c>
       <c r="R188" t="n">
-        <v>7217851</v>
+        <v>7217759</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20185,10 +20185,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103739</v>
+        <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>80133</v>
+        <v>78787</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20196,21 +20196,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626582</v>
+        <v>626290</v>
       </c>
       <c r="R189" t="n">
-        <v>7217455</v>
+        <v>7217851</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20285,7 +20285,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103836</v>
+        <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>90907</v>
+        <v>57776</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>900</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626328</v>
+        <v>626608</v>
       </c>
       <c r="R97" t="n">
-        <v>7217861</v>
+        <v>7217437</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103784</v>
+        <v>128103745</v>
       </c>
       <c r="B98" t="n">
-        <v>57776</v>
+        <v>78788</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626608</v>
+        <v>626149</v>
       </c>
       <c r="R98" t="n">
-        <v>7217437</v>
+        <v>7217977</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,6 +11321,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11339,10 +11340,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103745</v>
+        <v>128103836</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>90907</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,21 +11351,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>900</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11374,10 +11375,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626149</v>
+        <v>626328</v>
       </c>
       <c r="R99" t="n">
-        <v>7217977</v>
+        <v>7217861</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11418,7 +11419,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103850</v>
+        <v>128103757</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626593</v>
+        <v>626239</v>
       </c>
       <c r="R100" t="n">
-        <v>7217442</v>
+        <v>7218007</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11508,11 +11508,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11539,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103701</v>
+        <v>128103728</v>
       </c>
       <c r="B101" t="n">
-        <v>91350</v>
+        <v>80161</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11574,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626222</v>
+        <v>626453</v>
       </c>
       <c r="R101" t="n">
-        <v>7218014</v>
+        <v>7217719</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11636,10 +11631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103757</v>
+        <v>128103701</v>
       </c>
       <c r="B102" t="n">
-        <v>80132</v>
+        <v>91350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11647,21 +11642,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11671,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626239</v>
+        <v>626222</v>
       </c>
       <c r="R102" t="n">
-        <v>7218007</v>
+        <v>7218014</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11733,32 +11728,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103728</v>
+        <v>128103850</v>
       </c>
       <c r="B103" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11768,10 +11763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626453</v>
+        <v>626593</v>
       </c>
       <c r="R103" t="n">
-        <v>7217719</v>
+        <v>7217442</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,6 +11799,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12632,10 +12632,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103744</v>
+        <v>128103870</v>
       </c>
       <c r="B112" t="n">
-        <v>78788</v>
+        <v>78007</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626454</v>
+        <v>626270</v>
       </c>
       <c r="R112" t="n">
-        <v>7217736</v>
+        <v>7217834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12711,7 +12711,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12730,10 +12729,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103870</v>
+        <v>128103754</v>
       </c>
       <c r="B113" t="n">
-        <v>78007</v>
+        <v>80132</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12741,21 +12740,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12765,10 +12764,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626270</v>
+        <v>626325</v>
       </c>
       <c r="R113" t="n">
-        <v>7217834</v>
+        <v>7217934</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12827,7 +12826,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103754</v>
+        <v>128103765</v>
       </c>
       <c r="B114" t="n">
         <v>80132</v>
@@ -12862,10 +12861,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626325</v>
+        <v>626320</v>
       </c>
       <c r="R114" t="n">
-        <v>7217934</v>
+        <v>7217923</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12924,10 +12923,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103765</v>
+        <v>128103744</v>
       </c>
       <c r="B115" t="n">
-        <v>80132</v>
+        <v>78788</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12935,21 +12934,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12959,10 +12958,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R115" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13003,6 +13002,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13021,45 +13021,53 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103866</v>
+        <v>128103717</v>
       </c>
       <c r="B116" t="n">
-        <v>80167</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626282</v>
+        <v>626217</v>
       </c>
       <c r="R116" t="n">
-        <v>7217980</v>
+        <v>7217965</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13092,6 +13100,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13118,53 +13131,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103717</v>
+        <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626217</v>
+        <v>626282</v>
       </c>
       <c r="R117" t="n">
-        <v>7217965</v>
+        <v>7217980</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13197,11 +13202,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13228,32 +13228,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103831</v>
+        <v>128103871</v>
       </c>
       <c r="B118" t="n">
-        <v>98468</v>
+        <v>92634</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626373</v>
+        <v>626144</v>
       </c>
       <c r="R118" t="n">
-        <v>7217883</v>
+        <v>7217996</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13325,32 +13325,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103828</v>
+        <v>128103853</v>
       </c>
       <c r="B119" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626202</v>
+        <v>626328</v>
       </c>
       <c r="R119" t="n">
-        <v>7217956</v>
+        <v>7217861</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103871</v>
+        <v>128103831</v>
       </c>
       <c r="B120" t="n">
-        <v>92634</v>
+        <v>98468</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626144</v>
+        <v>626373</v>
       </c>
       <c r="R120" t="n">
-        <v>7217996</v>
+        <v>7217883</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,32 +13519,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103853</v>
+        <v>128103828</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13554,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626328</v>
+        <v>626202</v>
       </c>
       <c r="R121" t="n">
-        <v>7217861</v>
+        <v>7217956</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13713,53 +13713,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103721</v>
+        <v>128103782</v>
       </c>
       <c r="B123" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626306</v>
+        <v>626380</v>
       </c>
       <c r="R123" t="n">
-        <v>7217910</v>
+        <v>7217892</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13792,11 +13784,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13823,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103746</v>
+        <v>128103756</v>
       </c>
       <c r="B124" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13834,21 +13821,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13858,10 +13845,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626290</v>
+        <v>626277</v>
       </c>
       <c r="R124" t="n">
-        <v>7217851</v>
+        <v>7217976</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,7 +13889,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13921,32 +13907,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103824</v>
+        <v>128103772</v>
       </c>
       <c r="B125" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13956,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626300</v>
+        <v>626347</v>
       </c>
       <c r="R125" t="n">
-        <v>7217895</v>
+        <v>7217886</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14018,32 +14004,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103782</v>
+        <v>128103842</v>
       </c>
       <c r="B126" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14053,10 +14039,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626380</v>
+        <v>626317</v>
       </c>
       <c r="R126" t="n">
-        <v>7217892</v>
+        <v>7217935</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14115,10 +14101,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103756</v>
+        <v>128103740</v>
       </c>
       <c r="B127" t="n">
-        <v>80132</v>
+        <v>91646</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14126,21 +14112,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14150,10 +14136,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626277</v>
+        <v>626128</v>
       </c>
       <c r="R127" t="n">
-        <v>7217976</v>
+        <v>7218027</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14212,10 +14198,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103772</v>
+        <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14223,34 +14209,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626347</v>
+        <v>626306</v>
       </c>
       <c r="R128" t="n">
-        <v>7217886</v>
+        <v>7217910</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14283,6 +14277,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14309,32 +14308,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103842</v>
+        <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14344,10 +14343,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626317</v>
+        <v>626300</v>
       </c>
       <c r="R129" t="n">
-        <v>7217935</v>
+        <v>7217895</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14406,10 +14405,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103740</v>
+        <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>91646</v>
+        <v>78788</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14417,21 +14416,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14441,10 +14440,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626128</v>
+        <v>626290</v>
       </c>
       <c r="R130" t="n">
-        <v>7218027</v>
+        <v>7217851</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14485,6 +14484,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14503,32 +14503,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103696</v>
+        <v>128103781</v>
       </c>
       <c r="B131" t="n">
-        <v>91635</v>
+        <v>80168</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>71</v>
+        <v>6464</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14538,10 +14538,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626167</v>
+        <v>626239</v>
       </c>
       <c r="R131" t="n">
-        <v>7217957</v>
+        <v>7218007</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103781</v>
+        <v>128103867</v>
       </c>
       <c r="B132" t="n">
-        <v>80168</v>
+        <v>80167</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14611,21 +14611,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626239</v>
+        <v>626346</v>
       </c>
       <c r="R132" t="n">
-        <v>7218007</v>
+        <v>7217883</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14697,45 +14697,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103867</v>
+        <v>128103787</v>
       </c>
       <c r="B133" t="n">
-        <v>80167</v>
+        <v>91722</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6463</v>
+        <v>1505</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626346</v>
+        <v>626280</v>
       </c>
       <c r="R133" t="n">
-        <v>7217883</v>
+        <v>7217822</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14776,6 +14779,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14794,53 +14798,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103856</v>
+        <v>128103696</v>
       </c>
       <c r="B134" t="n">
-        <v>57672</v>
+        <v>91635</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>71</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626323</v>
+        <v>626167</v>
       </c>
       <c r="R134" t="n">
-        <v>7217908</v>
+        <v>7217957</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14873,11 +14869,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14904,45 +14895,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103811</v>
+        <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626311</v>
+        <v>626323</v>
       </c>
       <c r="R135" t="n">
-        <v>7217865</v>
+        <v>7217908</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14975,6 +14974,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15001,7 +15005,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103827</v>
+        <v>128103811</v>
       </c>
       <c r="B136" t="n">
         <v>98468</v>
@@ -15036,10 +15040,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626128</v>
+        <v>626311</v>
       </c>
       <c r="R136" t="n">
-        <v>7218027</v>
+        <v>7217865</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15098,10 +15102,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103787</v>
+        <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>91722</v>
+        <v>98468</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15109,37 +15113,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626280</v>
+        <v>626128</v>
       </c>
       <c r="R137" t="n">
-        <v>7217822</v>
+        <v>7218027</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15180,7 +15181,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103837</v>
+        <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626194</v>
+        <v>626290</v>
       </c>
       <c r="R141" t="n">
-        <v>7218055</v>
+        <v>7217851</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103810</v>
+        <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626290</v>
+        <v>626194</v>
       </c>
       <c r="R142" t="n">
-        <v>7217851</v>
+        <v>7218055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103857</v>
+        <v>128103843</v>
       </c>
       <c r="B143" t="n">
-        <v>91611</v>
+        <v>79029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626178</v>
+        <v>626276</v>
       </c>
       <c r="R143" t="n">
-        <v>7217957</v>
+        <v>7217891</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,32 +15781,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103743</v>
+        <v>128103863</v>
       </c>
       <c r="B144" t="n">
-        <v>92632</v>
+        <v>80167</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626130</v>
+        <v>626248</v>
       </c>
       <c r="R144" t="n">
-        <v>7218000</v>
+        <v>7218007</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,32 +15878,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103863</v>
+        <v>128103743</v>
       </c>
       <c r="B145" t="n">
-        <v>80167</v>
+        <v>92632</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6463</v>
+        <v>4361</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626248</v>
+        <v>626130</v>
       </c>
       <c r="R145" t="n">
-        <v>7218007</v>
+        <v>7218000</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15975,32 +15975,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103843</v>
+        <v>128103857</v>
       </c>
       <c r="B146" t="n">
-        <v>79029</v>
+        <v>91611</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626276</v>
+        <v>626178</v>
       </c>
       <c r="R146" t="n">
-        <v>7217891</v>
+        <v>7217957</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103704</v>
+        <v>128103753</v>
       </c>
       <c r="B147" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,21 +16083,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626182</v>
+        <v>626465</v>
       </c>
       <c r="R147" t="n">
-        <v>7218029</v>
+        <v>7217693</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,32 +16169,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103829</v>
+        <v>128103763</v>
       </c>
       <c r="B148" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626217</v>
+        <v>626343</v>
       </c>
       <c r="R148" t="n">
-        <v>7217956</v>
+        <v>7217927</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,32 +16266,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103807</v>
+        <v>128103839</v>
       </c>
       <c r="B149" t="n">
-        <v>98468</v>
+        <v>91368</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626532</v>
+        <v>626215</v>
       </c>
       <c r="R149" t="n">
-        <v>7217568</v>
+        <v>7218028</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,32 +16363,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103753</v>
+        <v>128103807</v>
       </c>
       <c r="B150" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626465</v>
+        <v>626532</v>
       </c>
       <c r="R150" t="n">
-        <v>7217693</v>
+        <v>7217568</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,32 +16460,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103763</v>
+        <v>128103829</v>
       </c>
       <c r="B151" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16495,10 +16495,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626343</v>
+        <v>626217</v>
       </c>
       <c r="R151" t="n">
-        <v>7217927</v>
+        <v>7217956</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16557,10 +16557,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103839</v>
+        <v>128103704</v>
       </c>
       <c r="B152" t="n">
-        <v>91368</v>
+        <v>91350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16568,21 +16568,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16592,10 +16592,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626215</v>
+        <v>626182</v>
       </c>
       <c r="R152" t="n">
-        <v>7218028</v>
+        <v>7218029</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16764,32 +16764,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128103699</v>
+        <v>128103737</v>
       </c>
       <c r="B154" t="n">
-        <v>91635</v>
+        <v>92644</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>71</v>
+        <v>4365</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>626262</v>
+        <v>626278</v>
       </c>
       <c r="R154" t="n">
-        <v>7217920</v>
+        <v>7217843</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103737</v>
+        <v>128103699</v>
       </c>
       <c r="B156" t="n">
-        <v>92644</v>
+        <v>91635</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4365</v>
+        <v>71</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626278</v>
+        <v>626262</v>
       </c>
       <c r="R156" t="n">
-        <v>7217843</v>
+        <v>7217920</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B157" t="n">
-        <v>92640</v>
+        <v>80132</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R157" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>80132</v>
+        <v>92640</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R158" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17249,32 +17249,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103770</v>
+        <v>128103808</v>
       </c>
       <c r="B159" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626249</v>
+        <v>626216</v>
       </c>
       <c r="R159" t="n">
-        <v>7218009</v>
+        <v>7217940</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17346,10 +17346,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103774</v>
+        <v>128103851</v>
       </c>
       <c r="B160" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17357,21 +17357,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626377</v>
+        <v>626264</v>
       </c>
       <c r="R160" t="n">
-        <v>7217880</v>
+        <v>7217994</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103768</v>
+        <v>128103770</v>
       </c>
       <c r="B161" t="n">
         <v>80132</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626272</v>
+        <v>626249</v>
       </c>
       <c r="R161" t="n">
-        <v>7217987</v>
+        <v>7218009</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,10 +17540,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103851</v>
+        <v>128103774</v>
       </c>
       <c r="B162" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17551,21 +17551,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626264</v>
+        <v>626377</v>
       </c>
       <c r="R162" t="n">
-        <v>7217994</v>
+        <v>7217880</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17637,32 +17637,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103808</v>
+        <v>128103768</v>
       </c>
       <c r="B163" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626216</v>
+        <v>626272</v>
       </c>
       <c r="R163" t="n">
-        <v>7217940</v>
+        <v>7217987</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103783</v>
+        <v>128103766</v>
       </c>
       <c r="B164" t="n">
-        <v>91733</v>
+        <v>80132</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>298</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626271</v>
+        <v>626308</v>
       </c>
       <c r="R164" t="n">
-        <v>7217852</v>
+        <v>7217938</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103766</v>
+        <v>128103736</v>
       </c>
       <c r="B165" t="n">
-        <v>80132</v>
+        <v>57669</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17842,34 +17842,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626308</v>
+        <v>626194</v>
       </c>
       <c r="R165" t="n">
-        <v>7217938</v>
+        <v>7217951</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17902,6 +17910,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17928,32 +17941,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103786</v>
+        <v>128103783</v>
       </c>
       <c r="B166" t="n">
-        <v>91823</v>
+        <v>91733</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5467</v>
+        <v>298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17963,10 +17976,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626319</v>
+        <v>626271</v>
       </c>
       <c r="R166" t="n">
-        <v>7217868</v>
+        <v>7217852</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18025,10 +18038,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103736</v>
+        <v>128103786</v>
       </c>
       <c r="B167" t="n">
-        <v>57669</v>
+        <v>91823</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18036,42 +18049,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>5467</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626194</v>
+        <v>626319</v>
       </c>
       <c r="R167" t="n">
-        <v>7217951</v>
+        <v>7217868</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18104,11 +18109,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18620,7 +18620,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103844</v>
+        <v>128103852</v>
       </c>
       <c r="B173" t="n">
         <v>79029</v>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626263</v>
+        <v>626320</v>
       </c>
       <c r="R173" t="n">
-        <v>7217877</v>
+        <v>7217901</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,10 +18717,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103852</v>
+        <v>128103792</v>
       </c>
       <c r="B174" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18728,21 +18728,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626320</v>
+        <v>626297</v>
       </c>
       <c r="R174" t="n">
-        <v>7217901</v>
+        <v>7217856</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18814,10 +18814,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103792</v>
+        <v>128103844</v>
       </c>
       <c r="B175" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18825,21 +18825,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626297</v>
+        <v>626263</v>
       </c>
       <c r="R175" t="n">
-        <v>7217856</v>
+        <v>7217877</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103845</v>
+        <v>128103727</v>
       </c>
       <c r="B179" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626363</v>
+        <v>626546</v>
       </c>
       <c r="R179" t="n">
-        <v>7217905</v>
+        <v>7217566</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19299,10 +19299,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103729</v>
+        <v>128103845</v>
       </c>
       <c r="B180" t="n">
-        <v>91300</v>
+        <v>79029</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19310,21 +19310,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626278</v>
+        <v>626363</v>
       </c>
       <c r="R180" t="n">
-        <v>7217843</v>
+        <v>7217905</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19396,32 +19396,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103727</v>
+        <v>128103729</v>
       </c>
       <c r="B181" t="n">
-        <v>80161</v>
+        <v>91300</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19431,10 +19431,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626546</v>
+        <v>626278</v>
       </c>
       <c r="R181" t="n">
-        <v>7217566</v>
+        <v>7217843</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103739</v>
+        <v>128103700</v>
       </c>
       <c r="B183" t="n">
-        <v>80133</v>
+        <v>91635</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2081</v>
+        <v>71</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626582</v>
+        <v>626271</v>
       </c>
       <c r="R183" t="n">
-        <v>7217455</v>
+        <v>7217852</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,32 +19700,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103700</v>
+        <v>128103695</v>
       </c>
       <c r="B184" t="n">
-        <v>91635</v>
+        <v>79647</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626271</v>
+        <v>626290</v>
       </c>
       <c r="R184" t="n">
-        <v>7217852</v>
+        <v>7217851</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,32 +19797,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103859</v>
+        <v>128103791</v>
       </c>
       <c r="B185" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626133</v>
+        <v>626290</v>
       </c>
       <c r="R185" t="n">
-        <v>7217998</v>
+        <v>7217851</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,32 +19894,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103759</v>
+        <v>128103859</v>
       </c>
       <c r="B186" t="n">
-        <v>80132</v>
+        <v>92640</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626350</v>
+        <v>626133</v>
       </c>
       <c r="R186" t="n">
-        <v>7217852</v>
+        <v>7217998</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,10 +19991,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103695</v>
+        <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20002,21 +20002,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626290</v>
+        <v>626350</v>
       </c>
       <c r="R187" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20185,10 +20185,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103791</v>
+        <v>128103739</v>
       </c>
       <c r="B189" t="n">
-        <v>78787</v>
+        <v>80133</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20196,21 +20196,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626290</v>
+        <v>626582</v>
       </c>
       <c r="R189" t="n">
-        <v>7217851</v>
+        <v>7217455</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11343,7 +11343,7 @@
         <v>128103836</v>
       </c>
       <c r="B99" t="n">
-        <v>90907</v>
+        <v>90908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11437,32 +11437,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103757</v>
+        <v>128103728</v>
       </c>
       <c r="B100" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626239</v>
+        <v>626453</v>
       </c>
       <c r="R100" t="n">
-        <v>7218007</v>
+        <v>7217719</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103728</v>
+        <v>128103850</v>
       </c>
       <c r="B101" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626453</v>
+        <v>626593</v>
       </c>
       <c r="R101" t="n">
-        <v>7217719</v>
+        <v>7217442</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11605,6 +11605,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11631,10 +11636,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103701</v>
+        <v>128103757</v>
       </c>
       <c r="B102" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11642,21 +11647,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11671,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626222</v>
+        <v>626239</v>
       </c>
       <c r="R102" t="n">
-        <v>7218014</v>
+        <v>7218007</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11728,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103850</v>
+        <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11739,21 +11744,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11763,10 +11768,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626593</v>
+        <v>626222</v>
       </c>
       <c r="R103" t="n">
-        <v>7217442</v>
+        <v>7218014</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,11 +11804,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11833,7 +11833,7 @@
         <v>128103703</v>
       </c>
       <c r="B104" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>128103812</v>
       </c>
       <c r="B106" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>128103806</v>
       </c>
       <c r="B107" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103716</v>
+        <v>128103870</v>
       </c>
       <c r="B111" t="n">
-        <v>57672</v>
+        <v>78007</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,42 +12533,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626454</v>
+        <v>626270</v>
       </c>
       <c r="R111" t="n">
-        <v>7217736</v>
+        <v>7217834</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12601,11 +12593,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12632,10 +12619,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103870</v>
+        <v>128103754</v>
       </c>
       <c r="B112" t="n">
-        <v>78007</v>
+        <v>80132</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12643,21 +12630,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12667,10 +12654,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626270</v>
+        <v>626325</v>
       </c>
       <c r="R112" t="n">
-        <v>7217834</v>
+        <v>7217934</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12729,7 +12716,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103754</v>
+        <v>128103765</v>
       </c>
       <c r="B113" t="n">
         <v>80132</v>
@@ -12764,10 +12751,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626325</v>
+        <v>626320</v>
       </c>
       <c r="R113" t="n">
-        <v>7217934</v>
+        <v>7217923</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12826,10 +12813,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103765</v>
+        <v>128103716</v>
       </c>
       <c r="B114" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12837,34 +12824,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R114" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12897,6 +12892,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13021,10 +13021,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103717</v>
+        <v>128103871</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>92635</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13032,42 +13032,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626217</v>
+        <v>626144</v>
       </c>
       <c r="R116" t="n">
-        <v>7217965</v>
+        <v>7217996</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13100,11 +13092,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13131,27 +13118,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103866</v>
+        <v>128103853</v>
       </c>
       <c r="B117" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13166,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626282</v>
+        <v>626328</v>
       </c>
       <c r="R117" t="n">
-        <v>7217980</v>
+        <v>7217861</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13228,32 +13215,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103871</v>
+        <v>128103866</v>
       </c>
       <c r="B118" t="n">
-        <v>92634</v>
+        <v>80167</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13263,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626144</v>
+        <v>626282</v>
       </c>
       <c r="R118" t="n">
-        <v>7217996</v>
+        <v>7217980</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13325,10 +13312,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103853</v>
+        <v>128103717</v>
       </c>
       <c r="B119" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,34 +13323,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626328</v>
+        <v>626217</v>
       </c>
       <c r="R119" t="n">
-        <v>7217861</v>
+        <v>7217965</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13396,6 +13391,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13422,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103831</v>
+        <v>128103733</v>
       </c>
       <c r="B120" t="n">
-        <v>98468</v>
+        <v>98490</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626373</v>
+        <v>626571</v>
       </c>
       <c r="R120" t="n">
-        <v>7217883</v>
+        <v>7217492</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,10 +13519,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103828</v>
+        <v>128103831</v>
       </c>
       <c r="B121" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13554,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626202</v>
+        <v>626373</v>
       </c>
       <c r="R121" t="n">
-        <v>7217956</v>
+        <v>7217883</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13616,32 +13616,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103733</v>
+        <v>128103828</v>
       </c>
       <c r="B122" t="n">
-        <v>98489</v>
+        <v>98469</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13651,10 +13651,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626571</v>
+        <v>626202</v>
       </c>
       <c r="R122" t="n">
-        <v>7217492</v>
+        <v>7217956</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13713,32 +13713,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103782</v>
+        <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>80168</v>
+        <v>91647</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626380</v>
+        <v>626128</v>
       </c>
       <c r="R123" t="n">
-        <v>7217892</v>
+        <v>7218027</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13810,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103756</v>
+        <v>128103721</v>
       </c>
       <c r="B124" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,34 +13821,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626277</v>
+        <v>626306</v>
       </c>
       <c r="R124" t="n">
-        <v>7217976</v>
+        <v>7217910</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,6 +13889,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13907,32 +13920,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103772</v>
+        <v>128103824</v>
       </c>
       <c r="B125" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13955,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626347</v>
+        <v>626300</v>
       </c>
       <c r="R125" t="n">
-        <v>7217886</v>
+        <v>7217895</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14004,10 +14017,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103842</v>
+        <v>128103746</v>
       </c>
       <c r="B126" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14015,21 +14028,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14039,10 +14052,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626317</v>
+        <v>626290</v>
       </c>
       <c r="R126" t="n">
-        <v>7217935</v>
+        <v>7217851</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14083,6 +14096,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14101,32 +14115,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103740</v>
+        <v>128103782</v>
       </c>
       <c r="B127" t="n">
-        <v>91646</v>
+        <v>80168</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14136,10 +14150,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626128</v>
+        <v>626380</v>
       </c>
       <c r="R127" t="n">
-        <v>7218027</v>
+        <v>7217892</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14198,10 +14212,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103721</v>
+        <v>128103756</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14209,42 +14223,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626306</v>
+        <v>626277</v>
       </c>
       <c r="R128" t="n">
-        <v>7217910</v>
+        <v>7217976</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14277,11 +14283,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14308,32 +14309,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103824</v>
+        <v>128103772</v>
       </c>
       <c r="B129" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14343,10 +14344,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626300</v>
+        <v>626347</v>
       </c>
       <c r="R129" t="n">
-        <v>7217895</v>
+        <v>7217886</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14405,10 +14406,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103746</v>
+        <v>128103842</v>
       </c>
       <c r="B130" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14416,21 +14417,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14440,10 +14441,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626290</v>
+        <v>626317</v>
       </c>
       <c r="R130" t="n">
-        <v>7217851</v>
+        <v>7217935</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14484,7 +14485,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14600,32 +14600,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103867</v>
+        <v>128103696</v>
       </c>
       <c r="B132" t="n">
-        <v>80167</v>
+        <v>91636</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6463</v>
+        <v>71</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626346</v>
+        <v>626167</v>
       </c>
       <c r="R132" t="n">
-        <v>7217883</v>
+        <v>7217957</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14697,48 +14697,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103787</v>
+        <v>128103867</v>
       </c>
       <c r="B133" t="n">
-        <v>91722</v>
+        <v>80167</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1505</v>
+        <v>6463</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626280</v>
+        <v>626346</v>
       </c>
       <c r="R133" t="n">
-        <v>7217822</v>
+        <v>7217883</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14779,7 +14776,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14798,45 +14794,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103696</v>
+        <v>128103787</v>
       </c>
       <c r="B134" t="n">
-        <v>91635</v>
+        <v>91723</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>71</v>
+        <v>1505</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626167</v>
+        <v>626280</v>
       </c>
       <c r="R134" t="n">
-        <v>7217957</v>
+        <v>7217822</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14877,6 +14876,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -15008,7 +15008,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B138" t="n">
         <v>80132</v>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R138" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,10 +15296,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103769</v>
+        <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>90908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15307,21 +15307,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>900</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626248</v>
+        <v>626354</v>
       </c>
       <c r="R139" t="n">
-        <v>7218007</v>
+        <v>7217769</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,10 +15393,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103835</v>
+        <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>90907</v>
+        <v>80132</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15404,21 +15404,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>900</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626354</v>
+        <v>626370</v>
       </c>
       <c r="R140" t="n">
-        <v>7217769</v>
+        <v>7217900</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15493,7 +15493,7 @@
         <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>128103743</v>
       </c>
       <c r="B145" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>128103857</v>
       </c>
       <c r="B146" t="n">
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>128103839</v>
       </c>
       <c r="B149" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16363,32 +16363,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103807</v>
+        <v>128103704</v>
       </c>
       <c r="B150" t="n">
-        <v>98468</v>
+        <v>91351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626532</v>
+        <v>626182</v>
       </c>
       <c r="R150" t="n">
-        <v>7217568</v>
+        <v>7218029</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,45 +16460,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103829</v>
+        <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>98468</v>
+        <v>57669</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626217</v>
+        <v>626159</v>
       </c>
       <c r="R151" t="n">
-        <v>7217956</v>
+        <v>7217940</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16531,6 +16539,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16557,32 +16570,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103704</v>
+        <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>91350</v>
+        <v>98469</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16592,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626182</v>
+        <v>626217</v>
       </c>
       <c r="R152" t="n">
-        <v>7218029</v>
+        <v>7217956</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16654,53 +16667,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103735</v>
+        <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>57669</v>
+        <v>98469</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626159</v>
+        <v>626532</v>
       </c>
       <c r="R153" t="n">
-        <v>7217940</v>
+        <v>7217568</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16733,11 +16738,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16764,32 +16764,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128103737</v>
+        <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>92644</v>
+        <v>91636</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4365</v>
+        <v>71</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>626278</v>
+        <v>626262</v>
       </c>
       <c r="R154" t="n">
-        <v>7217843</v>
+        <v>7217920</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103699</v>
+        <v>128103737</v>
       </c>
       <c r="B156" t="n">
-        <v>91635</v>
+        <v>92645</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>71</v>
+        <v>4365</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626262</v>
+        <v>626278</v>
       </c>
       <c r="R156" t="n">
-        <v>7217920</v>
+        <v>7217843</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17155,7 +17155,7 @@
         <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17249,32 +17249,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103808</v>
+        <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626216</v>
+        <v>626264</v>
       </c>
       <c r="R159" t="n">
-        <v>7217940</v>
+        <v>7217994</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17346,10 +17346,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103851</v>
+        <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17357,21 +17357,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626264</v>
+        <v>626249</v>
       </c>
       <c r="R160" t="n">
-        <v>7217994</v>
+        <v>7218009</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103770</v>
+        <v>128103774</v>
       </c>
       <c r="B161" t="n">
         <v>80132</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626249</v>
+        <v>626377</v>
       </c>
       <c r="R161" t="n">
-        <v>7218009</v>
+        <v>7217880</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,7 +17540,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103774</v>
+        <v>128103768</v>
       </c>
       <c r="B162" t="n">
         <v>80132</v>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626377</v>
+        <v>626272</v>
       </c>
       <c r="R162" t="n">
-        <v>7217880</v>
+        <v>7217987</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17637,32 +17637,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103768</v>
+        <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626272</v>
+        <v>626216</v>
       </c>
       <c r="R163" t="n">
-        <v>7217987</v>
+        <v>7217940</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103766</v>
+        <v>128103823</v>
       </c>
       <c r="B164" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626308</v>
+        <v>626337</v>
       </c>
       <c r="R164" t="n">
-        <v>7217938</v>
+        <v>7217840</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,53 +17831,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103736</v>
+        <v>128103813</v>
       </c>
       <c r="B165" t="n">
-        <v>57669</v>
+        <v>98469</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626194</v>
+        <v>626370</v>
       </c>
       <c r="R165" t="n">
-        <v>7217951</v>
+        <v>7217900</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17910,11 +17902,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17941,32 +17928,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103783</v>
+        <v>128103766</v>
       </c>
       <c r="B166" t="n">
-        <v>91733</v>
+        <v>80132</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>298</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17976,10 +17963,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626271</v>
+        <v>626308</v>
       </c>
       <c r="R166" t="n">
-        <v>7217852</v>
+        <v>7217938</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18041,7 +18028,7 @@
         <v>128103786</v>
       </c>
       <c r="B167" t="n">
-        <v>91823</v>
+        <v>91824</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18135,10 +18122,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103823</v>
+        <v>128103783</v>
       </c>
       <c r="B168" t="n">
-        <v>98468</v>
+        <v>91734</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18146,21 +18133,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18170,10 +18157,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626337</v>
+        <v>626271</v>
       </c>
       <c r="R168" t="n">
-        <v>7217840</v>
+        <v>7217852</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18232,45 +18219,53 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103813</v>
+        <v>128103736</v>
       </c>
       <c r="B169" t="n">
-        <v>98468</v>
+        <v>57669</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626370</v>
+        <v>626194</v>
       </c>
       <c r="R169" t="n">
-        <v>7217900</v>
+        <v>7217951</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18303,6 +18298,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18429,7 +18429,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103793</v>
+        <v>128103792</v>
       </c>
       <c r="B172" t="n">
         <v>78787</v>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626317</v>
+        <v>626297</v>
       </c>
       <c r="R172" t="n">
-        <v>7217867</v>
+        <v>7217856</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,32 +18620,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103852</v>
+        <v>128103825</v>
       </c>
       <c r="B173" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626320</v>
+        <v>626215</v>
       </c>
       <c r="R173" t="n">
-        <v>7217901</v>
+        <v>7218004</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,7 +18717,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103792</v>
+        <v>128103793</v>
       </c>
       <c r="B174" t="n">
         <v>78787</v>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626297</v>
+        <v>626317</v>
       </c>
       <c r="R174" t="n">
-        <v>7217856</v>
+        <v>7217867</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18911,32 +18911,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103825</v>
+        <v>128103852</v>
       </c>
       <c r="B176" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626215</v>
+        <v>626320</v>
       </c>
       <c r="R176" t="n">
-        <v>7218004</v>
+        <v>7217901</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19108,7 +19108,7 @@
         <v>128103692</v>
       </c>
       <c r="B178" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>128103729</v>
       </c>
       <c r="B181" t="n">
-        <v>91300</v>
+        <v>91301</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103700</v>
+        <v>128103759</v>
       </c>
       <c r="B183" t="n">
-        <v>91635</v>
+        <v>80132</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>71</v>
+        <v>6458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,7 +19638,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626271</v>
+        <v>626350</v>
       </c>
       <c r="R183" t="n">
         <v>7217852</v>
@@ -19797,10 +19797,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103791</v>
+        <v>128103761</v>
       </c>
       <c r="B185" t="n">
-        <v>78787</v>
+        <v>80132</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19808,21 +19808,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626290</v>
+        <v>626398</v>
       </c>
       <c r="R185" t="n">
-        <v>7217851</v>
+        <v>7217759</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,32 +19894,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103859</v>
+        <v>128103791</v>
       </c>
       <c r="B186" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626133</v>
+        <v>626290</v>
       </c>
       <c r="R186" t="n">
-        <v>7217998</v>
+        <v>7217851</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,32 +19991,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103759</v>
+        <v>128103859</v>
       </c>
       <c r="B187" t="n">
-        <v>80132</v>
+        <v>92641</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626350</v>
+        <v>626133</v>
       </c>
       <c r="R187" t="n">
-        <v>7217852</v>
+        <v>7217998</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,10 +20088,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103761</v>
+        <v>128103739</v>
       </c>
       <c r="B188" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20099,21 +20099,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626398</v>
+        <v>626582</v>
       </c>
       <c r="R188" t="n">
-        <v>7217759</v>
+        <v>7217455</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20185,32 +20185,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103739</v>
+        <v>128103822</v>
       </c>
       <c r="B189" t="n">
-        <v>80133</v>
+        <v>98469</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626582</v>
+        <v>626528</v>
       </c>
       <c r="R189" t="n">
-        <v>7217455</v>
+        <v>7217613</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20282,32 +20282,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128103822</v>
+        <v>128103700</v>
       </c>
       <c r="B190" t="n">
-        <v>98468</v>
+        <v>91636</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>71</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>626528</v>
+        <v>626271</v>
       </c>
       <c r="R190" t="n">
-        <v>7217613</v>
+        <v>7217852</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103784</v>
+        <v>128103836</v>
       </c>
       <c r="B97" t="n">
-        <v>57776</v>
+        <v>90909</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>900</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626608</v>
+        <v>626328</v>
       </c>
       <c r="R97" t="n">
-        <v>7217437</v>
+        <v>7217861</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103745</v>
+        <v>128103784</v>
       </c>
       <c r="B98" t="n">
-        <v>78788</v>
+        <v>57776</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626149</v>
+        <v>626608</v>
       </c>
       <c r="R98" t="n">
-        <v>7217977</v>
+        <v>7217437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,7 +11321,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11340,10 +11339,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>90908</v>
+        <v>78788</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11351,21 +11350,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11375,10 +11374,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R99" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11419,6 +11418,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11437,32 +11437,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103728</v>
+        <v>128103757</v>
       </c>
       <c r="B100" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626453</v>
+        <v>626239</v>
       </c>
       <c r="R100" t="n">
-        <v>7217719</v>
+        <v>7218007</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103850</v>
+        <v>128103728</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626593</v>
+        <v>626453</v>
       </c>
       <c r="R101" t="n">
-        <v>7217442</v>
+        <v>7217719</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11605,11 +11605,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11636,10 +11631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103757</v>
+        <v>128103850</v>
       </c>
       <c r="B102" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11647,21 +11642,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11671,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626239</v>
+        <v>626593</v>
       </c>
       <c r="R102" t="n">
-        <v>7218007</v>
+        <v>7217442</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11707,6 +11702,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11736,7 +11736,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>128103703</v>
       </c>
       <c r="B104" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>128103812</v>
       </c>
       <c r="B106" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>128103806</v>
       </c>
       <c r="B107" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103870</v>
+        <v>128103744</v>
       </c>
       <c r="B111" t="n">
-        <v>78007</v>
+        <v>78788</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626270</v>
+        <v>626454</v>
       </c>
       <c r="R111" t="n">
-        <v>7217834</v>
+        <v>7217736</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12601,6 +12601,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12619,10 +12620,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103754</v>
+        <v>128103870</v>
       </c>
       <c r="B112" t="n">
-        <v>80132</v>
+        <v>78007</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12630,21 +12631,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12654,10 +12655,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626325</v>
+        <v>626270</v>
       </c>
       <c r="R112" t="n">
-        <v>7217934</v>
+        <v>7217834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12716,7 +12717,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103765</v>
+        <v>128103754</v>
       </c>
       <c r="B113" t="n">
         <v>80132</v>
@@ -12751,10 +12752,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626320</v>
+        <v>626325</v>
       </c>
       <c r="R113" t="n">
-        <v>7217923</v>
+        <v>7217934</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12813,10 +12814,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103716</v>
+        <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12824,42 +12825,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626454</v>
+        <v>626320</v>
       </c>
       <c r="R114" t="n">
-        <v>7217736</v>
+        <v>7217923</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12892,11 +12885,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12923,10 +12911,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103744</v>
+        <v>128103716</v>
       </c>
       <c r="B115" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12934,24 +12922,32 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
@@ -12996,13 +12992,17 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103871</v>
+        <v>128103866</v>
       </c>
       <c r="B116" t="n">
-        <v>92635</v>
+        <v>80167</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626144</v>
+        <v>626282</v>
       </c>
       <c r="R116" t="n">
-        <v>7217996</v>
+        <v>7217980</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,10 +13118,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103853</v>
+        <v>128103871</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>92636</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13129,21 +13129,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626328</v>
+        <v>626144</v>
       </c>
       <c r="R117" t="n">
-        <v>7217861</v>
+        <v>7217996</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13215,27 +13215,27 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103866</v>
+        <v>128103853</v>
       </c>
       <c r="B118" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -13250,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626282</v>
+        <v>626328</v>
       </c>
       <c r="R118" t="n">
-        <v>7217980</v>
+        <v>7217861</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103733</v>
+        <v>128103831</v>
       </c>
       <c r="B120" t="n">
-        <v>98490</v>
+        <v>98470</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626571</v>
+        <v>626373</v>
       </c>
       <c r="R120" t="n">
-        <v>7217492</v>
+        <v>7217883</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,10 +13519,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103831</v>
+        <v>128103828</v>
       </c>
       <c r="B121" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13554,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626373</v>
+        <v>626202</v>
       </c>
       <c r="R121" t="n">
-        <v>7217883</v>
+        <v>7217956</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13616,32 +13616,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103828</v>
+        <v>128103733</v>
       </c>
       <c r="B122" t="n">
-        <v>98469</v>
+        <v>98491</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13651,10 +13651,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626202</v>
+        <v>626571</v>
       </c>
       <c r="R122" t="n">
-        <v>7217956</v>
+        <v>7217492</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13716,7 +13716,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13810,53 +13810,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103721</v>
+        <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626306</v>
+        <v>626380</v>
       </c>
       <c r="R124" t="n">
-        <v>7217910</v>
+        <v>7217892</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,11 +13881,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13920,32 +13907,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103824</v>
+        <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13955,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626300</v>
+        <v>626277</v>
       </c>
       <c r="R125" t="n">
-        <v>7217895</v>
+        <v>7217976</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14017,10 +14004,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103746</v>
+        <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14028,21 +14015,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14052,10 +14039,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626290</v>
+        <v>626347</v>
       </c>
       <c r="R126" t="n">
-        <v>7217851</v>
+        <v>7217886</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14096,7 +14083,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14115,32 +14101,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103782</v>
+        <v>128103824</v>
       </c>
       <c r="B127" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14150,10 +14136,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626380</v>
+        <v>626300</v>
       </c>
       <c r="R127" t="n">
-        <v>7217892</v>
+        <v>7217895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14212,10 +14198,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103756</v>
+        <v>128103746</v>
       </c>
       <c r="B128" t="n">
-        <v>80132</v>
+        <v>78788</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14223,21 +14209,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14247,10 +14233,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626277</v>
+        <v>626290</v>
       </c>
       <c r="R128" t="n">
-        <v>7217976</v>
+        <v>7217851</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14291,6 +14277,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14309,10 +14296,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103772</v>
+        <v>128103842</v>
       </c>
       <c r="B129" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14320,21 +14307,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14344,10 +14331,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626347</v>
+        <v>626317</v>
       </c>
       <c r="R129" t="n">
-        <v>7217886</v>
+        <v>7217935</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14406,10 +14393,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103842</v>
+        <v>128103721</v>
       </c>
       <c r="B130" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14417,34 +14404,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626317</v>
+        <v>626306</v>
       </c>
       <c r="R130" t="n">
-        <v>7217935</v>
+        <v>7217910</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14477,6 +14472,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14503,32 +14503,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103781</v>
+        <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>80168</v>
+        <v>91637</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6464</v>
+        <v>71</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14538,10 +14538,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626239</v>
+        <v>626167</v>
       </c>
       <c r="R131" t="n">
-        <v>7218007</v>
+        <v>7217957</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14600,45 +14600,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103696</v>
+        <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91636</v>
+        <v>91724</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>71</v>
+        <v>1505</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626167</v>
+        <v>626280</v>
       </c>
       <c r="R132" t="n">
-        <v>7217957</v>
+        <v>7217822</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14679,6 +14682,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14697,10 +14701,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103867</v>
+        <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14708,21 +14712,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14732,10 +14736,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626346</v>
+        <v>626239</v>
       </c>
       <c r="R133" t="n">
-        <v>7217883</v>
+        <v>7218007</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14794,48 +14798,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103787</v>
+        <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>91723</v>
+        <v>80167</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1505</v>
+        <v>6463</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626280</v>
+        <v>626346</v>
       </c>
       <c r="R134" t="n">
-        <v>7217822</v>
+        <v>7217883</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,7 +14877,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -15008,7 +15008,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15199,10 +15199,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103769</v>
+        <v>128103835</v>
       </c>
       <c r="B138" t="n">
-        <v>80132</v>
+        <v>90909</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15210,21 +15210,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>900</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626248</v>
+        <v>626354</v>
       </c>
       <c r="R138" t="n">
-        <v>7218007</v>
+        <v>7217769</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,10 +15296,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103835</v>
+        <v>128103773</v>
       </c>
       <c r="B139" t="n">
-        <v>90908</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15307,21 +15307,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>900</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626354</v>
+        <v>626370</v>
       </c>
       <c r="R139" t="n">
-        <v>7217769</v>
+        <v>7217900</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B140" t="n">
         <v>80132</v>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R140" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15493,7 +15493,7 @@
         <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15684,10 +15684,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103843</v>
+        <v>128103743</v>
       </c>
       <c r="B143" t="n">
-        <v>79029</v>
+        <v>92634</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15695,21 +15695,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626276</v>
+        <v>626130</v>
       </c>
       <c r="R143" t="n">
-        <v>7217891</v>
+        <v>7218000</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,27 +15781,27 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103863</v>
+        <v>128103843</v>
       </c>
       <c r="B144" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626248</v>
+        <v>626276</v>
       </c>
       <c r="R144" t="n">
-        <v>7218007</v>
+        <v>7217891</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,32 +15878,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103743</v>
+        <v>128103863</v>
       </c>
       <c r="B145" t="n">
-        <v>92633</v>
+        <v>80167</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626130</v>
+        <v>626248</v>
       </c>
       <c r="R145" t="n">
-        <v>7218000</v>
+        <v>7218007</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15978,7 +15978,7 @@
         <v>128103857</v>
       </c>
       <c r="B146" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103753</v>
+        <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>80132</v>
+        <v>91370</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,21 +16083,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626465</v>
+        <v>626215</v>
       </c>
       <c r="R147" t="n">
-        <v>7217693</v>
+        <v>7218028</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,10 +16169,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103763</v>
+        <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16180,21 +16180,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626343</v>
+        <v>626182</v>
       </c>
       <c r="R148" t="n">
-        <v>7217927</v>
+        <v>7218029</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103839</v>
+        <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>91369</v>
+        <v>80132</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16277,21 +16277,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626215</v>
+        <v>626465</v>
       </c>
       <c r="R149" t="n">
-        <v>7218028</v>
+        <v>7217693</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,10 +16363,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103704</v>
+        <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>91351</v>
+        <v>80132</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16374,21 +16374,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626182</v>
+        <v>626343</v>
       </c>
       <c r="R150" t="n">
-        <v>7218029</v>
+        <v>7217927</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16573,7 +16573,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91636</v>
+        <v>91637</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>128103737</v>
       </c>
       <c r="B156" t="n">
-        <v>92645</v>
+        <v>92646</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92641</v>
+        <v>80132</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17249,10 +17249,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103851</v>
+        <v>128103770</v>
       </c>
       <c r="B159" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17260,21 +17260,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626264</v>
+        <v>626249</v>
       </c>
       <c r="R159" t="n">
-        <v>7217994</v>
+        <v>7218009</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17346,7 +17346,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103770</v>
+        <v>128103774</v>
       </c>
       <c r="B160" t="n">
         <v>80132</v>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626249</v>
+        <v>626377</v>
       </c>
       <c r="R160" t="n">
-        <v>7218009</v>
+        <v>7217880</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103774</v>
+        <v>128103768</v>
       </c>
       <c r="B161" t="n">
         <v>80132</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626377</v>
+        <v>626272</v>
       </c>
       <c r="R161" t="n">
-        <v>7217880</v>
+        <v>7217987</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,10 +17540,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103768</v>
+        <v>128103851</v>
       </c>
       <c r="B162" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17551,21 +17551,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626272</v>
+        <v>626264</v>
       </c>
       <c r="R162" t="n">
-        <v>7217987</v>
+        <v>7217994</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17640,7 +17640,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103823</v>
+        <v>128103786</v>
       </c>
       <c r="B164" t="n">
-        <v>98469</v>
+        <v>91825</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626337</v>
+        <v>626319</v>
       </c>
       <c r="R164" t="n">
-        <v>7217840</v>
+        <v>7217868</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103813</v>
+        <v>128103783</v>
       </c>
       <c r="B165" t="n">
-        <v>98469</v>
+        <v>91735</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17842,21 +17842,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626370</v>
+        <v>626271</v>
       </c>
       <c r="R165" t="n">
-        <v>7217900</v>
+        <v>7217852</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18025,10 +18025,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103786</v>
+        <v>128103736</v>
       </c>
       <c r="B167" t="n">
-        <v>91824</v>
+        <v>57669</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18036,34 +18036,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626319</v>
+        <v>626194</v>
       </c>
       <c r="R167" t="n">
-        <v>7217868</v>
+        <v>7217951</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18096,6 +18104,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18122,10 +18135,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103783</v>
+        <v>128103823</v>
       </c>
       <c r="B168" t="n">
-        <v>91734</v>
+        <v>98470</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18133,21 +18146,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>298</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18157,10 +18170,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626271</v>
+        <v>626337</v>
       </c>
       <c r="R168" t="n">
-        <v>7217852</v>
+        <v>7217840</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18219,53 +18232,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103736</v>
+        <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626194</v>
+        <v>626370</v>
       </c>
       <c r="R169" t="n">
-        <v>7217951</v>
+        <v>7217900</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18298,11 +18303,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18329,32 +18329,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128103785</v>
+        <v>128103809</v>
       </c>
       <c r="B170" t="n">
-        <v>57776</v>
+        <v>98470</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>626322</v>
+        <v>626232</v>
       </c>
       <c r="R170" t="n">
-        <v>7217855</v>
+        <v>7217960</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18426,32 +18426,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128103809</v>
+        <v>128103785</v>
       </c>
       <c r="B171" t="n">
-        <v>98469</v>
+        <v>57776</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18461,10 +18461,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>626232</v>
+        <v>626322</v>
       </c>
       <c r="R171" t="n">
-        <v>7217960</v>
+        <v>7217855</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18523,32 +18523,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103792</v>
+        <v>128103825</v>
       </c>
       <c r="B172" t="n">
-        <v>78787</v>
+        <v>98470</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626297</v>
+        <v>626215</v>
       </c>
       <c r="R172" t="n">
-        <v>7217856</v>
+        <v>7218004</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,32 +18620,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103825</v>
+        <v>128103793</v>
       </c>
       <c r="B173" t="n">
-        <v>98469</v>
+        <v>78787</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626215</v>
+        <v>626317</v>
       </c>
       <c r="R173" t="n">
-        <v>7218004</v>
+        <v>7217867</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,7 +18717,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103793</v>
+        <v>128103792</v>
       </c>
       <c r="B174" t="n">
         <v>78787</v>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626317</v>
+        <v>626297</v>
       </c>
       <c r="R174" t="n">
-        <v>7217867</v>
+        <v>7217856</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18814,7 +18814,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103844</v>
+        <v>128103852</v>
       </c>
       <c r="B175" t="n">
         <v>79029</v>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626263</v>
+        <v>626320</v>
       </c>
       <c r="R175" t="n">
-        <v>7217877</v>
+        <v>7217901</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18911,7 +18911,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103852</v>
+        <v>128103844</v>
       </c>
       <c r="B176" t="n">
         <v>79029</v>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626320</v>
+        <v>626263</v>
       </c>
       <c r="R176" t="n">
-        <v>7217901</v>
+        <v>7217877</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19008,32 +19008,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128103758</v>
+        <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>80132</v>
+        <v>91317</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19043,10 +19043,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>626196</v>
+        <v>626320</v>
       </c>
       <c r="R177" t="n">
-        <v>7218053</v>
+        <v>7217864</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,32 +19105,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128103692</v>
+        <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>91316</v>
+        <v>80132</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19140,10 +19140,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>626320</v>
+        <v>626196</v>
       </c>
       <c r="R178" t="n">
-        <v>7217864</v>
+        <v>7218053</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103727</v>
+        <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>80161</v>
+        <v>91302</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626546</v>
+        <v>626278</v>
       </c>
       <c r="R179" t="n">
-        <v>7217566</v>
+        <v>7217843</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19299,32 +19299,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103845</v>
+        <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626363</v>
+        <v>626546</v>
       </c>
       <c r="R180" t="n">
-        <v>7217905</v>
+        <v>7217566</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19396,10 +19396,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103729</v>
+        <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>91301</v>
+        <v>79029</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19407,21 +19407,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19431,10 +19431,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626278</v>
+        <v>626363</v>
       </c>
       <c r="R181" t="n">
-        <v>7217843</v>
+        <v>7217905</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19991,32 +19991,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103859</v>
+        <v>128103700</v>
       </c>
       <c r="B187" t="n">
-        <v>92641</v>
+        <v>91637</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626133</v>
+        <v>626271</v>
       </c>
       <c r="R187" t="n">
-        <v>7217998</v>
+        <v>7217852</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,32 +20088,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103739</v>
+        <v>128103859</v>
       </c>
       <c r="B188" t="n">
-        <v>80133</v>
+        <v>92642</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626582</v>
+        <v>626133</v>
       </c>
       <c r="R188" t="n">
-        <v>7217455</v>
+        <v>7217998</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20185,32 +20185,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103822</v>
+        <v>128103739</v>
       </c>
       <c r="B189" t="n">
-        <v>98469</v>
+        <v>80133</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626528</v>
+        <v>626582</v>
       </c>
       <c r="R189" t="n">
-        <v>7217613</v>
+        <v>7217455</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20282,32 +20282,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128103700</v>
+        <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>91636</v>
+        <v>98470</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>71</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>626271</v>
+        <v>626528</v>
       </c>
       <c r="R190" t="n">
-        <v>7217852</v>
+        <v>7217613</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103784</v>
+        <v>128103745</v>
       </c>
       <c r="B98" t="n">
-        <v>57776</v>
+        <v>78788</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626608</v>
+        <v>626149</v>
       </c>
       <c r="R98" t="n">
-        <v>7217437</v>
+        <v>7217977</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,6 +11321,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11339,32 +11340,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103745</v>
+        <v>128103784</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>57776</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11374,10 +11375,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626149</v>
+        <v>626608</v>
       </c>
       <c r="R99" t="n">
-        <v>7217977</v>
+        <v>7217437</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11418,7 +11419,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103744</v>
+        <v>128103870</v>
       </c>
       <c r="B111" t="n">
-        <v>78788</v>
+        <v>78007</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626454</v>
+        <v>626270</v>
       </c>
       <c r="R111" t="n">
-        <v>7217736</v>
+        <v>7217834</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12601,7 +12601,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12620,10 +12619,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103870</v>
+        <v>128103754</v>
       </c>
       <c r="B112" t="n">
-        <v>78007</v>
+        <v>80132</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12631,21 +12630,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12655,10 +12654,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626270</v>
+        <v>626325</v>
       </c>
       <c r="R112" t="n">
-        <v>7217834</v>
+        <v>7217934</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12717,7 +12716,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103754</v>
+        <v>128103765</v>
       </c>
       <c r="B113" t="n">
         <v>80132</v>
@@ -12752,10 +12751,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626325</v>
+        <v>626320</v>
       </c>
       <c r="R113" t="n">
-        <v>7217934</v>
+        <v>7217923</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12814,10 +12813,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103765</v>
+        <v>128103716</v>
       </c>
       <c r="B114" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12825,34 +12824,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R114" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12885,6 +12892,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12911,10 +12923,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103716</v>
+        <v>128103744</v>
       </c>
       <c r="B115" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12922,32 +12934,24 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
@@ -12992,17 +12996,13 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103866</v>
+        <v>128103831</v>
       </c>
       <c r="B116" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626282</v>
+        <v>626373</v>
       </c>
       <c r="R116" t="n">
-        <v>7217980</v>
+        <v>7217883</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,32 +13118,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103871</v>
+        <v>128103828</v>
       </c>
       <c r="B117" t="n">
-        <v>92636</v>
+        <v>98470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626144</v>
+        <v>626202</v>
       </c>
       <c r="R117" t="n">
-        <v>7217996</v>
+        <v>7217956</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13215,32 +13215,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103853</v>
+        <v>128103733</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13250,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626328</v>
+        <v>626571</v>
       </c>
       <c r="R118" t="n">
-        <v>7217861</v>
+        <v>7217492</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13312,53 +13312,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103717</v>
+        <v>128103866</v>
       </c>
       <c r="B119" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626217</v>
+        <v>626282</v>
       </c>
       <c r="R119" t="n">
-        <v>7217965</v>
+        <v>7217980</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13391,11 +13383,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13422,32 +13409,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103831</v>
+        <v>128103853</v>
       </c>
       <c r="B120" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13444,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626373</v>
+        <v>626328</v>
       </c>
       <c r="R120" t="n">
-        <v>7217883</v>
+        <v>7217861</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,32 +13506,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103828</v>
+        <v>128103871</v>
       </c>
       <c r="B121" t="n">
-        <v>98470</v>
+        <v>92636</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13554,10 +13541,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626202</v>
+        <v>626144</v>
       </c>
       <c r="R121" t="n">
-        <v>7217956</v>
+        <v>7217996</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13616,45 +13603,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103733</v>
+        <v>128103717</v>
       </c>
       <c r="B122" t="n">
-        <v>98491</v>
+        <v>57672</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626571</v>
+        <v>626217</v>
       </c>
       <c r="R122" t="n">
-        <v>7217492</v>
+        <v>7217965</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13687,6 +13682,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13810,32 +13810,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103782</v>
+        <v>128103824</v>
       </c>
       <c r="B124" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13845,10 +13845,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626380</v>
+        <v>626300</v>
       </c>
       <c r="R124" t="n">
-        <v>7217892</v>
+        <v>7217895</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13907,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103756</v>
+        <v>128103746</v>
       </c>
       <c r="B125" t="n">
-        <v>80132</v>
+        <v>78788</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13918,21 +13918,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626277</v>
+        <v>626290</v>
       </c>
       <c r="R125" t="n">
-        <v>7217976</v>
+        <v>7217851</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13986,6 +13986,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14004,32 +14005,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103772</v>
+        <v>128103782</v>
       </c>
       <c r="B126" t="n">
-        <v>80132</v>
+        <v>80168</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14039,10 +14040,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626347</v>
+        <v>626380</v>
       </c>
       <c r="R126" t="n">
-        <v>7217886</v>
+        <v>7217892</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14101,32 +14102,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103824</v>
+        <v>128103756</v>
       </c>
       <c r="B127" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14136,10 +14137,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626300</v>
+        <v>626277</v>
       </c>
       <c r="R127" t="n">
-        <v>7217895</v>
+        <v>7217976</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14198,10 +14199,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103746</v>
+        <v>128103772</v>
       </c>
       <c r="B128" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14209,21 +14210,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14233,10 +14234,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626290</v>
+        <v>626347</v>
       </c>
       <c r="R128" t="n">
-        <v>7217851</v>
+        <v>7217886</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14277,7 +14278,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14600,37 +14600,42 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103787</v>
+        <v>128103856</v>
       </c>
       <c r="B132" t="n">
-        <v>91724</v>
+        <v>57672</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1505</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14638,10 +14643,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626280</v>
+        <v>626323</v>
       </c>
       <c r="R132" t="n">
-        <v>7217822</v>
+        <v>7217908</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14676,13 +14681,17 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14701,32 +14710,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103781</v>
+        <v>128103811</v>
       </c>
       <c r="B133" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14736,10 +14745,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626239</v>
+        <v>626311</v>
       </c>
       <c r="R133" t="n">
-        <v>7218007</v>
+        <v>7217865</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14798,32 +14807,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103867</v>
+        <v>128103827</v>
       </c>
       <c r="B134" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14833,10 +14842,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626346</v>
+        <v>626128</v>
       </c>
       <c r="R134" t="n">
-        <v>7217883</v>
+        <v>7218027</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14895,42 +14904,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103856</v>
+        <v>128103787</v>
       </c>
       <c r="B135" t="n">
-        <v>57672</v>
+        <v>91724</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>1505</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14938,10 +14942,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626323</v>
+        <v>626280</v>
       </c>
       <c r="R135" t="n">
-        <v>7217908</v>
+        <v>7217822</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14976,17 +14980,13 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15005,32 +15005,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103811</v>
+        <v>128103781</v>
       </c>
       <c r="B136" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15040,10 +15040,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626311</v>
+        <v>626239</v>
       </c>
       <c r="R136" t="n">
-        <v>7217865</v>
+        <v>7218007</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15102,32 +15102,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103827</v>
+        <v>128103867</v>
       </c>
       <c r="B137" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626128</v>
+        <v>626346</v>
       </c>
       <c r="R137" t="n">
-        <v>7218027</v>
+        <v>7217883</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15199,10 +15199,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103835</v>
+        <v>128103773</v>
       </c>
       <c r="B138" t="n">
-        <v>90909</v>
+        <v>80132</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15210,21 +15210,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>900</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626354</v>
+        <v>626370</v>
       </c>
       <c r="R138" t="n">
-        <v>7217769</v>
+        <v>7217900</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103773</v>
+        <v>128103810</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626370</v>
+        <v>626290</v>
       </c>
       <c r="R139" t="n">
-        <v>7217900</v>
+        <v>7217851</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103769</v>
+        <v>128103837</v>
       </c>
       <c r="B140" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626248</v>
+        <v>626194</v>
       </c>
       <c r="R140" t="n">
-        <v>7218007</v>
+        <v>7218055</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103810</v>
+        <v>128103835</v>
       </c>
       <c r="B141" t="n">
-        <v>98470</v>
+        <v>90909</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>900</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626290</v>
+        <v>626354</v>
       </c>
       <c r="R141" t="n">
-        <v>7217851</v>
+        <v>7217769</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103837</v>
+        <v>128103769</v>
       </c>
       <c r="B142" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626194</v>
+        <v>626248</v>
       </c>
       <c r="R142" t="n">
-        <v>7218055</v>
+        <v>7218007</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103743</v>
+        <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>92634</v>
+        <v>91613</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626130</v>
+        <v>626178</v>
       </c>
       <c r="R143" t="n">
-        <v>7218000</v>
+        <v>7217957</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,27 +15781,27 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103843</v>
+        <v>128103863</v>
       </c>
       <c r="B144" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626276</v>
+        <v>626248</v>
       </c>
       <c r="R144" t="n">
-        <v>7217891</v>
+        <v>7218007</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,27 +15878,27 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103863</v>
+        <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626248</v>
+        <v>626276</v>
       </c>
       <c r="R145" t="n">
-        <v>7218007</v>
+        <v>7217891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15975,32 +15975,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103857</v>
+        <v>128103743</v>
       </c>
       <c r="B146" t="n">
-        <v>91613</v>
+        <v>92634</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626178</v>
+        <v>626130</v>
       </c>
       <c r="R146" t="n">
-        <v>7217957</v>
+        <v>7218000</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16072,32 +16072,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103839</v>
+        <v>128103829</v>
       </c>
       <c r="B147" t="n">
-        <v>91370</v>
+        <v>98470</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626215</v>
+        <v>626217</v>
       </c>
       <c r="R147" t="n">
-        <v>7218028</v>
+        <v>7217956</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,32 +16169,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103704</v>
+        <v>128103807</v>
       </c>
       <c r="B148" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626182</v>
+        <v>626532</v>
       </c>
       <c r="R148" t="n">
-        <v>7218029</v>
+        <v>7217568</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103753</v>
+        <v>128103839</v>
       </c>
       <c r="B149" t="n">
-        <v>80132</v>
+        <v>91370</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16277,21 +16277,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626465</v>
+        <v>626215</v>
       </c>
       <c r="R149" t="n">
-        <v>7217693</v>
+        <v>7218028</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103763</v>
+        <v>128103753</v>
       </c>
       <c r="B150" t="n">
         <v>80132</v>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626343</v>
+        <v>626465</v>
       </c>
       <c r="R150" t="n">
-        <v>7217927</v>
+        <v>7217693</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103735</v>
+        <v>128103763</v>
       </c>
       <c r="B151" t="n">
-        <v>57669</v>
+        <v>80132</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,42 +16471,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626159</v>
+        <v>626343</v>
       </c>
       <c r="R151" t="n">
-        <v>7217940</v>
+        <v>7217927</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16539,11 +16531,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16570,32 +16557,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103829</v>
+        <v>128103704</v>
       </c>
       <c r="B152" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16605,10 +16592,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626217</v>
+        <v>626182</v>
       </c>
       <c r="R152" t="n">
-        <v>7217956</v>
+        <v>7218029</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16667,45 +16654,53 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103807</v>
+        <v>128103735</v>
       </c>
       <c r="B153" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626532</v>
+        <v>626159</v>
       </c>
       <c r="R153" t="n">
-        <v>7217568</v>
+        <v>7217940</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16738,6 +16733,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16861,32 +16861,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128103694</v>
+        <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>79647</v>
+        <v>92646</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626150</v>
+        <v>626278</v>
       </c>
       <c r="R155" t="n">
-        <v>7217973</v>
+        <v>7217843</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103737</v>
+        <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>92646</v>
+        <v>79647</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626278</v>
+        <v>626150</v>
       </c>
       <c r="R156" t="n">
-        <v>7217843</v>
+        <v>7217973</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B157" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R157" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R158" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17249,32 +17249,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103770</v>
+        <v>128103808</v>
       </c>
       <c r="B159" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626249</v>
+        <v>626216</v>
       </c>
       <c r="R159" t="n">
-        <v>7218009</v>
+        <v>7217940</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17346,10 +17346,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103774</v>
+        <v>128103851</v>
       </c>
       <c r="B160" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17357,21 +17357,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626377</v>
+        <v>626264</v>
       </c>
       <c r="R160" t="n">
-        <v>7217880</v>
+        <v>7217994</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103768</v>
+        <v>128103770</v>
       </c>
       <c r="B161" t="n">
         <v>80132</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626272</v>
+        <v>626249</v>
       </c>
       <c r="R161" t="n">
-        <v>7217987</v>
+        <v>7218009</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,10 +17540,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103851</v>
+        <v>128103774</v>
       </c>
       <c r="B162" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17551,21 +17551,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626264</v>
+        <v>626377</v>
       </c>
       <c r="R162" t="n">
-        <v>7217994</v>
+        <v>7217880</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17637,32 +17637,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103808</v>
+        <v>128103768</v>
       </c>
       <c r="B163" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626216</v>
+        <v>626272</v>
       </c>
       <c r="R163" t="n">
-        <v>7217940</v>
+        <v>7217987</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103786</v>
+        <v>128103823</v>
       </c>
       <c r="B164" t="n">
-        <v>91825</v>
+        <v>98470</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626319</v>
+        <v>626337</v>
       </c>
       <c r="R164" t="n">
-        <v>7217868</v>
+        <v>7217840</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103783</v>
+        <v>128103813</v>
       </c>
       <c r="B165" t="n">
-        <v>91735</v>
+        <v>98470</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17842,21 +17842,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>298</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626271</v>
+        <v>626370</v>
       </c>
       <c r="R165" t="n">
-        <v>7217852</v>
+        <v>7217900</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,32 +17928,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103766</v>
+        <v>128103783</v>
       </c>
       <c r="B166" t="n">
-        <v>80132</v>
+        <v>91735</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626308</v>
+        <v>626271</v>
       </c>
       <c r="R166" t="n">
-        <v>7217938</v>
+        <v>7217852</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18135,32 +18135,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103823</v>
+        <v>128103786</v>
       </c>
       <c r="B168" t="n">
-        <v>98470</v>
+        <v>91825</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18170,10 +18170,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626337</v>
+        <v>626319</v>
       </c>
       <c r="R168" t="n">
-        <v>7217840</v>
+        <v>7217868</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18232,32 +18232,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103813</v>
+        <v>128103766</v>
       </c>
       <c r="B169" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626370</v>
+        <v>626308</v>
       </c>
       <c r="R169" t="n">
-        <v>7217900</v>
+        <v>7217938</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18329,32 +18329,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128103809</v>
+        <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>98470</v>
+        <v>57776</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>626232</v>
+        <v>626322</v>
       </c>
       <c r="R170" t="n">
-        <v>7217960</v>
+        <v>7217855</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18426,32 +18426,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128103785</v>
+        <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>57776</v>
+        <v>98470</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18461,10 +18461,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>626322</v>
+        <v>626232</v>
       </c>
       <c r="R171" t="n">
-        <v>7217855</v>
+        <v>7217960</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18523,32 +18523,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103825</v>
+        <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>98470</v>
+        <v>78787</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626215</v>
+        <v>626317</v>
       </c>
       <c r="R172" t="n">
-        <v>7218004</v>
+        <v>7217867</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,10 +18620,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103793</v>
+        <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18631,21 +18631,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626317</v>
+        <v>626263</v>
       </c>
       <c r="R173" t="n">
-        <v>7217867</v>
+        <v>7217877</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18911,32 +18911,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103844</v>
+        <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626263</v>
+        <v>626215</v>
       </c>
       <c r="R176" t="n">
-        <v>7217877</v>
+        <v>7218004</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103759</v>
+        <v>128103700</v>
       </c>
       <c r="B183" t="n">
-        <v>80132</v>
+        <v>91637</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>71</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,7 +19638,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626350</v>
+        <v>626271</v>
       </c>
       <c r="R183" t="n">
         <v>7217852</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103695</v>
+        <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>79647</v>
+        <v>80132</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626290</v>
+        <v>626398</v>
       </c>
       <c r="R184" t="n">
-        <v>7217851</v>
+        <v>7217759</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,32 +19797,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103761</v>
+        <v>128103822</v>
       </c>
       <c r="B185" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626398</v>
+        <v>626528</v>
       </c>
       <c r="R185" t="n">
-        <v>7217759</v>
+        <v>7217613</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103791</v>
+        <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>78787</v>
+        <v>80133</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626290</v>
+        <v>626582</v>
       </c>
       <c r="R186" t="n">
-        <v>7217851</v>
+        <v>7217455</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,32 +19991,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103700</v>
+        <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>91637</v>
+        <v>80132</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>71</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,7 +20026,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626271</v>
+        <v>626350</v>
       </c>
       <c r="R187" t="n">
         <v>7217852</v>
@@ -20088,32 +20088,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103859</v>
+        <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626133</v>
+        <v>626290</v>
       </c>
       <c r="R188" t="n">
-        <v>7217998</v>
+        <v>7217851</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20185,10 +20185,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103739</v>
+        <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>80133</v>
+        <v>78787</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20196,21 +20196,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626582</v>
+        <v>626290</v>
       </c>
       <c r="R189" t="n">
-        <v>7217455</v>
+        <v>7217851</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20282,32 +20282,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128103822</v>
+        <v>128103859</v>
       </c>
       <c r="B190" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>626528</v>
+        <v>626133</v>
       </c>
       <c r="R190" t="n">
-        <v>7217613</v>
+        <v>7217998</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -13713,10 +13713,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103740</v>
+        <v>128103746</v>
       </c>
       <c r="B123" t="n">
-        <v>91648</v>
+        <v>78788</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13724,21 +13724,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626128</v>
+        <v>626290</v>
       </c>
       <c r="R123" t="n">
-        <v>7218027</v>
+        <v>7217851</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13792,6 +13792,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13810,45 +13811,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103824</v>
+        <v>128103721</v>
       </c>
       <c r="B124" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626300</v>
+        <v>626306</v>
       </c>
       <c r="R124" t="n">
-        <v>7217895</v>
+        <v>7217910</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,6 +13890,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13907,32 +13921,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103746</v>
+        <v>128103824</v>
       </c>
       <c r="B125" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626290</v>
+        <v>626300</v>
       </c>
       <c r="R125" t="n">
-        <v>7217851</v>
+        <v>7217895</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13986,7 +14000,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14393,10 +14406,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103721</v>
+        <v>128103740</v>
       </c>
       <c r="B130" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14404,42 +14417,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626306</v>
+        <v>626128</v>
       </c>
       <c r="R130" t="n">
-        <v>7217910</v>
+        <v>7218027</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14472,11 +14477,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15199,7 +15199,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B138" t="n">
         <v>80132</v>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R138" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103810</v>
+        <v>128103773</v>
       </c>
       <c r="B139" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626290</v>
+        <v>626370</v>
       </c>
       <c r="R139" t="n">
-        <v>7217851</v>
+        <v>7217900</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103837</v>
+        <v>128103835</v>
       </c>
       <c r="B140" t="n">
-        <v>105508</v>
+        <v>90909</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221144</v>
+        <v>900</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626194</v>
+        <v>626354</v>
       </c>
       <c r="R140" t="n">
-        <v>7218055</v>
+        <v>7217769</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103835</v>
+        <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>90909</v>
+        <v>98470</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>900</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626354</v>
+        <v>626290</v>
       </c>
       <c r="R141" t="n">
-        <v>7217769</v>
+        <v>7217851</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103769</v>
+        <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626248</v>
+        <v>626194</v>
       </c>
       <c r="R142" t="n">
-        <v>7218007</v>
+        <v>7218055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16072,32 +16072,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103829</v>
+        <v>128103704</v>
       </c>
       <c r="B147" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626217</v>
+        <v>626182</v>
       </c>
       <c r="R147" t="n">
-        <v>7217956</v>
+        <v>7218029</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,32 +16169,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103807</v>
+        <v>128103839</v>
       </c>
       <c r="B148" t="n">
-        <v>98470</v>
+        <v>91370</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626532</v>
+        <v>626215</v>
       </c>
       <c r="R148" t="n">
-        <v>7217568</v>
+        <v>7218028</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103839</v>
+        <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>91370</v>
+        <v>80132</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16277,21 +16277,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626215</v>
+        <v>626465</v>
       </c>
       <c r="R149" t="n">
-        <v>7218028</v>
+        <v>7217693</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103753</v>
+        <v>128103763</v>
       </c>
       <c r="B150" t="n">
         <v>80132</v>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626465</v>
+        <v>626343</v>
       </c>
       <c r="R150" t="n">
-        <v>7217693</v>
+        <v>7217927</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103763</v>
+        <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>80132</v>
+        <v>57669</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,34 +16471,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626343</v>
+        <v>626159</v>
       </c>
       <c r="R151" t="n">
-        <v>7217927</v>
+        <v>7217940</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16531,6 +16539,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16557,32 +16570,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103704</v>
+        <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16592,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626182</v>
+        <v>626217</v>
       </c>
       <c r="R152" t="n">
-        <v>7218029</v>
+        <v>7217956</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16654,53 +16667,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103735</v>
+        <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626159</v>
+        <v>626532</v>
       </c>
       <c r="R153" t="n">
-        <v>7217940</v>
+        <v>7217568</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16733,11 +16738,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103757</v>
+        <v>128103701</v>
       </c>
       <c r="B100" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626239</v>
+        <v>626222</v>
       </c>
       <c r="R100" t="n">
-        <v>7218007</v>
+        <v>7218014</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103728</v>
+        <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626453</v>
+        <v>626239</v>
       </c>
       <c r="R101" t="n">
-        <v>7217719</v>
+        <v>7218007</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11631,32 +11631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103850</v>
+        <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626593</v>
+        <v>626453</v>
       </c>
       <c r="R102" t="n">
-        <v>7217442</v>
+        <v>7217719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,11 +11702,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11733,10 +11728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103701</v>
+        <v>128103850</v>
       </c>
       <c r="B103" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11744,21 +11739,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11768,10 +11763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626222</v>
+        <v>626593</v>
       </c>
       <c r="R103" t="n">
-        <v>7218014</v>
+        <v>7217442</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,6 +11799,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14503,45 +14503,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103696</v>
+        <v>128103856</v>
       </c>
       <c r="B131" t="n">
-        <v>91637</v>
+        <v>57672</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>71</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626167</v>
+        <v>626323</v>
       </c>
       <c r="R131" t="n">
-        <v>7217957</v>
+        <v>7217908</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14574,6 +14582,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14600,53 +14613,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103856</v>
+        <v>128103696</v>
       </c>
       <c r="B132" t="n">
-        <v>57672</v>
+        <v>91637</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>71</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626323</v>
+        <v>626167</v>
       </c>
       <c r="R132" t="n">
-        <v>7217908</v>
+        <v>7217957</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14679,11 +14684,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14710,10 +14710,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103811</v>
+        <v>128103787</v>
       </c>
       <c r="B133" t="n">
-        <v>98470</v>
+        <v>91724</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14721,34 +14721,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626311</v>
+        <v>626280</v>
       </c>
       <c r="R133" t="n">
-        <v>7217865</v>
+        <v>7217822</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14789,6 +14792,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14807,32 +14811,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103827</v>
+        <v>128103781</v>
       </c>
       <c r="B134" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14842,10 +14846,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626128</v>
+        <v>626239</v>
       </c>
       <c r="R134" t="n">
-        <v>7218027</v>
+        <v>7218007</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14904,48 +14908,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103787</v>
+        <v>128103867</v>
       </c>
       <c r="B135" t="n">
-        <v>91724</v>
+        <v>80167</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1505</v>
+        <v>6463</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626280</v>
+        <v>626346</v>
       </c>
       <c r="R135" t="n">
-        <v>7217822</v>
+        <v>7217883</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14986,7 +14987,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15005,32 +15005,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103781</v>
+        <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15040,10 +15040,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626239</v>
+        <v>626311</v>
       </c>
       <c r="R136" t="n">
-        <v>7218007</v>
+        <v>7217865</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15102,32 +15102,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103867</v>
+        <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626346</v>
+        <v>626128</v>
       </c>
       <c r="R137" t="n">
-        <v>7217883</v>
+        <v>7218027</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15199,7 +15199,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103769</v>
+        <v>128103773</v>
       </c>
       <c r="B138" t="n">
         <v>80132</v>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626248</v>
+        <v>626370</v>
       </c>
       <c r="R138" t="n">
-        <v>7218007</v>
+        <v>7217900</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103773</v>
+        <v>128103810</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626370</v>
+        <v>626290</v>
       </c>
       <c r="R139" t="n">
-        <v>7217900</v>
+        <v>7217851</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103835</v>
+        <v>128103837</v>
       </c>
       <c r="B140" t="n">
-        <v>90909</v>
+        <v>105508</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>900</v>
+        <v>221144</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626354</v>
+        <v>626194</v>
       </c>
       <c r="R140" t="n">
-        <v>7217769</v>
+        <v>7218055</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103810</v>
+        <v>128103835</v>
       </c>
       <c r="B141" t="n">
-        <v>98470</v>
+        <v>90909</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>900</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626290</v>
+        <v>626354</v>
       </c>
       <c r="R141" t="n">
-        <v>7217851</v>
+        <v>7217769</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103837</v>
+        <v>128103769</v>
       </c>
       <c r="B142" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626194</v>
+        <v>626248</v>
       </c>
       <c r="R142" t="n">
-        <v>7218055</v>
+        <v>7218007</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B157" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R157" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R158" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103823</v>
+        <v>128103766</v>
       </c>
       <c r="B164" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626337</v>
+        <v>626308</v>
       </c>
       <c r="R164" t="n">
-        <v>7217840</v>
+        <v>7217938</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103813</v>
+        <v>128103783</v>
       </c>
       <c r="B165" t="n">
-        <v>98470</v>
+        <v>91735</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17842,21 +17842,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626370</v>
+        <v>626271</v>
       </c>
       <c r="R165" t="n">
-        <v>7217900</v>
+        <v>7217852</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,45 +17928,53 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103783</v>
+        <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>91735</v>
+        <v>57669</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>298</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626271</v>
+        <v>626194</v>
       </c>
       <c r="R166" t="n">
-        <v>7217852</v>
+        <v>7217951</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17999,6 +18007,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18025,10 +18038,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103736</v>
+        <v>128103786</v>
       </c>
       <c r="B167" t="n">
-        <v>57669</v>
+        <v>91825</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18036,42 +18049,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>5467</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626194</v>
+        <v>626319</v>
       </c>
       <c r="R167" t="n">
-        <v>7217951</v>
+        <v>7217868</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18104,11 +18109,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18135,32 +18135,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103786</v>
+        <v>128103823</v>
       </c>
       <c r="B168" t="n">
-        <v>91825</v>
+        <v>98470</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18170,10 +18170,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626319</v>
+        <v>626337</v>
       </c>
       <c r="R168" t="n">
-        <v>7217868</v>
+        <v>7217840</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18232,32 +18232,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103766</v>
+        <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626308</v>
+        <v>626370</v>
       </c>
       <c r="R169" t="n">
-        <v>7217938</v>
+        <v>7217900</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11830,32 +11830,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103703</v>
+        <v>128103806</v>
       </c>
       <c r="B104" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626128</v>
+        <v>626574</v>
       </c>
       <c r="R104" t="n">
-        <v>7218027</v>
+        <v>7217449</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11927,10 +11927,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103719</v>
+        <v>128103703</v>
       </c>
       <c r="B105" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11938,42 +11938,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626269</v>
+        <v>626128</v>
       </c>
       <c r="R105" t="n">
-        <v>7217921</v>
+        <v>7218027</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12006,11 +11998,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12037,45 +12024,53 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103812</v>
+        <v>128103719</v>
       </c>
       <c r="B106" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626319</v>
+        <v>626269</v>
       </c>
       <c r="R106" t="n">
-        <v>7217868</v>
+        <v>7217921</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12108,6 +12103,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12134,7 +12134,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128103806</v>
+        <v>128103812</v>
       </c>
       <c r="B107" t="n">
         <v>98470</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>626574</v>
+        <v>626319</v>
       </c>
       <c r="R107" t="n">
-        <v>7217449</v>
+        <v>7217868</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103831</v>
+        <v>128103866</v>
       </c>
       <c r="B116" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626373</v>
+        <v>626282</v>
       </c>
       <c r="R116" t="n">
-        <v>7217883</v>
+        <v>7217980</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,32 +13118,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103828</v>
+        <v>128103853</v>
       </c>
       <c r="B117" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626202</v>
+        <v>626328</v>
       </c>
       <c r="R117" t="n">
-        <v>7217956</v>
+        <v>7217861</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13215,45 +13215,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103733</v>
+        <v>128103717</v>
       </c>
       <c r="B118" t="n">
-        <v>98491</v>
+        <v>57672</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626571</v>
+        <v>626217</v>
       </c>
       <c r="R118" t="n">
-        <v>7217492</v>
+        <v>7217965</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13286,6 +13294,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13312,32 +13325,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103866</v>
+        <v>128103871</v>
       </c>
       <c r="B119" t="n">
-        <v>80167</v>
+        <v>92636</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6463</v>
+        <v>4362</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13347,10 +13360,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626282</v>
+        <v>626144</v>
       </c>
       <c r="R119" t="n">
-        <v>7217980</v>
+        <v>7217996</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13409,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103853</v>
+        <v>128103831</v>
       </c>
       <c r="B120" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13444,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626328</v>
+        <v>626373</v>
       </c>
       <c r="R120" t="n">
-        <v>7217861</v>
+        <v>7217883</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13506,32 +13519,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103871</v>
+        <v>128103828</v>
       </c>
       <c r="B121" t="n">
-        <v>92636</v>
+        <v>98470</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13541,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626144</v>
+        <v>626202</v>
       </c>
       <c r="R121" t="n">
-        <v>7217996</v>
+        <v>7217956</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13603,53 +13616,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103717</v>
+        <v>128103733</v>
       </c>
       <c r="B122" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626217</v>
+        <v>626571</v>
       </c>
       <c r="R122" t="n">
-        <v>7217965</v>
+        <v>7217492</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13682,11 +13687,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13713,10 +13713,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103746</v>
+        <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>78788</v>
+        <v>91648</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13724,21 +13724,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626290</v>
+        <v>626128</v>
       </c>
       <c r="R123" t="n">
-        <v>7217851</v>
+        <v>7218027</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13792,7 +13792,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13811,53 +13810,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103721</v>
+        <v>128103824</v>
       </c>
       <c r="B124" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626306</v>
+        <v>626300</v>
       </c>
       <c r="R124" t="n">
-        <v>7217910</v>
+        <v>7217895</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13890,11 +13881,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13921,32 +13907,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103824</v>
+        <v>128103746</v>
       </c>
       <c r="B125" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13956,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626300</v>
+        <v>626290</v>
       </c>
       <c r="R125" t="n">
-        <v>7217895</v>
+        <v>7217851</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14000,6 +13986,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14406,10 +14393,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103740</v>
+        <v>128103721</v>
       </c>
       <c r="B130" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14417,34 +14404,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626128</v>
+        <v>626306</v>
       </c>
       <c r="R130" t="n">
-        <v>7218027</v>
+        <v>7217910</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14477,6 +14472,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15199,7 +15199,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B138" t="n">
         <v>80132</v>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R138" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103810</v>
+        <v>128103773</v>
       </c>
       <c r="B139" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626290</v>
+        <v>626370</v>
       </c>
       <c r="R139" t="n">
-        <v>7217851</v>
+        <v>7217900</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103837</v>
+        <v>128103835</v>
       </c>
       <c r="B140" t="n">
-        <v>105508</v>
+        <v>90909</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221144</v>
+        <v>900</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626194</v>
+        <v>626354</v>
       </c>
       <c r="R140" t="n">
-        <v>7218055</v>
+        <v>7217769</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103835</v>
+        <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>90909</v>
+        <v>98470</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>900</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626354</v>
+        <v>626290</v>
       </c>
       <c r="R141" t="n">
-        <v>7217769</v>
+        <v>7217851</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103769</v>
+        <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626248</v>
+        <v>626194</v>
       </c>
       <c r="R142" t="n">
-        <v>7218007</v>
+        <v>7218055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103766</v>
+        <v>128103823</v>
       </c>
       <c r="B164" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626308</v>
+        <v>626337</v>
       </c>
       <c r="R164" t="n">
-        <v>7217938</v>
+        <v>7217840</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103783</v>
+        <v>128103813</v>
       </c>
       <c r="B165" t="n">
-        <v>91735</v>
+        <v>98470</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17842,21 +17842,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>298</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626271</v>
+        <v>626370</v>
       </c>
       <c r="R165" t="n">
-        <v>7217852</v>
+        <v>7217900</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,53 +17928,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103736</v>
+        <v>128103783</v>
       </c>
       <c r="B166" t="n">
-        <v>57669</v>
+        <v>91735</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626194</v>
+        <v>626271</v>
       </c>
       <c r="R166" t="n">
-        <v>7217951</v>
+        <v>7217852</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18007,11 +17999,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18038,10 +18025,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103786</v>
+        <v>128103736</v>
       </c>
       <c r="B167" t="n">
-        <v>91825</v>
+        <v>57669</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18049,34 +18036,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626319</v>
+        <v>626194</v>
       </c>
       <c r="R167" t="n">
-        <v>7217868</v>
+        <v>7217951</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18109,6 +18104,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18135,32 +18135,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103823</v>
+        <v>128103786</v>
       </c>
       <c r="B168" t="n">
-        <v>98470</v>
+        <v>91825</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18170,10 +18170,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626337</v>
+        <v>626319</v>
       </c>
       <c r="R168" t="n">
-        <v>7217840</v>
+        <v>7217868</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18232,32 +18232,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103813</v>
+        <v>128103766</v>
       </c>
       <c r="B169" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626370</v>
+        <v>626308</v>
       </c>
       <c r="R169" t="n">
-        <v>7217900</v>
+        <v>7217938</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103700</v>
+        <v>128103822</v>
       </c>
       <c r="B183" t="n">
-        <v>91637</v>
+        <v>98470</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>71</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626271</v>
+        <v>626528</v>
       </c>
       <c r="R183" t="n">
-        <v>7217852</v>
+        <v>7217613</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103761</v>
+        <v>128103739</v>
       </c>
       <c r="B184" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626398</v>
+        <v>626582</v>
       </c>
       <c r="R184" t="n">
-        <v>7217759</v>
+        <v>7217455</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,32 +19797,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103822</v>
+        <v>128103759</v>
       </c>
       <c r="B185" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626528</v>
+        <v>626350</v>
       </c>
       <c r="R185" t="n">
-        <v>7217613</v>
+        <v>7217852</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103739</v>
+        <v>128103695</v>
       </c>
       <c r="B186" t="n">
-        <v>80133</v>
+        <v>79647</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626582</v>
+        <v>626290</v>
       </c>
       <c r="R186" t="n">
-        <v>7217455</v>
+        <v>7217851</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,7 +19991,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103759</v>
+        <v>128103761</v>
       </c>
       <c r="B187" t="n">
         <v>80132</v>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626350</v>
+        <v>626398</v>
       </c>
       <c r="R187" t="n">
-        <v>7217852</v>
+        <v>7217759</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,32 +20088,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103695</v>
+        <v>128103700</v>
       </c>
       <c r="B188" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626290</v>
+        <v>626271</v>
       </c>
       <c r="R188" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103701</v>
+        <v>128103757</v>
       </c>
       <c r="B100" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626222</v>
+        <v>626239</v>
       </c>
       <c r="R100" t="n">
-        <v>7218014</v>
+        <v>7218007</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103757</v>
+        <v>128103728</v>
       </c>
       <c r="B101" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626239</v>
+        <v>626453</v>
       </c>
       <c r="R101" t="n">
-        <v>7218007</v>
+        <v>7217719</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11631,32 +11631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103728</v>
+        <v>128103850</v>
       </c>
       <c r="B102" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626453</v>
+        <v>626593</v>
       </c>
       <c r="R102" t="n">
-        <v>7217719</v>
+        <v>7217442</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,6 +11702,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11728,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103850</v>
+        <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11739,21 +11744,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11763,10 +11768,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626593</v>
+        <v>626222</v>
       </c>
       <c r="R103" t="n">
-        <v>7217442</v>
+        <v>7218014</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,11 +11804,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12619,10 +12619,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103754</v>
+        <v>128103716</v>
       </c>
       <c r="B112" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12630,34 +12630,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626325</v>
+        <v>626454</v>
       </c>
       <c r="R112" t="n">
-        <v>7217934</v>
+        <v>7217736</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12690,6 +12698,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12716,10 +12729,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103765</v>
+        <v>128103744</v>
       </c>
       <c r="B113" t="n">
-        <v>80132</v>
+        <v>78788</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12727,21 +12740,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12751,10 +12764,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R113" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12795,6 +12808,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12813,10 +12827,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103716</v>
+        <v>128103754</v>
       </c>
       <c r="B114" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12824,42 +12838,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626454</v>
+        <v>626325</v>
       </c>
       <c r="R114" t="n">
-        <v>7217736</v>
+        <v>7217934</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12892,11 +12898,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12923,10 +12924,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103744</v>
+        <v>128103765</v>
       </c>
       <c r="B115" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12934,21 +12935,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12958,10 +12959,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626454</v>
+        <v>626320</v>
       </c>
       <c r="R115" t="n">
-        <v>7217736</v>
+        <v>7217923</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13002,7 +13003,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103866</v>
+        <v>128103831</v>
       </c>
       <c r="B116" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626282</v>
+        <v>626373</v>
       </c>
       <c r="R116" t="n">
-        <v>7217980</v>
+        <v>7217883</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,32 +13118,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103853</v>
+        <v>128103828</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626328</v>
+        <v>626202</v>
       </c>
       <c r="R117" t="n">
-        <v>7217861</v>
+        <v>7217956</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13215,53 +13215,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103717</v>
+        <v>128103733</v>
       </c>
       <c r="B118" t="n">
-        <v>57672</v>
+        <v>98491</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626217</v>
+        <v>626571</v>
       </c>
       <c r="R118" t="n">
-        <v>7217965</v>
+        <v>7217492</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13294,11 +13286,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13325,32 +13312,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103871</v>
+        <v>128103866</v>
       </c>
       <c r="B119" t="n">
-        <v>92636</v>
+        <v>80167</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13360,10 +13347,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626144</v>
+        <v>626282</v>
       </c>
       <c r="R119" t="n">
-        <v>7217996</v>
+        <v>7217980</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13422,32 +13409,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103831</v>
+        <v>128103853</v>
       </c>
       <c r="B120" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13444,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626373</v>
+        <v>626328</v>
       </c>
       <c r="R120" t="n">
-        <v>7217883</v>
+        <v>7217861</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,32 +13506,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103828</v>
+        <v>128103871</v>
       </c>
       <c r="B121" t="n">
-        <v>98470</v>
+        <v>92636</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13554,10 +13541,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626202</v>
+        <v>626144</v>
       </c>
       <c r="R121" t="n">
-        <v>7217956</v>
+        <v>7217996</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13616,45 +13603,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103733</v>
+        <v>128103717</v>
       </c>
       <c r="B122" t="n">
-        <v>98491</v>
+        <v>57672</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626571</v>
+        <v>626217</v>
       </c>
       <c r="R122" t="n">
-        <v>7217492</v>
+        <v>7217965</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13687,6 +13682,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13713,10 +13713,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103740</v>
+        <v>128103746</v>
       </c>
       <c r="B123" t="n">
-        <v>91648</v>
+        <v>78788</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13724,21 +13724,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626128</v>
+        <v>626290</v>
       </c>
       <c r="R123" t="n">
-        <v>7218027</v>
+        <v>7217851</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13792,6 +13792,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13810,45 +13811,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103824</v>
+        <v>128103721</v>
       </c>
       <c r="B124" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626300</v>
+        <v>626306</v>
       </c>
       <c r="R124" t="n">
-        <v>7217895</v>
+        <v>7217910</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,6 +13890,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13907,32 +13921,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103746</v>
+        <v>128103824</v>
       </c>
       <c r="B125" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13956,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626290</v>
+        <v>626300</v>
       </c>
       <c r="R125" t="n">
-        <v>7217851</v>
+        <v>7217895</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13986,7 +14000,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14393,10 +14406,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103721</v>
+        <v>128103740</v>
       </c>
       <c r="B130" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14404,42 +14417,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626306</v>
+        <v>626128</v>
       </c>
       <c r="R130" t="n">
-        <v>7217910</v>
+        <v>7218027</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14472,11 +14477,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14503,53 +14503,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103856</v>
+        <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>57672</v>
+        <v>91637</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>71</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626323</v>
+        <v>626167</v>
       </c>
       <c r="R131" t="n">
-        <v>7217908</v>
+        <v>7217957</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14582,11 +14574,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14613,45 +14600,53 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103696</v>
+        <v>128103856</v>
       </c>
       <c r="B132" t="n">
-        <v>91637</v>
+        <v>57672</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>71</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626167</v>
+        <v>626323</v>
       </c>
       <c r="R132" t="n">
-        <v>7217957</v>
+        <v>7217908</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14684,6 +14679,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14710,10 +14710,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103787</v>
+        <v>128103811</v>
       </c>
       <c r="B133" t="n">
-        <v>91724</v>
+        <v>98470</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14721,37 +14721,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626280</v>
+        <v>626311</v>
       </c>
       <c r="R133" t="n">
-        <v>7217822</v>
+        <v>7217865</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14792,7 +14789,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14811,32 +14807,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103781</v>
+        <v>128103827</v>
       </c>
       <c r="B134" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14846,10 +14842,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626239</v>
+        <v>626128</v>
       </c>
       <c r="R134" t="n">
-        <v>7218007</v>
+        <v>7218027</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14908,45 +14904,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103867</v>
+        <v>128103787</v>
       </c>
       <c r="B135" t="n">
-        <v>80167</v>
+        <v>91724</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6463</v>
+        <v>1505</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626346</v>
+        <v>626280</v>
       </c>
       <c r="R135" t="n">
-        <v>7217883</v>
+        <v>7217822</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14987,6 +14986,7 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15005,32 +15005,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103811</v>
+        <v>128103781</v>
       </c>
       <c r="B136" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15040,10 +15040,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626311</v>
+        <v>626239</v>
       </c>
       <c r="R136" t="n">
-        <v>7217865</v>
+        <v>7218007</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15102,32 +15102,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103827</v>
+        <v>128103867</v>
       </c>
       <c r="B137" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626128</v>
+        <v>626346</v>
       </c>
       <c r="R137" t="n">
-        <v>7218027</v>
+        <v>7217883</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15199,7 +15199,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103769</v>
+        <v>128103773</v>
       </c>
       <c r="B138" t="n">
         <v>80132</v>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626248</v>
+        <v>626370</v>
       </c>
       <c r="R138" t="n">
-        <v>7218007</v>
+        <v>7217900</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103773</v>
+        <v>128103810</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626370</v>
+        <v>626290</v>
       </c>
       <c r="R139" t="n">
-        <v>7217900</v>
+        <v>7217851</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103835</v>
+        <v>128103837</v>
       </c>
       <c r="B140" t="n">
-        <v>90909</v>
+        <v>105508</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>900</v>
+        <v>221144</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626354</v>
+        <v>626194</v>
       </c>
       <c r="R140" t="n">
-        <v>7217769</v>
+        <v>7218055</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103810</v>
+        <v>128103835</v>
       </c>
       <c r="B141" t="n">
-        <v>98470</v>
+        <v>90909</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>900</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626290</v>
+        <v>626354</v>
       </c>
       <c r="R141" t="n">
-        <v>7217851</v>
+        <v>7217769</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103837</v>
+        <v>128103769</v>
       </c>
       <c r="B142" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626194</v>
+        <v>626248</v>
       </c>
       <c r="R142" t="n">
-        <v>7218055</v>
+        <v>7218007</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16072,32 +16072,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103704</v>
+        <v>128103829</v>
       </c>
       <c r="B147" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626182</v>
+        <v>626217</v>
       </c>
       <c r="R147" t="n">
-        <v>7218029</v>
+        <v>7217956</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,32 +16169,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103839</v>
+        <v>128103807</v>
       </c>
       <c r="B148" t="n">
-        <v>91370</v>
+        <v>98470</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626215</v>
+        <v>626532</v>
       </c>
       <c r="R148" t="n">
-        <v>7218028</v>
+        <v>7217568</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103753</v>
+        <v>128103839</v>
       </c>
       <c r="B149" t="n">
-        <v>80132</v>
+        <v>91370</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16277,21 +16277,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626465</v>
+        <v>626215</v>
       </c>
       <c r="R149" t="n">
-        <v>7217693</v>
+        <v>7218028</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103763</v>
+        <v>128103753</v>
       </c>
       <c r="B150" t="n">
         <v>80132</v>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626343</v>
+        <v>626465</v>
       </c>
       <c r="R150" t="n">
-        <v>7217927</v>
+        <v>7217693</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103735</v>
+        <v>128103763</v>
       </c>
       <c r="B151" t="n">
-        <v>57669</v>
+        <v>80132</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,42 +16471,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626159</v>
+        <v>626343</v>
       </c>
       <c r="R151" t="n">
-        <v>7217940</v>
+        <v>7217927</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16539,11 +16531,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16570,32 +16557,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103829</v>
+        <v>128103704</v>
       </c>
       <c r="B152" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16605,10 +16592,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626217</v>
+        <v>626182</v>
       </c>
       <c r="R152" t="n">
-        <v>7217956</v>
+        <v>7218029</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16667,45 +16654,53 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103807</v>
+        <v>128103735</v>
       </c>
       <c r="B153" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626532</v>
+        <v>626159</v>
       </c>
       <c r="R153" t="n">
-        <v>7217568</v>
+        <v>7217940</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16738,6 +16733,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B157" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R157" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R158" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17346,10 +17346,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103851</v>
+        <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17357,21 +17357,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626264</v>
+        <v>626249</v>
       </c>
       <c r="R160" t="n">
-        <v>7217994</v>
+        <v>7218009</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103770</v>
+        <v>128103774</v>
       </c>
       <c r="B161" t="n">
         <v>80132</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626249</v>
+        <v>626377</v>
       </c>
       <c r="R161" t="n">
-        <v>7218009</v>
+        <v>7217880</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,7 +17540,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103774</v>
+        <v>128103768</v>
       </c>
       <c r="B162" t="n">
         <v>80132</v>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626377</v>
+        <v>626272</v>
       </c>
       <c r="R162" t="n">
-        <v>7217880</v>
+        <v>7217987</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17637,10 +17637,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103768</v>
+        <v>128103851</v>
       </c>
       <c r="B163" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17648,21 +17648,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626272</v>
+        <v>626264</v>
       </c>
       <c r="R163" t="n">
-        <v>7217987</v>
+        <v>7217994</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103822</v>
+        <v>128103700</v>
       </c>
       <c r="B183" t="n">
-        <v>98470</v>
+        <v>91637</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>71</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626528</v>
+        <v>626271</v>
       </c>
       <c r="R183" t="n">
-        <v>7217613</v>
+        <v>7217852</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103739</v>
+        <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80133</v>
+        <v>80132</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626582</v>
+        <v>626398</v>
       </c>
       <c r="R184" t="n">
-        <v>7217455</v>
+        <v>7217759</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,32 +19797,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103759</v>
+        <v>128103822</v>
       </c>
       <c r="B185" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626350</v>
+        <v>626528</v>
       </c>
       <c r="R185" t="n">
-        <v>7217852</v>
+        <v>7217613</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103695</v>
+        <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>79647</v>
+        <v>80133</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626290</v>
+        <v>626582</v>
       </c>
       <c r="R186" t="n">
-        <v>7217851</v>
+        <v>7217455</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,7 +19991,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103761</v>
+        <v>128103759</v>
       </c>
       <c r="B187" t="n">
         <v>80132</v>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626398</v>
+        <v>626350</v>
       </c>
       <c r="R187" t="n">
-        <v>7217759</v>
+        <v>7217852</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,32 +20088,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103700</v>
+        <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>91637</v>
+        <v>79647</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626271</v>
+        <v>626290</v>
       </c>
       <c r="R188" t="n">
-        <v>7217852</v>
+        <v>7217851</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103757</v>
+        <v>128103701</v>
       </c>
       <c r="B100" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626239</v>
+        <v>626222</v>
       </c>
       <c r="R100" t="n">
-        <v>7218007</v>
+        <v>7218014</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103728</v>
+        <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626453</v>
+        <v>626239</v>
       </c>
       <c r="R101" t="n">
-        <v>7217719</v>
+        <v>7218007</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11631,32 +11631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103850</v>
+        <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626593</v>
+        <v>626453</v>
       </c>
       <c r="R102" t="n">
-        <v>7217442</v>
+        <v>7217719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,11 +11702,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11733,10 +11728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103701</v>
+        <v>128103850</v>
       </c>
       <c r="B103" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11744,21 +11739,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11768,10 +11763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626222</v>
+        <v>626593</v>
       </c>
       <c r="R103" t="n">
-        <v>7218014</v>
+        <v>7217442</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,6 +11799,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11830,32 +11830,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103806</v>
+        <v>128103703</v>
       </c>
       <c r="B104" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626574</v>
+        <v>626128</v>
       </c>
       <c r="R104" t="n">
-        <v>7217449</v>
+        <v>7218027</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11927,10 +11927,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103703</v>
+        <v>128103719</v>
       </c>
       <c r="B105" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11938,34 +11938,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626128</v>
+        <v>626269</v>
       </c>
       <c r="R105" t="n">
-        <v>7218027</v>
+        <v>7217921</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11998,6 +12006,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12024,53 +12037,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103719</v>
+        <v>128103812</v>
       </c>
       <c r="B106" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626269</v>
+        <v>626319</v>
       </c>
       <c r="R106" t="n">
-        <v>7217921</v>
+        <v>7217868</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12103,11 +12108,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12134,7 +12134,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128103812</v>
+        <v>128103806</v>
       </c>
       <c r="B107" t="n">
         <v>98470</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>626319</v>
+        <v>626574</v>
       </c>
       <c r="R107" t="n">
-        <v>7217868</v>
+        <v>7217449</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -15199,7 +15199,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B138" t="n">
         <v>80132</v>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R138" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103810</v>
+        <v>128103773</v>
       </c>
       <c r="B139" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626290</v>
+        <v>626370</v>
       </c>
       <c r="R139" t="n">
-        <v>7217851</v>
+        <v>7217900</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103837</v>
+        <v>128103835</v>
       </c>
       <c r="B140" t="n">
-        <v>105508</v>
+        <v>90909</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221144</v>
+        <v>900</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626194</v>
+        <v>626354</v>
       </c>
       <c r="R140" t="n">
-        <v>7218055</v>
+        <v>7217769</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103835</v>
+        <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>90909</v>
+        <v>98470</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>900</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626354</v>
+        <v>626290</v>
       </c>
       <c r="R141" t="n">
-        <v>7217769</v>
+        <v>7217851</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103769</v>
+        <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626248</v>
+        <v>626194</v>
       </c>
       <c r="R142" t="n">
-        <v>7218007</v>
+        <v>7218055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103701</v>
+        <v>128103757</v>
       </c>
       <c r="B100" t="n">
-        <v>91352</v>
+        <v>80132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626222</v>
+        <v>626239</v>
       </c>
       <c r="R100" t="n">
-        <v>7218014</v>
+        <v>7218007</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103757</v>
+        <v>128103728</v>
       </c>
       <c r="B101" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626239</v>
+        <v>626453</v>
       </c>
       <c r="R101" t="n">
-        <v>7218007</v>
+        <v>7217719</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11631,32 +11631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103728</v>
+        <v>128103850</v>
       </c>
       <c r="B102" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626453</v>
+        <v>626593</v>
       </c>
       <c r="R102" t="n">
-        <v>7217719</v>
+        <v>7217442</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,6 +11702,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11728,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103850</v>
+        <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11739,21 +11744,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11763,10 +11768,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626593</v>
+        <v>626222</v>
       </c>
       <c r="R103" t="n">
-        <v>7217442</v>
+        <v>7218014</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,11 +11804,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13713,10 +13713,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103746</v>
+        <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>78788</v>
+        <v>91648</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13724,21 +13724,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626290</v>
+        <v>626128</v>
       </c>
       <c r="R123" t="n">
-        <v>7217851</v>
+        <v>7218027</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13792,7 +13792,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13811,53 +13810,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103721</v>
+        <v>128103824</v>
       </c>
       <c r="B124" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626306</v>
+        <v>626300</v>
       </c>
       <c r="R124" t="n">
-        <v>7217910</v>
+        <v>7217895</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13890,11 +13881,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13921,32 +13907,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103824</v>
+        <v>128103746</v>
       </c>
       <c r="B125" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13956,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626300</v>
+        <v>626290</v>
       </c>
       <c r="R125" t="n">
-        <v>7217895</v>
+        <v>7217851</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14000,6 +13986,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14406,10 +14393,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103740</v>
+        <v>128103721</v>
       </c>
       <c r="B130" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14417,34 +14404,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626128</v>
+        <v>626306</v>
       </c>
       <c r="R130" t="n">
-        <v>7218027</v>
+        <v>7217910</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14477,6 +14472,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14503,45 +14503,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103696</v>
+        <v>128103856</v>
       </c>
       <c r="B131" t="n">
-        <v>91637</v>
+        <v>57672</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>71</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626167</v>
+        <v>626323</v>
       </c>
       <c r="R131" t="n">
-        <v>7217957</v>
+        <v>7217908</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14574,6 +14582,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14600,53 +14613,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103856</v>
+        <v>128103696</v>
       </c>
       <c r="B132" t="n">
-        <v>57672</v>
+        <v>91637</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>71</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626323</v>
+        <v>626167</v>
       </c>
       <c r="R132" t="n">
-        <v>7217908</v>
+        <v>7217957</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14679,11 +14684,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14710,10 +14710,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103811</v>
+        <v>128103787</v>
       </c>
       <c r="B133" t="n">
-        <v>98470</v>
+        <v>91724</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14721,34 +14721,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626311</v>
+        <v>626280</v>
       </c>
       <c r="R133" t="n">
-        <v>7217865</v>
+        <v>7217822</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14789,6 +14792,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14807,32 +14811,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103827</v>
+        <v>128103781</v>
       </c>
       <c r="B134" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14842,10 +14846,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626128</v>
+        <v>626239</v>
       </c>
       <c r="R134" t="n">
-        <v>7218027</v>
+        <v>7218007</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14904,48 +14908,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103787</v>
+        <v>128103867</v>
       </c>
       <c r="B135" t="n">
-        <v>91724</v>
+        <v>80167</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1505</v>
+        <v>6463</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626280</v>
+        <v>626346</v>
       </c>
       <c r="R135" t="n">
-        <v>7217822</v>
+        <v>7217883</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14986,7 +14987,6 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -15005,32 +15005,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103781</v>
+        <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15040,10 +15040,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626239</v>
+        <v>626311</v>
       </c>
       <c r="R136" t="n">
-        <v>7218007</v>
+        <v>7217865</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15102,32 +15102,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103867</v>
+        <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626346</v>
+        <v>626128</v>
       </c>
       <c r="R137" t="n">
-        <v>7217883</v>
+        <v>7218027</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16072,32 +16072,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103829</v>
+        <v>128103704</v>
       </c>
       <c r="B147" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626217</v>
+        <v>626182</v>
       </c>
       <c r="R147" t="n">
-        <v>7217956</v>
+        <v>7218029</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,32 +16169,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103807</v>
+        <v>128103839</v>
       </c>
       <c r="B148" t="n">
-        <v>98470</v>
+        <v>91370</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626532</v>
+        <v>626215</v>
       </c>
       <c r="R148" t="n">
-        <v>7217568</v>
+        <v>7218028</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103839</v>
+        <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>91370</v>
+        <v>80132</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16277,21 +16277,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626215</v>
+        <v>626465</v>
       </c>
       <c r="R149" t="n">
-        <v>7218028</v>
+        <v>7217693</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103753</v>
+        <v>128103763</v>
       </c>
       <c r="B150" t="n">
         <v>80132</v>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626465</v>
+        <v>626343</v>
       </c>
       <c r="R150" t="n">
-        <v>7217693</v>
+        <v>7217927</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103763</v>
+        <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>80132</v>
+        <v>57669</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,34 +16471,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626343</v>
+        <v>626159</v>
       </c>
       <c r="R151" t="n">
-        <v>7217927</v>
+        <v>7217940</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16531,6 +16539,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16557,32 +16570,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103704</v>
+        <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16592,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626182</v>
+        <v>626217</v>
       </c>
       <c r="R152" t="n">
-        <v>7218029</v>
+        <v>7217956</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16654,53 +16667,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103735</v>
+        <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626159</v>
+        <v>626532</v>
       </c>
       <c r="R153" t="n">
-        <v>7217940</v>
+        <v>7217568</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16733,11 +16738,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B157" t="n">
-        <v>92642</v>
+        <v>80132</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R157" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>80132</v>
+        <v>92642</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R158" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103823</v>
+        <v>128103766</v>
       </c>
       <c r="B164" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626337</v>
+        <v>626308</v>
       </c>
       <c r="R164" t="n">
-        <v>7217840</v>
+        <v>7217938</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103813</v>
+        <v>128103783</v>
       </c>
       <c r="B165" t="n">
-        <v>98470</v>
+        <v>91735</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17842,21 +17842,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626370</v>
+        <v>626271</v>
       </c>
       <c r="R165" t="n">
-        <v>7217900</v>
+        <v>7217852</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,45 +17928,53 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103783</v>
+        <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>91735</v>
+        <v>57669</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>298</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626271</v>
+        <v>626194</v>
       </c>
       <c r="R166" t="n">
-        <v>7217852</v>
+        <v>7217951</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17999,6 +18007,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18025,10 +18038,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103736</v>
+        <v>128103786</v>
       </c>
       <c r="B167" t="n">
-        <v>57669</v>
+        <v>91825</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18036,42 +18049,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>5467</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626194</v>
+        <v>626319</v>
       </c>
       <c r="R167" t="n">
-        <v>7217951</v>
+        <v>7217868</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18104,11 +18109,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18135,32 +18135,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103786</v>
+        <v>128103823</v>
       </c>
       <c r="B168" t="n">
-        <v>91825</v>
+        <v>98470</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18170,10 +18170,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626319</v>
+        <v>626337</v>
       </c>
       <c r="R168" t="n">
-        <v>7217868</v>
+        <v>7217840</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18232,32 +18232,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103766</v>
+        <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626308</v>
+        <v>626370</v>
       </c>
       <c r="R169" t="n">
-        <v>7217938</v>
+        <v>7217900</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,10 +11145,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B97" t="n">
-        <v>90909</v>
+        <v>78791</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11156,21 +11156,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R97" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11224,6 +11224,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11242,10 +11243,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103745</v>
+        <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>78788</v>
+        <v>90915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11253,21 +11254,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>900</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11278,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626149</v>
+        <v>626328</v>
       </c>
       <c r="R98" t="n">
-        <v>7217977</v>
+        <v>7217861</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,7 +11322,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>128103784</v>
       </c>
       <c r="B99" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103757</v>
+        <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>80132</v>
+        <v>79032</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626239</v>
+        <v>626593</v>
       </c>
       <c r="R100" t="n">
-        <v>7218007</v>
+        <v>7217442</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11508,6 +11508,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11534,32 +11539,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103728</v>
+        <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80161</v>
+        <v>80135</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11574,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626453</v>
+        <v>626239</v>
       </c>
       <c r="R101" t="n">
-        <v>7217719</v>
+        <v>7218007</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11631,32 +11636,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103850</v>
+        <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>80164</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11671,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626593</v>
+        <v>626453</v>
       </c>
       <c r="R102" t="n">
-        <v>7217442</v>
+        <v>7217719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,11 +11707,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11736,7 +11736,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11830,32 +11830,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103703</v>
+        <v>128103812</v>
       </c>
       <c r="B104" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626128</v>
+        <v>626319</v>
       </c>
       <c r="R104" t="n">
-        <v>7218027</v>
+        <v>7217868</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11927,53 +11927,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103719</v>
+        <v>128103806</v>
       </c>
       <c r="B105" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626269</v>
+        <v>626574</v>
       </c>
       <c r="R105" t="n">
-        <v>7217921</v>
+        <v>7217449</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12006,11 +11998,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12037,45 +12024,53 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103812</v>
+        <v>128103719</v>
       </c>
       <c r="B106" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626319</v>
+        <v>626269</v>
       </c>
       <c r="R106" t="n">
-        <v>7217868</v>
+        <v>7217921</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12108,6 +12103,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12134,32 +12134,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128103806</v>
+        <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>626574</v>
+        <v>626128</v>
       </c>
       <c r="R107" t="n">
-        <v>7217449</v>
+        <v>7218027</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12234,7 +12234,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103870</v>
+        <v>128103744</v>
       </c>
       <c r="B111" t="n">
-        <v>78007</v>
+        <v>78791</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626270</v>
+        <v>626454</v>
       </c>
       <c r="R111" t="n">
-        <v>7217834</v>
+        <v>7217736</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12601,6 +12601,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12619,10 +12620,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103716</v>
+        <v>128103870</v>
       </c>
       <c r="B112" t="n">
-        <v>57672</v>
+        <v>78010</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12630,42 +12631,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626454</v>
+        <v>626270</v>
       </c>
       <c r="R112" t="n">
-        <v>7217736</v>
+        <v>7217834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12698,11 +12691,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12729,10 +12717,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103744</v>
+        <v>128103754</v>
       </c>
       <c r="B113" t="n">
-        <v>78788</v>
+        <v>80135</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12740,21 +12728,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12764,10 +12752,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626454</v>
+        <v>626325</v>
       </c>
       <c r="R113" t="n">
-        <v>7217736</v>
+        <v>7217934</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12808,7 +12796,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12827,10 +12814,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103754</v>
+        <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12862,10 +12849,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626325</v>
+        <v>626320</v>
       </c>
       <c r="R114" t="n">
-        <v>7217934</v>
+        <v>7217923</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12924,10 +12911,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103765</v>
+        <v>128103716</v>
       </c>
       <c r="B115" t="n">
-        <v>80132</v>
+        <v>57673</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12935,34 +12922,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R115" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12995,6 +12990,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103831</v>
+        <v>128103871</v>
       </c>
       <c r="B116" t="n">
-        <v>98470</v>
+        <v>92644</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626373</v>
+        <v>626144</v>
       </c>
       <c r="R116" t="n">
-        <v>7217883</v>
+        <v>7217996</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,45 +13118,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103828</v>
+        <v>128103717</v>
       </c>
       <c r="B117" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626202</v>
+        <v>626217</v>
       </c>
       <c r="R117" t="n">
-        <v>7217956</v>
+        <v>7217965</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13189,6 +13197,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13215,32 +13228,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103733</v>
+        <v>128103831</v>
       </c>
       <c r="B118" t="n">
-        <v>98491</v>
+        <v>98478</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13250,10 +13263,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626571</v>
+        <v>626373</v>
       </c>
       <c r="R118" t="n">
-        <v>7217492</v>
+        <v>7217883</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13312,27 +13325,27 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103866</v>
+        <v>128103853</v>
       </c>
       <c r="B119" t="n">
-        <v>80167</v>
+        <v>79032</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -13347,10 +13360,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626282</v>
+        <v>626328</v>
       </c>
       <c r="R119" t="n">
-        <v>7217980</v>
+        <v>7217861</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13409,27 +13422,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103853</v>
+        <v>128103866</v>
       </c>
       <c r="B120" t="n">
-        <v>79029</v>
+        <v>80170</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13444,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626328</v>
+        <v>626282</v>
       </c>
       <c r="R120" t="n">
-        <v>7217861</v>
+        <v>7217980</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13506,32 +13519,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103871</v>
+        <v>128103828</v>
       </c>
       <c r="B121" t="n">
-        <v>92636</v>
+        <v>98478</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13541,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626144</v>
+        <v>626202</v>
       </c>
       <c r="R121" t="n">
-        <v>7217996</v>
+        <v>7217956</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13603,53 +13616,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103717</v>
+        <v>128103733</v>
       </c>
       <c r="B122" t="n">
-        <v>57672</v>
+        <v>98499</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626217</v>
+        <v>626571</v>
       </c>
       <c r="R122" t="n">
-        <v>7217965</v>
+        <v>7217492</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13682,11 +13687,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13713,32 +13713,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103740</v>
+        <v>128103824</v>
       </c>
       <c r="B123" t="n">
-        <v>91648</v>
+        <v>98478</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626128</v>
+        <v>626300</v>
       </c>
       <c r="R123" t="n">
-        <v>7218027</v>
+        <v>7217895</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13810,45 +13810,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103824</v>
+        <v>128103721</v>
       </c>
       <c r="B124" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626300</v>
+        <v>626306</v>
       </c>
       <c r="R124" t="n">
-        <v>7217895</v>
+        <v>7217910</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,6 +13889,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13907,10 +13920,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103746</v>
+        <v>128103740</v>
       </c>
       <c r="B125" t="n">
-        <v>78788</v>
+        <v>91656</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13918,21 +13931,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13955,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626290</v>
+        <v>626128</v>
       </c>
       <c r="R125" t="n">
-        <v>7217851</v>
+        <v>7218027</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13986,7 +13999,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14005,32 +14017,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103782</v>
+        <v>128103746</v>
       </c>
       <c r="B126" t="n">
-        <v>80168</v>
+        <v>78791</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14040,10 +14052,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626380</v>
+        <v>626290</v>
       </c>
       <c r="R126" t="n">
-        <v>7217892</v>
+        <v>7217851</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14084,6 +14096,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14102,32 +14115,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103756</v>
+        <v>128103782</v>
       </c>
       <c r="B127" t="n">
-        <v>80132</v>
+        <v>80171</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14137,10 +14150,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626277</v>
+        <v>626380</v>
       </c>
       <c r="R127" t="n">
-        <v>7217976</v>
+        <v>7217892</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14199,10 +14212,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103772</v>
+        <v>128103756</v>
       </c>
       <c r="B128" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14234,10 +14247,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626347</v>
+        <v>626277</v>
       </c>
       <c r="R128" t="n">
-        <v>7217886</v>
+        <v>7217976</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14296,10 +14309,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103842</v>
+        <v>128103772</v>
       </c>
       <c r="B129" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14307,21 +14320,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14331,10 +14344,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626317</v>
+        <v>626347</v>
       </c>
       <c r="R129" t="n">
-        <v>7217935</v>
+        <v>7217886</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14393,10 +14406,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103721</v>
+        <v>128103842</v>
       </c>
       <c r="B130" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14404,42 +14417,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626306</v>
+        <v>626317</v>
       </c>
       <c r="R130" t="n">
-        <v>7217910</v>
+        <v>7217935</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14472,11 +14477,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14503,53 +14503,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103856</v>
+        <v>128103781</v>
       </c>
       <c r="B131" t="n">
-        <v>57672</v>
+        <v>80171</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626323</v>
+        <v>626239</v>
       </c>
       <c r="R131" t="n">
-        <v>7217908</v>
+        <v>7218007</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14582,11 +14574,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14613,32 +14600,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103696</v>
+        <v>128103867</v>
       </c>
       <c r="B132" t="n">
-        <v>91637</v>
+        <v>80170</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>71</v>
+        <v>6463</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14648,10 +14635,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626167</v>
+        <v>626346</v>
       </c>
       <c r="R132" t="n">
-        <v>7217957</v>
+        <v>7217883</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14710,37 +14697,42 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103787</v>
+        <v>128103856</v>
       </c>
       <c r="B133" t="n">
-        <v>91724</v>
+        <v>57673</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1505</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14748,10 +14740,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626280</v>
+        <v>626323</v>
       </c>
       <c r="R133" t="n">
-        <v>7217822</v>
+        <v>7217908</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14786,13 +14778,17 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14811,32 +14807,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103781</v>
+        <v>128103696</v>
       </c>
       <c r="B134" t="n">
-        <v>80168</v>
+        <v>91645</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6464</v>
+        <v>71</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14846,10 +14842,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626239</v>
+        <v>626167</v>
       </c>
       <c r="R134" t="n">
-        <v>7218007</v>
+        <v>7217957</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14908,32 +14904,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103867</v>
+        <v>128103811</v>
       </c>
       <c r="B135" t="n">
-        <v>80167</v>
+        <v>98478</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14943,10 +14939,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626346</v>
+        <v>626311</v>
       </c>
       <c r="R135" t="n">
-        <v>7217883</v>
+        <v>7217865</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15005,10 +15001,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103811</v>
+        <v>128103787</v>
       </c>
       <c r="B136" t="n">
-        <v>98470</v>
+        <v>91732</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15016,34 +15012,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626311</v>
+        <v>626280</v>
       </c>
       <c r="R136" t="n">
-        <v>7217865</v>
+        <v>7217822</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15084,6 +15083,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15105,7 +15105,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15199,10 +15199,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103769</v>
+        <v>128103773</v>
       </c>
       <c r="B138" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626248</v>
+        <v>626370</v>
       </c>
       <c r="R138" t="n">
-        <v>7218007</v>
+        <v>7217900</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,10 +15296,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R139" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15396,7 +15396,7 @@
         <v>128103835</v>
       </c>
       <c r="B140" t="n">
-        <v>90909</v>
+        <v>90915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103810</v>
+        <v>128103837</v>
       </c>
       <c r="B141" t="n">
-        <v>98470</v>
+        <v>105516</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626290</v>
+        <v>626194</v>
       </c>
       <c r="R141" t="n">
-        <v>7217851</v>
+        <v>7218055</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103837</v>
+        <v>128103810</v>
       </c>
       <c r="B142" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626194</v>
+        <v>626290</v>
       </c>
       <c r="R142" t="n">
-        <v>7218055</v>
+        <v>7217851</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103857</v>
+        <v>128103743</v>
       </c>
       <c r="B143" t="n">
-        <v>91613</v>
+        <v>92642</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626178</v>
+        <v>626130</v>
       </c>
       <c r="R143" t="n">
-        <v>7217957</v>
+        <v>7218000</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,32 +15781,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103863</v>
+        <v>128103857</v>
       </c>
       <c r="B144" t="n">
-        <v>80167</v>
+        <v>91621</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>65</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626248</v>
+        <v>626178</v>
       </c>
       <c r="R144" t="n">
-        <v>7218007</v>
+        <v>7217957</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15881,7 +15881,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15975,32 +15975,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103743</v>
+        <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>92634</v>
+        <v>80170</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626130</v>
+        <v>626248</v>
       </c>
       <c r="R146" t="n">
-        <v>7218000</v>
+        <v>7218007</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103704</v>
+        <v>128103735</v>
       </c>
       <c r="B147" t="n">
-        <v>91352</v>
+        <v>57670</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,34 +16083,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626182</v>
+        <v>626159</v>
       </c>
       <c r="R147" t="n">
-        <v>7218029</v>
+        <v>7217940</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16143,6 +16151,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16169,32 +16182,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103839</v>
+        <v>128103829</v>
       </c>
       <c r="B148" t="n">
-        <v>91370</v>
+        <v>98478</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16217,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626215</v>
+        <v>626217</v>
       </c>
       <c r="R148" t="n">
-        <v>7218028</v>
+        <v>7217956</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,32 +16279,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103753</v>
+        <v>128103807</v>
       </c>
       <c r="B149" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626465</v>
+        <v>626532</v>
       </c>
       <c r="R149" t="n">
-        <v>7217693</v>
+        <v>7217568</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,10 +16376,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103763</v>
+        <v>128103704</v>
       </c>
       <c r="B150" t="n">
-        <v>80132</v>
+        <v>91360</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16374,21 +16387,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16398,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626343</v>
+        <v>626182</v>
       </c>
       <c r="R150" t="n">
-        <v>7217927</v>
+        <v>7218029</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,10 +16473,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103735</v>
+        <v>128103839</v>
       </c>
       <c r="B151" t="n">
-        <v>57669</v>
+        <v>91378</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,42 +16484,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626159</v>
+        <v>626215</v>
       </c>
       <c r="R151" t="n">
-        <v>7217940</v>
+        <v>7218028</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16539,11 +16544,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16570,32 +16570,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103829</v>
+        <v>128103753</v>
       </c>
       <c r="B152" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626217</v>
+        <v>626465</v>
       </c>
       <c r="R152" t="n">
-        <v>7217956</v>
+        <v>7217693</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16667,32 +16667,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103807</v>
+        <v>128103763</v>
       </c>
       <c r="B153" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626532</v>
+        <v>626343</v>
       </c>
       <c r="R153" t="n">
-        <v>7217568</v>
+        <v>7217927</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16764,32 +16764,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128103699</v>
+        <v>128103737</v>
       </c>
       <c r="B154" t="n">
-        <v>91637</v>
+        <v>92654</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>71</v>
+        <v>4365</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>626262</v>
+        <v>626278</v>
       </c>
       <c r="R154" t="n">
-        <v>7217920</v>
+        <v>7217843</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16861,32 +16861,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128103737</v>
+        <v>128103694</v>
       </c>
       <c r="B155" t="n">
-        <v>92646</v>
+        <v>79650</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626278</v>
+        <v>626150</v>
       </c>
       <c r="R155" t="n">
-        <v>7217843</v>
+        <v>7217973</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103694</v>
+        <v>128103699</v>
       </c>
       <c r="B156" t="n">
-        <v>79647</v>
+        <v>91645</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626150</v>
+        <v>626262</v>
       </c>
       <c r="R156" t="n">
-        <v>7217973</v>
+        <v>7217920</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80132</v>
+        <v>92650</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92642</v>
+        <v>80135</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17252,7 +17252,7 @@
         <v>128103808</v>
       </c>
       <c r="B159" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17346,10 +17346,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103770</v>
+        <v>128103851</v>
       </c>
       <c r="B160" t="n">
-        <v>80132</v>
+        <v>79032</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17357,21 +17357,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626249</v>
+        <v>626264</v>
       </c>
       <c r="R160" t="n">
-        <v>7218009</v>
+        <v>7217994</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,10 +17443,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103774</v>
+        <v>128103770</v>
       </c>
       <c r="B161" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626377</v>
+        <v>626249</v>
       </c>
       <c r="R161" t="n">
-        <v>7217880</v>
+        <v>7218009</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17543,7 +17543,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17637,10 +17637,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103851</v>
+        <v>128103774</v>
       </c>
       <c r="B163" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17648,21 +17648,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626264</v>
+        <v>626377</v>
       </c>
       <c r="R163" t="n">
-        <v>7217994</v>
+        <v>7217880</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17734,10 +17734,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103766</v>
+        <v>128103736</v>
       </c>
       <c r="B164" t="n">
-        <v>80132</v>
+        <v>57670</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17745,34 +17745,42 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626308</v>
+        <v>626194</v>
       </c>
       <c r="R164" t="n">
-        <v>7217938</v>
+        <v>7217951</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17805,6 +17813,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17831,32 +17844,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103783</v>
+        <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91735</v>
+        <v>91833</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>298</v>
+        <v>5467</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17879,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626271</v>
+        <v>626319</v>
       </c>
       <c r="R165" t="n">
-        <v>7217852</v>
+        <v>7217868</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,10 +17941,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103736</v>
+        <v>128103766</v>
       </c>
       <c r="B166" t="n">
-        <v>57669</v>
+        <v>80135</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17939,42 +17952,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626194</v>
+        <v>626308</v>
       </c>
       <c r="R166" t="n">
-        <v>7217951</v>
+        <v>7217938</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18007,11 +18012,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18038,32 +18038,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103786</v>
+        <v>128103783</v>
       </c>
       <c r="B167" t="n">
-        <v>91825</v>
+        <v>91743</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5467</v>
+        <v>298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18073,10 +18073,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626319</v>
+        <v>626271</v>
       </c>
       <c r="R167" t="n">
-        <v>7217868</v>
+        <v>7217852</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18138,7 +18138,7 @@
         <v>128103823</v>
       </c>
       <c r="B168" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18523,32 +18523,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103793</v>
+        <v>128103825</v>
       </c>
       <c r="B172" t="n">
-        <v>78787</v>
+        <v>98478</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626317</v>
+        <v>626215</v>
       </c>
       <c r="R172" t="n">
-        <v>7217867</v>
+        <v>7218004</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,10 +18620,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103844</v>
+        <v>128103793</v>
       </c>
       <c r="B173" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18631,21 +18631,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626263</v>
+        <v>626317</v>
       </c>
       <c r="R173" t="n">
-        <v>7217877</v>
+        <v>7217867</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,10 +18717,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103792</v>
+        <v>128103844</v>
       </c>
       <c r="B174" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18728,21 +18728,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626297</v>
+        <v>626263</v>
       </c>
       <c r="R174" t="n">
-        <v>7217856</v>
+        <v>7217877</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18817,7 +18817,7 @@
         <v>128103852</v>
       </c>
       <c r="B175" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18911,32 +18911,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103825</v>
+        <v>128103792</v>
       </c>
       <c r="B176" t="n">
-        <v>98470</v>
+        <v>78790</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626215</v>
+        <v>626297</v>
       </c>
       <c r="R176" t="n">
-        <v>7218004</v>
+        <v>7217856</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19008,32 +19008,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128103692</v>
+        <v>128103758</v>
       </c>
       <c r="B177" t="n">
-        <v>91317</v>
+        <v>80135</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19043,10 +19043,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>626320</v>
+        <v>626196</v>
       </c>
       <c r="R177" t="n">
-        <v>7217864</v>
+        <v>7218053</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,32 +19105,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128103758</v>
+        <v>128103692</v>
       </c>
       <c r="B178" t="n">
-        <v>80132</v>
+        <v>91325</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19140,10 +19140,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>626196</v>
+        <v>626320</v>
       </c>
       <c r="R178" t="n">
-        <v>7218053</v>
+        <v>7217864</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19205,7 +19205,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91302</v>
+        <v>91310</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19299,45 +19299,53 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103727</v>
+        <v>128103734</v>
       </c>
       <c r="B180" t="n">
-        <v>80161</v>
+        <v>57670</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626546</v>
+        <v>626084</v>
       </c>
       <c r="R180" t="n">
-        <v>7217566</v>
+        <v>7218019</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19370,6 +19378,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19396,32 +19409,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103845</v>
+        <v>128103727</v>
       </c>
       <c r="B181" t="n">
-        <v>79029</v>
+        <v>80164</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19431,10 +19444,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626363</v>
+        <v>626546</v>
       </c>
       <c r="R181" t="n">
-        <v>7217905</v>
+        <v>7217566</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19493,10 +19506,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128103734</v>
+        <v>128103845</v>
       </c>
       <c r="B182" t="n">
-        <v>57669</v>
+        <v>79032</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19504,42 +19517,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>626084</v>
+        <v>626363</v>
       </c>
       <c r="R182" t="n">
-        <v>7218019</v>
+        <v>7217905</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19572,11 +19577,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103700</v>
+        <v>128103739</v>
       </c>
       <c r="B183" t="n">
-        <v>91637</v>
+        <v>80136</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>71</v>
+        <v>2081</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626271</v>
+        <v>626582</v>
       </c>
       <c r="R183" t="n">
-        <v>7217852</v>
+        <v>7217455</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,32 +19700,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103761</v>
+        <v>128103859</v>
       </c>
       <c r="B184" t="n">
-        <v>80132</v>
+        <v>92650</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626398</v>
+        <v>626133</v>
       </c>
       <c r="R184" t="n">
-        <v>7217759</v>
+        <v>7217998</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,32 +19797,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103822</v>
+        <v>128103759</v>
       </c>
       <c r="B185" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626528</v>
+        <v>626350</v>
       </c>
       <c r="R185" t="n">
-        <v>7217613</v>
+        <v>7217852</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103739</v>
+        <v>128103695</v>
       </c>
       <c r="B186" t="n">
-        <v>80133</v>
+        <v>79650</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626582</v>
+        <v>626290</v>
       </c>
       <c r="R186" t="n">
-        <v>7217455</v>
+        <v>7217851</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,10 +19991,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103759</v>
+        <v>128103761</v>
       </c>
       <c r="B187" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626350</v>
+        <v>626398</v>
       </c>
       <c r="R187" t="n">
-        <v>7217852</v>
+        <v>7217759</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,10 +20088,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103695</v>
+        <v>128103791</v>
       </c>
       <c r="B188" t="n">
-        <v>79647</v>
+        <v>78790</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20099,21 +20099,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20185,32 +20185,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103791</v>
+        <v>128103700</v>
       </c>
       <c r="B189" t="n">
-        <v>78787</v>
+        <v>91645</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6446</v>
+        <v>71</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626290</v>
+        <v>626271</v>
       </c>
       <c r="R189" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20282,32 +20282,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128103859</v>
+        <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>92642</v>
+        <v>98478</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>626133</v>
+        <v>626528</v>
       </c>
       <c r="R190" t="n">
-        <v>7217998</v>
+        <v>7217613</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -13713,32 +13713,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103824</v>
+        <v>128103782</v>
       </c>
       <c r="B123" t="n">
-        <v>98478</v>
+        <v>80171</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626300</v>
+        <v>626380</v>
       </c>
       <c r="R123" t="n">
-        <v>7217895</v>
+        <v>7217892</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13810,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103721</v>
+        <v>128103756</v>
       </c>
       <c r="B124" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,42 +13821,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626306</v>
+        <v>626277</v>
       </c>
       <c r="R124" t="n">
-        <v>7217910</v>
+        <v>7217976</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,11 +13881,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13920,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103740</v>
+        <v>128103772</v>
       </c>
       <c r="B125" t="n">
-        <v>91656</v>
+        <v>80135</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13931,21 +13918,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13955,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626128</v>
+        <v>626347</v>
       </c>
       <c r="R125" t="n">
-        <v>7218027</v>
+        <v>7217886</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14017,10 +14004,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103746</v>
+        <v>128103842</v>
       </c>
       <c r="B126" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14028,21 +14015,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14052,10 +14039,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626290</v>
+        <v>626317</v>
       </c>
       <c r="R126" t="n">
-        <v>7217851</v>
+        <v>7217935</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14096,7 +14083,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14115,32 +14101,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103782</v>
+        <v>128103824</v>
       </c>
       <c r="B127" t="n">
-        <v>80171</v>
+        <v>98478</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14150,10 +14136,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626380</v>
+        <v>626300</v>
       </c>
       <c r="R127" t="n">
-        <v>7217892</v>
+        <v>7217895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14212,10 +14198,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103756</v>
+        <v>128103746</v>
       </c>
       <c r="B128" t="n">
-        <v>80135</v>
+        <v>78791</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14223,21 +14209,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14247,10 +14233,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626277</v>
+        <v>626290</v>
       </c>
       <c r="R128" t="n">
-        <v>7217976</v>
+        <v>7217851</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14291,6 +14277,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14309,10 +14296,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103772</v>
+        <v>128103721</v>
       </c>
       <c r="B129" t="n">
-        <v>80135</v>
+        <v>57673</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14320,34 +14307,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626347</v>
+        <v>626306</v>
       </c>
       <c r="R129" t="n">
-        <v>7217886</v>
+        <v>7217910</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14380,6 +14375,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14406,10 +14406,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103842</v>
+        <v>128103740</v>
       </c>
       <c r="B130" t="n">
-        <v>79032</v>
+        <v>91656</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14417,21 +14417,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14441,10 +14441,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626317</v>
+        <v>626128</v>
       </c>
       <c r="R130" t="n">
-        <v>7217935</v>
+        <v>7218027</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103735</v>
+        <v>128103753</v>
       </c>
       <c r="B147" t="n">
-        <v>57670</v>
+        <v>80135</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,42 +16083,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626159</v>
+        <v>626465</v>
       </c>
       <c r="R147" t="n">
-        <v>7217940</v>
+        <v>7217693</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16151,11 +16143,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16182,45 +16169,53 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103829</v>
+        <v>128103735</v>
       </c>
       <c r="B148" t="n">
-        <v>98478</v>
+        <v>57670</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626217</v>
+        <v>626159</v>
       </c>
       <c r="R148" t="n">
-        <v>7217956</v>
+        <v>7217940</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16253,6 +16248,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16279,32 +16279,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103807</v>
+        <v>128103704</v>
       </c>
       <c r="B149" t="n">
-        <v>98478</v>
+        <v>91360</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16314,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626532</v>
+        <v>626182</v>
       </c>
       <c r="R149" t="n">
-        <v>7217568</v>
+        <v>7218029</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16376,10 +16376,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103704</v>
+        <v>128103839</v>
       </c>
       <c r="B150" t="n">
-        <v>91360</v>
+        <v>91378</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16387,21 +16387,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16411,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626182</v>
+        <v>626215</v>
       </c>
       <c r="R150" t="n">
-        <v>7218029</v>
+        <v>7218028</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16473,10 +16473,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103839</v>
+        <v>128103763</v>
       </c>
       <c r="B151" t="n">
-        <v>91378</v>
+        <v>80135</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16484,21 +16484,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626215</v>
+        <v>626343</v>
       </c>
       <c r="R151" t="n">
-        <v>7218028</v>
+        <v>7217927</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16570,32 +16570,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103753</v>
+        <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626465</v>
+        <v>626217</v>
       </c>
       <c r="R152" t="n">
-        <v>7217693</v>
+        <v>7217956</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16667,32 +16667,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103763</v>
+        <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626343</v>
+        <v>626532</v>
       </c>
       <c r="R153" t="n">
-        <v>7217927</v>
+        <v>7217568</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -19008,32 +19008,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128103758</v>
+        <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>80135</v>
+        <v>91325</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19043,10 +19043,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>626196</v>
+        <v>626320</v>
       </c>
       <c r="R177" t="n">
-        <v>7218053</v>
+        <v>7217864</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,32 +19105,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128103692</v>
+        <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>91325</v>
+        <v>80135</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19140,10 +19140,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>626320</v>
+        <v>626196</v>
       </c>
       <c r="R178" t="n">
-        <v>7217864</v>
+        <v>7218053</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103745</v>
+        <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>78791</v>
+        <v>57789</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626149</v>
+        <v>626608</v>
       </c>
       <c r="R97" t="n">
-        <v>7217977</v>
+        <v>7217437</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11224,7 +11224,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11243,10 +11242,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B98" t="n">
-        <v>90915</v>
+        <v>78841</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11254,21 +11253,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11278,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R98" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11322,6 +11321,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11340,32 +11340,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103784</v>
+        <v>128103836</v>
       </c>
       <c r="B99" t="n">
-        <v>57777</v>
+        <v>91007</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103031</v>
+        <v>900</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626608</v>
+        <v>626328</v>
       </c>
       <c r="R99" t="n">
-        <v>7217437</v>
+        <v>7217861</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103850</v>
+        <v>128103701</v>
       </c>
       <c r="B100" t="n">
-        <v>79032</v>
+        <v>91452</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626593</v>
+        <v>626222</v>
       </c>
       <c r="R100" t="n">
-        <v>7217442</v>
+        <v>7218014</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11508,11 +11508,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11539,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103757</v>
+        <v>128103728</v>
       </c>
       <c r="B101" t="n">
-        <v>80135</v>
+        <v>80217</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11574,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626239</v>
+        <v>626453</v>
       </c>
       <c r="R101" t="n">
-        <v>7218007</v>
+        <v>7217719</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11636,32 +11631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103728</v>
+        <v>128103850</v>
       </c>
       <c r="B102" t="n">
-        <v>80164</v>
+        <v>79083</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11671,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626453</v>
+        <v>626593</v>
       </c>
       <c r="R102" t="n">
-        <v>7217719</v>
+        <v>7217442</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11707,6 +11702,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11733,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103701</v>
+        <v>128103757</v>
       </c>
       <c r="B103" t="n">
-        <v>91360</v>
+        <v>80188</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11744,21 +11744,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11768,10 +11768,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626222</v>
+        <v>626239</v>
       </c>
       <c r="R103" t="n">
-        <v>7218014</v>
+        <v>7218007</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11830,45 +11830,53 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103812</v>
+        <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626319</v>
+        <v>626269</v>
       </c>
       <c r="R104" t="n">
-        <v>7217868</v>
+        <v>7217921</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11901,6 +11909,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11927,10 +11940,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103806</v>
+        <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11962,10 +11975,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626574</v>
+        <v>626319</v>
       </c>
       <c r="R105" t="n">
-        <v>7217449</v>
+        <v>7217868</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12024,53 +12037,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103719</v>
+        <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626269</v>
+        <v>626574</v>
       </c>
       <c r="R106" t="n">
-        <v>7217921</v>
+        <v>7217449</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12103,11 +12108,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12137,7 +12137,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103744</v>
+        <v>128103870</v>
       </c>
       <c r="B111" t="n">
-        <v>78791</v>
+        <v>78055</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626454</v>
+        <v>626270</v>
       </c>
       <c r="R111" t="n">
-        <v>7217736</v>
+        <v>7217834</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12601,7 +12601,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12620,10 +12619,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103870</v>
+        <v>128103754</v>
       </c>
       <c r="B112" t="n">
-        <v>78010</v>
+        <v>80188</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12631,21 +12630,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12655,10 +12654,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626270</v>
+        <v>626325</v>
       </c>
       <c r="R112" t="n">
-        <v>7217834</v>
+        <v>7217934</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12717,10 +12716,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103754</v>
+        <v>128103716</v>
       </c>
       <c r="B113" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12728,34 +12727,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626325</v>
+        <v>626454</v>
       </c>
       <c r="R113" t="n">
-        <v>7217934</v>
+        <v>7217736</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12788,6 +12795,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12814,10 +12826,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103765</v>
+        <v>128103744</v>
       </c>
       <c r="B114" t="n">
-        <v>80135</v>
+        <v>78841</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12825,21 +12837,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12849,10 +12861,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R114" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12893,6 +12905,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12911,10 +12924,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103716</v>
+        <v>128103765</v>
       </c>
       <c r="B115" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12922,42 +12935,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626454</v>
+        <v>626320</v>
       </c>
       <c r="R115" t="n">
-        <v>7217736</v>
+        <v>7217923</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12990,11 +12995,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13021,10 +13021,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103871</v>
+        <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>92644</v>
+        <v>79083</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13032,21 +13032,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626144</v>
+        <v>626328</v>
       </c>
       <c r="R116" t="n">
-        <v>7217996</v>
+        <v>7217861</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13121,7 +13121,7 @@
         <v>128103717</v>
       </c>
       <c r="B117" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13228,32 +13228,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103831</v>
+        <v>128103866</v>
       </c>
       <c r="B118" t="n">
-        <v>98478</v>
+        <v>80223</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626373</v>
+        <v>626282</v>
       </c>
       <c r="R118" t="n">
-        <v>7217883</v>
+        <v>7217980</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13325,10 +13325,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103853</v>
+        <v>128103871</v>
       </c>
       <c r="B119" t="n">
-        <v>79032</v>
+        <v>92736</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13336,21 +13336,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626328</v>
+        <v>626144</v>
       </c>
       <c r="R119" t="n">
-        <v>7217861</v>
+        <v>7217996</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103866</v>
+        <v>128103831</v>
       </c>
       <c r="B120" t="n">
-        <v>80170</v>
+        <v>98571</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626282</v>
+        <v>626373</v>
       </c>
       <c r="R120" t="n">
-        <v>7217980</v>
+        <v>7217883</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13522,7 +13522,7 @@
         <v>128103828</v>
       </c>
       <c r="B121" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>128103733</v>
       </c>
       <c r="B122" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13713,32 +13713,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103782</v>
+        <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>80171</v>
+        <v>91748</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626380</v>
+        <v>626128</v>
       </c>
       <c r="R123" t="n">
-        <v>7217892</v>
+        <v>7218027</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13810,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103756</v>
+        <v>128103842</v>
       </c>
       <c r="B124" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,21 +13821,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13845,10 +13845,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626277</v>
+        <v>626317</v>
       </c>
       <c r="R124" t="n">
-        <v>7217976</v>
+        <v>7217935</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13907,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103772</v>
+        <v>128103721</v>
       </c>
       <c r="B125" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13918,34 +13918,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626347</v>
+        <v>626306</v>
       </c>
       <c r="R125" t="n">
-        <v>7217886</v>
+        <v>7217910</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13978,6 +13986,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14004,32 +14017,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103842</v>
+        <v>128103824</v>
       </c>
       <c r="B126" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14039,10 +14052,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626317</v>
+        <v>626300</v>
       </c>
       <c r="R126" t="n">
-        <v>7217935</v>
+        <v>7217895</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14101,32 +14114,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103824</v>
+        <v>128103782</v>
       </c>
       <c r="B127" t="n">
-        <v>98478</v>
+        <v>80224</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14136,10 +14149,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626300</v>
+        <v>626380</v>
       </c>
       <c r="R127" t="n">
-        <v>7217895</v>
+        <v>7217892</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14198,10 +14211,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103746</v>
+        <v>128103756</v>
       </c>
       <c r="B128" t="n">
-        <v>78791</v>
+        <v>80188</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14209,21 +14222,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14233,10 +14246,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626290</v>
+        <v>626277</v>
       </c>
       <c r="R128" t="n">
-        <v>7217851</v>
+        <v>7217976</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14277,7 +14290,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14296,10 +14308,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103721</v>
+        <v>128103772</v>
       </c>
       <c r="B129" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14307,42 +14319,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626306</v>
+        <v>626347</v>
       </c>
       <c r="R129" t="n">
-        <v>7217910</v>
+        <v>7217886</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14375,11 +14379,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14406,10 +14405,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103740</v>
+        <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>91656</v>
+        <v>78841</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14417,21 +14416,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14441,10 +14440,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626128</v>
+        <v>626290</v>
       </c>
       <c r="R130" t="n">
-        <v>7218027</v>
+        <v>7217851</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14485,6 +14484,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14503,45 +14503,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103781</v>
+        <v>128103787</v>
       </c>
       <c r="B131" t="n">
-        <v>80171</v>
+        <v>91824</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6464</v>
+        <v>1505</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626239</v>
+        <v>626280</v>
       </c>
       <c r="R131" t="n">
-        <v>7218007</v>
+        <v>7217822</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14582,6 +14585,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14600,10 +14604,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103867</v>
+        <v>128103781</v>
       </c>
       <c r="B132" t="n">
-        <v>80170</v>
+        <v>80224</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14611,21 +14615,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14635,10 +14639,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626346</v>
+        <v>626239</v>
       </c>
       <c r="R132" t="n">
-        <v>7217883</v>
+        <v>7218007</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14697,53 +14701,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103856</v>
+        <v>128103867</v>
       </c>
       <c r="B133" t="n">
-        <v>57673</v>
+        <v>80223</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626323</v>
+        <v>626346</v>
       </c>
       <c r="R133" t="n">
-        <v>7217908</v>
+        <v>7217883</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14776,11 +14772,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14810,7 +14801,7 @@
         <v>128103696</v>
       </c>
       <c r="B134" t="n">
-        <v>91645</v>
+        <v>91737</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14904,45 +14895,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103811</v>
+        <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626311</v>
+        <v>626323</v>
       </c>
       <c r="R135" t="n">
-        <v>7217865</v>
+        <v>7217908</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14975,6 +14974,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15001,10 +15005,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103787</v>
+        <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>91732</v>
+        <v>98571</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15012,37 +15016,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626280</v>
+        <v>626311</v>
       </c>
       <c r="R136" t="n">
-        <v>7217822</v>
+        <v>7217865</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15083,7 +15084,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -15105,7 +15105,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15199,10 +15199,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103773</v>
+        <v>128103835</v>
       </c>
       <c r="B138" t="n">
-        <v>80135</v>
+        <v>91007</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15210,21 +15210,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>900</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626370</v>
+        <v>626354</v>
       </c>
       <c r="R138" t="n">
-        <v>7217900</v>
+        <v>7217769</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15299,7 +15299,7 @@
         <v>128103769</v>
       </c>
       <c r="B139" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15393,10 +15393,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103835</v>
+        <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>90915</v>
+        <v>80188</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15404,21 +15404,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>900</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626354</v>
+        <v>626370</v>
       </c>
       <c r="R140" t="n">
-        <v>7217769</v>
+        <v>7217900</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103837</v>
+        <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>105516</v>
+        <v>98571</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626194</v>
+        <v>626290</v>
       </c>
       <c r="R141" t="n">
-        <v>7218055</v>
+        <v>7217851</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103810</v>
+        <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>98478</v>
+        <v>105609</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626290</v>
+        <v>626194</v>
       </c>
       <c r="R142" t="n">
-        <v>7217851</v>
+        <v>7218055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103743</v>
+        <v>128103863</v>
       </c>
       <c r="B143" t="n">
-        <v>92642</v>
+        <v>80223</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626130</v>
+        <v>626248</v>
       </c>
       <c r="R143" t="n">
-        <v>7218000</v>
+        <v>7218007</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15784,7 +15784,7 @@
         <v>128103857</v>
       </c>
       <c r="B144" t="n">
-        <v>91621</v>
+        <v>91713</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15878,10 +15878,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103843</v>
+        <v>128103743</v>
       </c>
       <c r="B145" t="n">
-        <v>79032</v>
+        <v>92734</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15889,21 +15889,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626276</v>
+        <v>626130</v>
       </c>
       <c r="R145" t="n">
-        <v>7217891</v>
+        <v>7218000</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15975,27 +15975,27 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103863</v>
+        <v>128103843</v>
       </c>
       <c r="B146" t="n">
-        <v>80170</v>
+        <v>79083</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626248</v>
+        <v>626276</v>
       </c>
       <c r="R146" t="n">
-        <v>7218007</v>
+        <v>7217891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16075,7 +16075,7 @@
         <v>128103753</v>
       </c>
       <c r="B147" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16169,10 +16169,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103735</v>
+        <v>128103763</v>
       </c>
       <c r="B148" t="n">
-        <v>57670</v>
+        <v>80188</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16180,42 +16180,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626159</v>
+        <v>626343</v>
       </c>
       <c r="R148" t="n">
-        <v>7217940</v>
+        <v>7217927</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16248,11 +16240,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16282,7 +16269,7 @@
         <v>128103704</v>
       </c>
       <c r="B149" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16376,10 +16363,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103839</v>
+        <v>128103735</v>
       </c>
       <c r="B150" t="n">
-        <v>91378</v>
+        <v>57682</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16387,34 +16374,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626215</v>
+        <v>626159</v>
       </c>
       <c r="R150" t="n">
-        <v>7218028</v>
+        <v>7217940</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16447,6 +16442,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16473,10 +16473,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103763</v>
+        <v>128103839</v>
       </c>
       <c r="B151" t="n">
-        <v>80135</v>
+        <v>91470</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16484,21 +16484,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626343</v>
+        <v>626215</v>
       </c>
       <c r="R151" t="n">
-        <v>7217927</v>
+        <v>7218028</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16573,7 +16573,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16764,32 +16764,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128103737</v>
+        <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>92654</v>
+        <v>91737</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4365</v>
+        <v>71</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>626278</v>
+        <v>626262</v>
       </c>
       <c r="R154" t="n">
-        <v>7217843</v>
+        <v>7217920</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16861,32 +16861,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128103694</v>
+        <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>79650</v>
+        <v>92746</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626150</v>
+        <v>626278</v>
       </c>
       <c r="R155" t="n">
-        <v>7217973</v>
+        <v>7217843</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103699</v>
+        <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>91645</v>
+        <v>79702</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626262</v>
+        <v>626150</v>
       </c>
       <c r="R156" t="n">
-        <v>7217920</v>
+        <v>7217973</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17058,7 +17058,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>128103808</v>
       </c>
       <c r="B159" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17346,10 +17346,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103851</v>
+        <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17357,21 +17357,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626264</v>
+        <v>626249</v>
       </c>
       <c r="R160" t="n">
-        <v>7217994</v>
+        <v>7218009</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,10 +17443,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103770</v>
+        <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626249</v>
+        <v>626377</v>
       </c>
       <c r="R161" t="n">
-        <v>7218009</v>
+        <v>7217880</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17543,7 +17543,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17637,10 +17637,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103774</v>
+        <v>128103851</v>
       </c>
       <c r="B163" t="n">
-        <v>80135</v>
+        <v>79083</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17648,21 +17648,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626377</v>
+        <v>626264</v>
       </c>
       <c r="R163" t="n">
-        <v>7217880</v>
+        <v>7217994</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17734,10 +17734,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103736</v>
+        <v>128103766</v>
       </c>
       <c r="B164" t="n">
-        <v>57670</v>
+        <v>80188</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17745,42 +17745,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626194</v>
+        <v>626308</v>
       </c>
       <c r="R164" t="n">
-        <v>7217951</v>
+        <v>7217938</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17813,11 +17805,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17847,7 +17834,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91833</v>
+        <v>91925</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17941,32 +17928,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103766</v>
+        <v>128103783</v>
       </c>
       <c r="B166" t="n">
-        <v>80135</v>
+        <v>91835</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17976,10 +17963,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626308</v>
+        <v>626271</v>
       </c>
       <c r="R166" t="n">
-        <v>7217938</v>
+        <v>7217852</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18038,45 +18025,53 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103783</v>
+        <v>128103736</v>
       </c>
       <c r="B167" t="n">
-        <v>91743</v>
+        <v>57682</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>298</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626271</v>
+        <v>626194</v>
       </c>
       <c r="R167" t="n">
-        <v>7217852</v>
+        <v>7217951</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18109,6 +18104,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18138,7 +18138,7 @@
         <v>128103823</v>
       </c>
       <c r="B168" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18523,32 +18523,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103825</v>
+        <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>98478</v>
+        <v>78840</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626215</v>
+        <v>626317</v>
       </c>
       <c r="R172" t="n">
-        <v>7218004</v>
+        <v>7217867</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,10 +18620,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103793</v>
+        <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>78790</v>
+        <v>79083</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18631,21 +18631,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626317</v>
+        <v>626263</v>
       </c>
       <c r="R173" t="n">
-        <v>7217867</v>
+        <v>7217877</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,10 +18717,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103844</v>
+        <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626263</v>
+        <v>626320</v>
       </c>
       <c r="R174" t="n">
-        <v>7217877</v>
+        <v>7217901</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18814,10 +18814,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103852</v>
+        <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>79032</v>
+        <v>78840</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18825,21 +18825,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626320</v>
+        <v>626297</v>
       </c>
       <c r="R175" t="n">
-        <v>7217901</v>
+        <v>7217856</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18911,32 +18911,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103792</v>
+        <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>78790</v>
+        <v>98571</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626297</v>
+        <v>626215</v>
       </c>
       <c r="R176" t="n">
-        <v>7217856</v>
+        <v>7218004</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19011,7 +19011,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19202,10 +19202,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103729</v>
+        <v>128103734</v>
       </c>
       <c r="B179" t="n">
-        <v>91310</v>
+        <v>57682</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19213,34 +19213,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626278</v>
+        <v>626084</v>
       </c>
       <c r="R179" t="n">
-        <v>7217843</v>
+        <v>7218019</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19273,6 +19281,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19299,10 +19312,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103734</v>
+        <v>128103845</v>
       </c>
       <c r="B180" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19310,42 +19323,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626084</v>
+        <v>626363</v>
       </c>
       <c r="R180" t="n">
-        <v>7218019</v>
+        <v>7217905</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19378,11 +19383,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19412,7 +19412,7 @@
         <v>128103727</v>
       </c>
       <c r="B181" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19506,10 +19506,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128103845</v>
+        <v>128103729</v>
       </c>
       <c r="B182" t="n">
-        <v>79032</v>
+        <v>91402</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19517,21 +19517,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19541,10 +19541,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>626363</v>
+        <v>626278</v>
       </c>
       <c r="R182" t="n">
-        <v>7217905</v>
+        <v>7217843</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19606,7 +19606,7 @@
         <v>128103739</v>
       </c>
       <c r="B183" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19700,32 +19700,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103859</v>
+        <v>128103759</v>
       </c>
       <c r="B184" t="n">
-        <v>92650</v>
+        <v>80188</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626133</v>
+        <v>626350</v>
       </c>
       <c r="R184" t="n">
-        <v>7217998</v>
+        <v>7217852</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,10 +19797,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103759</v>
+        <v>128103761</v>
       </c>
       <c r="B185" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626350</v>
+        <v>626398</v>
       </c>
       <c r="R185" t="n">
-        <v>7217852</v>
+        <v>7217759</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19897,7 +19897,7 @@
         <v>128103695</v>
       </c>
       <c r="B186" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19991,10 +19991,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103761</v>
+        <v>128103791</v>
       </c>
       <c r="B187" t="n">
-        <v>80135</v>
+        <v>78840</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20002,21 +20002,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626398</v>
+        <v>626290</v>
       </c>
       <c r="R187" t="n">
-        <v>7217759</v>
+        <v>7217851</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,32 +20088,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103791</v>
+        <v>128103700</v>
       </c>
       <c r="B188" t="n">
-        <v>78790</v>
+        <v>91737</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>71</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626290</v>
+        <v>626271</v>
       </c>
       <c r="R188" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20185,32 +20185,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103700</v>
+        <v>128103859</v>
       </c>
       <c r="B189" t="n">
-        <v>91645</v>
+        <v>92742</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626271</v>
+        <v>626133</v>
       </c>
       <c r="R189" t="n">
-        <v>7217852</v>
+        <v>7217998</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20285,7 +20285,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11242,10 +11242,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103745</v>
+        <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>78841</v>
+        <v>91007</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11253,21 +11253,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>900</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626149</v>
+        <v>626328</v>
       </c>
       <c r="R98" t="n">
-        <v>7217977</v>
+        <v>7217861</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,7 +11321,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11340,10 +11339,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>91007</v>
+        <v>78841</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11351,21 +11350,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11375,10 +11374,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R99" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11419,6 +11418,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11830,53 +11830,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103719</v>
+        <v>128103812</v>
       </c>
       <c r="B104" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626269</v>
+        <v>626319</v>
       </c>
       <c r="R104" t="n">
-        <v>7217921</v>
+        <v>7217868</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11909,11 +11901,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11940,7 +11927,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103812</v>
+        <v>128103806</v>
       </c>
       <c r="B105" t="n">
         <v>98571</v>
@@ -11975,10 +11962,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626319</v>
+        <v>626574</v>
       </c>
       <c r="R105" t="n">
-        <v>7217868</v>
+        <v>7217449</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12037,45 +12024,53 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103806</v>
+        <v>128103719</v>
       </c>
       <c r="B106" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626574</v>
+        <v>626269</v>
       </c>
       <c r="R106" t="n">
-        <v>7217449</v>
+        <v>7217921</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12108,6 +12103,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103870</v>
+        <v>128103765</v>
       </c>
       <c r="B111" t="n">
-        <v>78055</v>
+        <v>80188</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626270</v>
+        <v>626320</v>
       </c>
       <c r="R111" t="n">
-        <v>7217834</v>
+        <v>7217923</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103754</v>
+        <v>128103870</v>
       </c>
       <c r="B112" t="n">
-        <v>80188</v>
+        <v>78055</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626325</v>
+        <v>626270</v>
       </c>
       <c r="R112" t="n">
-        <v>7217934</v>
+        <v>7217834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12716,10 +12716,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103716</v>
+        <v>128103754</v>
       </c>
       <c r="B113" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12727,42 +12727,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626454</v>
+        <v>626325</v>
       </c>
       <c r="R113" t="n">
-        <v>7217736</v>
+        <v>7217934</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12795,11 +12787,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12826,10 +12813,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103744</v>
+        <v>128103716</v>
       </c>
       <c r="B114" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12837,24 +12824,32 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
@@ -12899,13 +12894,17 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12924,10 +12923,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103765</v>
+        <v>128103744</v>
       </c>
       <c r="B115" t="n">
-        <v>80188</v>
+        <v>78841</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12935,21 +12934,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12959,10 +12958,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R115" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13003,6 +13002,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13118,53 +13118,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103717</v>
+        <v>128103831</v>
       </c>
       <c r="B117" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626217</v>
+        <v>626373</v>
       </c>
       <c r="R117" t="n">
-        <v>7217965</v>
+        <v>7217883</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13197,11 +13189,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13228,32 +13215,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103866</v>
+        <v>128103828</v>
       </c>
       <c r="B118" t="n">
-        <v>80223</v>
+        <v>98571</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13263,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626282</v>
+        <v>626202</v>
       </c>
       <c r="R118" t="n">
-        <v>7217980</v>
+        <v>7217956</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13422,32 +13409,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103831</v>
+        <v>128103866</v>
       </c>
       <c r="B120" t="n">
-        <v>98571</v>
+        <v>80223</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13444,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626373</v>
+        <v>626282</v>
       </c>
       <c r="R120" t="n">
-        <v>7217883</v>
+        <v>7217980</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,45 +13506,53 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103828</v>
+        <v>128103717</v>
       </c>
       <c r="B121" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626202</v>
+        <v>626217</v>
       </c>
       <c r="R121" t="n">
-        <v>7217956</v>
+        <v>7217965</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13590,6 +13585,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13810,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103842</v>
+        <v>128103721</v>
       </c>
       <c r="B124" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,34 +13821,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626317</v>
+        <v>626306</v>
       </c>
       <c r="R124" t="n">
-        <v>7217935</v>
+        <v>7217910</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,6 +13889,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13907,10 +13920,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103721</v>
+        <v>128103746</v>
       </c>
       <c r="B125" t="n">
-        <v>57685</v>
+        <v>78841</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13918,42 +13931,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626306</v>
+        <v>626290</v>
       </c>
       <c r="R125" t="n">
-        <v>7217910</v>
+        <v>7217851</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13988,17 +13993,13 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14017,32 +14018,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103824</v>
+        <v>128103756</v>
       </c>
       <c r="B126" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14052,10 +14053,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626300</v>
+        <v>626277</v>
       </c>
       <c r="R126" t="n">
-        <v>7217895</v>
+        <v>7217976</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14114,32 +14115,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103782</v>
+        <v>128103772</v>
       </c>
       <c r="B127" t="n">
-        <v>80224</v>
+        <v>80188</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14149,10 +14150,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626380</v>
+        <v>626347</v>
       </c>
       <c r="R127" t="n">
-        <v>7217892</v>
+        <v>7217886</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14211,32 +14212,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103756</v>
+        <v>128103782</v>
       </c>
       <c r="B128" t="n">
-        <v>80188</v>
+        <v>80224</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14246,10 +14247,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626277</v>
+        <v>626380</v>
       </c>
       <c r="R128" t="n">
-        <v>7217976</v>
+        <v>7217892</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14308,10 +14309,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103772</v>
+        <v>128103842</v>
       </c>
       <c r="B129" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,21 +14320,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14343,10 +14344,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626347</v>
+        <v>626317</v>
       </c>
       <c r="R129" t="n">
-        <v>7217886</v>
+        <v>7217935</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14405,32 +14406,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103746</v>
+        <v>128103824</v>
       </c>
       <c r="B130" t="n">
-        <v>78841</v>
+        <v>98571</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14440,10 +14441,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626290</v>
+        <v>626300</v>
       </c>
       <c r="R130" t="n">
-        <v>7217851</v>
+        <v>7217895</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14484,7 +14485,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14503,10 +14503,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103787</v>
+        <v>128103811</v>
       </c>
       <c r="B131" t="n">
-        <v>91824</v>
+        <v>98571</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14514,37 +14514,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626280</v>
+        <v>626311</v>
       </c>
       <c r="R131" t="n">
-        <v>7217822</v>
+        <v>7217865</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14585,7 +14582,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14604,32 +14600,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103781</v>
+        <v>128103827</v>
       </c>
       <c r="B132" t="n">
-        <v>80224</v>
+        <v>98571</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14639,10 +14635,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626239</v>
+        <v>626128</v>
       </c>
       <c r="R132" t="n">
-        <v>7218007</v>
+        <v>7218027</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14701,45 +14697,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103867</v>
+        <v>128103787</v>
       </c>
       <c r="B133" t="n">
-        <v>80223</v>
+        <v>91824</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6463</v>
+        <v>1505</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626346</v>
+        <v>626280</v>
       </c>
       <c r="R133" t="n">
-        <v>7217883</v>
+        <v>7217822</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14780,6 +14779,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14895,53 +14895,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103856</v>
+        <v>128103781</v>
       </c>
       <c r="B135" t="n">
-        <v>57685</v>
+        <v>80224</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626323</v>
+        <v>626239</v>
       </c>
       <c r="R135" t="n">
-        <v>7217908</v>
+        <v>7218007</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14974,11 +14966,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15005,32 +14992,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103811</v>
+        <v>128103867</v>
       </c>
       <c r="B136" t="n">
-        <v>98571</v>
+        <v>80223</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15040,10 +15027,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626311</v>
+        <v>626346</v>
       </c>
       <c r="R136" t="n">
-        <v>7217865</v>
+        <v>7217883</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15102,45 +15089,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103827</v>
+        <v>128103856</v>
       </c>
       <c r="B137" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626128</v>
+        <v>626323</v>
       </c>
       <c r="R137" t="n">
-        <v>7218027</v>
+        <v>7217908</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15173,6 +15168,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15199,32 +15199,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103835</v>
+        <v>128103837</v>
       </c>
       <c r="B138" t="n">
-        <v>91007</v>
+        <v>105609</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>900</v>
+        <v>221144</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626354</v>
+        <v>626194</v>
       </c>
       <c r="R138" t="n">
-        <v>7217769</v>
+        <v>7218055</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103769</v>
+        <v>128103810</v>
       </c>
       <c r="B139" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626248</v>
+        <v>626290</v>
       </c>
       <c r="R139" t="n">
-        <v>7218007</v>
+        <v>7217851</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103810</v>
+        <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626290</v>
+        <v>626248</v>
       </c>
       <c r="R141" t="n">
-        <v>7217851</v>
+        <v>7218007</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103837</v>
+        <v>128103835</v>
       </c>
       <c r="B142" t="n">
-        <v>105609</v>
+        <v>91007</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221144</v>
+        <v>900</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626194</v>
+        <v>626354</v>
       </c>
       <c r="R142" t="n">
-        <v>7218055</v>
+        <v>7217769</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103863</v>
+        <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>80223</v>
+        <v>91713</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>65</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626248</v>
+        <v>626178</v>
       </c>
       <c r="R143" t="n">
-        <v>7218007</v>
+        <v>7217957</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,32 +15781,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103857</v>
+        <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>91713</v>
+        <v>92734</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626178</v>
+        <v>626130</v>
       </c>
       <c r="R144" t="n">
-        <v>7217957</v>
+        <v>7218000</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,10 +15878,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103743</v>
+        <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>92734</v>
+        <v>79083</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15889,21 +15889,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626130</v>
+        <v>626276</v>
       </c>
       <c r="R145" t="n">
-        <v>7218000</v>
+        <v>7217891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15975,27 +15975,27 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103843</v>
+        <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>79083</v>
+        <v>80223</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626276</v>
+        <v>626248</v>
       </c>
       <c r="R146" t="n">
-        <v>7217891</v>
+        <v>7218007</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16363,10 +16363,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103735</v>
+        <v>128103839</v>
       </c>
       <c r="B150" t="n">
-        <v>57682</v>
+        <v>91470</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16374,42 +16374,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626159</v>
+        <v>626215</v>
       </c>
       <c r="R150" t="n">
-        <v>7217940</v>
+        <v>7218028</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16442,11 +16434,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16473,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103839</v>
+        <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>91470</v>
+        <v>57682</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16484,34 +16471,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626215</v>
+        <v>626159</v>
       </c>
       <c r="R151" t="n">
-        <v>7218028</v>
+        <v>7217940</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16544,6 +16539,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B157" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R157" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R158" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17249,32 +17249,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103808</v>
+        <v>128103774</v>
       </c>
       <c r="B159" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626216</v>
+        <v>626377</v>
       </c>
       <c r="R159" t="n">
-        <v>7217940</v>
+        <v>7217880</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17443,10 +17443,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103774</v>
+        <v>128103851</v>
       </c>
       <c r="B161" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17454,21 +17454,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626377</v>
+        <v>626264</v>
       </c>
       <c r="R161" t="n">
-        <v>7217880</v>
+        <v>7217994</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17637,32 +17637,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128103851</v>
+        <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>626264</v>
+        <v>626216</v>
       </c>
       <c r="R163" t="n">
-        <v>7217994</v>
+        <v>7217940</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103766</v>
+        <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>80188</v>
+        <v>91835</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626308</v>
+        <v>626271</v>
       </c>
       <c r="R164" t="n">
-        <v>7217938</v>
+        <v>7217852</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17928,32 +17928,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103783</v>
+        <v>128103766</v>
       </c>
       <c r="B166" t="n">
-        <v>91835</v>
+        <v>80188</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>298</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626271</v>
+        <v>626308</v>
       </c>
       <c r="R166" t="n">
-        <v>7217852</v>
+        <v>7217938</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18329,32 +18329,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128103785</v>
+        <v>128103809</v>
       </c>
       <c r="B170" t="n">
-        <v>57789</v>
+        <v>98571</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>626322</v>
+        <v>626232</v>
       </c>
       <c r="R170" t="n">
-        <v>7217855</v>
+        <v>7217960</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18426,32 +18426,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128103809</v>
+        <v>128103785</v>
       </c>
       <c r="B171" t="n">
-        <v>98571</v>
+        <v>57789</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18461,10 +18461,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>626232</v>
+        <v>626322</v>
       </c>
       <c r="R171" t="n">
-        <v>7217960</v>
+        <v>7217855</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18523,10 +18523,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103793</v>
+        <v>128103852</v>
       </c>
       <c r="B172" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18534,21 +18534,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626317</v>
+        <v>626320</v>
       </c>
       <c r="R172" t="n">
-        <v>7217867</v>
+        <v>7217901</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,10 +18620,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103844</v>
+        <v>128103792</v>
       </c>
       <c r="B173" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18631,21 +18631,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626263</v>
+        <v>626297</v>
       </c>
       <c r="R173" t="n">
-        <v>7217877</v>
+        <v>7217856</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,7 +18717,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103852</v>
+        <v>128103844</v>
       </c>
       <c r="B174" t="n">
         <v>79083</v>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626320</v>
+        <v>626263</v>
       </c>
       <c r="R174" t="n">
-        <v>7217901</v>
+        <v>7217877</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18814,7 +18814,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103792</v>
+        <v>128103793</v>
       </c>
       <c r="B175" t="n">
         <v>78840</v>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626297</v>
+        <v>626317</v>
       </c>
       <c r="R175" t="n">
-        <v>7217856</v>
+        <v>7217867</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19008,32 +19008,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128103692</v>
+        <v>128103758</v>
       </c>
       <c r="B177" t="n">
-        <v>91417</v>
+        <v>80188</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19043,10 +19043,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>626320</v>
+        <v>626196</v>
       </c>
       <c r="R177" t="n">
-        <v>7217864</v>
+        <v>7218053</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,32 +19105,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128103758</v>
+        <v>128103692</v>
       </c>
       <c r="B178" t="n">
-        <v>80188</v>
+        <v>91417</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19140,10 +19140,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>626196</v>
+        <v>626320</v>
       </c>
       <c r="R178" t="n">
-        <v>7218053</v>
+        <v>7217864</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19202,10 +19202,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103734</v>
+        <v>128103845</v>
       </c>
       <c r="B179" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19213,42 +19213,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626084</v>
+        <v>626363</v>
       </c>
       <c r="R179" t="n">
-        <v>7218019</v>
+        <v>7217905</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19281,11 +19273,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19312,32 +19299,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103845</v>
+        <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19347,10 +19334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626363</v>
+        <v>626546</v>
       </c>
       <c r="R180" t="n">
-        <v>7217905</v>
+        <v>7217566</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19409,45 +19396,53 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103727</v>
+        <v>128103734</v>
       </c>
       <c r="B181" t="n">
-        <v>80217</v>
+        <v>57682</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626546</v>
+        <v>626084</v>
       </c>
       <c r="R181" t="n">
-        <v>7217566</v>
+        <v>7218019</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19480,6 +19475,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103739</v>
+        <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>80189</v>
+        <v>92742</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626582</v>
+        <v>626133</v>
       </c>
       <c r="R183" t="n">
-        <v>7217455</v>
+        <v>7217998</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103759</v>
+        <v>128103791</v>
       </c>
       <c r="B184" t="n">
-        <v>80188</v>
+        <v>78840</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626350</v>
+        <v>626290</v>
       </c>
       <c r="R184" t="n">
-        <v>7217852</v>
+        <v>7217851</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,10 +19797,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103761</v>
+        <v>128103695</v>
       </c>
       <c r="B185" t="n">
-        <v>80188</v>
+        <v>79702</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19808,21 +19808,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626398</v>
+        <v>626290</v>
       </c>
       <c r="R185" t="n">
-        <v>7217759</v>
+        <v>7217851</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103695</v>
+        <v>128103761</v>
       </c>
       <c r="B186" t="n">
-        <v>79702</v>
+        <v>80188</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626290</v>
+        <v>626398</v>
       </c>
       <c r="R186" t="n">
-        <v>7217851</v>
+        <v>7217759</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,10 +19991,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103791</v>
+        <v>128103739</v>
       </c>
       <c r="B187" t="n">
-        <v>78840</v>
+        <v>80189</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20002,21 +20002,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626290</v>
+        <v>626582</v>
       </c>
       <c r="R187" t="n">
-        <v>7217851</v>
+        <v>7217455</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20185,32 +20185,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103859</v>
+        <v>128103759</v>
       </c>
       <c r="B189" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626133</v>
+        <v>626350</v>
       </c>
       <c r="R189" t="n">
-        <v>7217998</v>
+        <v>7217852</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103784</v>
+        <v>128103836</v>
       </c>
       <c r="B97" t="n">
-        <v>57789</v>
+        <v>91007</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>900</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626608</v>
+        <v>626328</v>
       </c>
       <c r="R97" t="n">
-        <v>7217437</v>
+        <v>7217861</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11242,10 +11242,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B98" t="n">
-        <v>91007</v>
+        <v>78841</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11253,21 +11253,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R98" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,6 +11321,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11339,32 +11340,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103745</v>
+        <v>128103784</v>
       </c>
       <c r="B99" t="n">
-        <v>78841</v>
+        <v>57789</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11374,10 +11375,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626149</v>
+        <v>626608</v>
       </c>
       <c r="R99" t="n">
-        <v>7217977</v>
+        <v>7217437</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11418,7 +11419,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103701</v>
+        <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626222</v>
+        <v>626593</v>
       </c>
       <c r="R100" t="n">
-        <v>7218014</v>
+        <v>7217442</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11508,6 +11508,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11534,32 +11539,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103728</v>
+        <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11574,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626453</v>
+        <v>626239</v>
       </c>
       <c r="R101" t="n">
-        <v>7217719</v>
+        <v>7218007</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11631,32 +11636,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103850</v>
+        <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11671,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626593</v>
+        <v>626453</v>
       </c>
       <c r="R102" t="n">
-        <v>7217442</v>
+        <v>7217719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,11 +11707,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11733,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103757</v>
+        <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>80188</v>
+        <v>91452</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11744,21 +11744,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11768,10 +11768,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626239</v>
+        <v>626222</v>
       </c>
       <c r="R103" t="n">
-        <v>7218007</v>
+        <v>7218014</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11830,32 +11830,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103812</v>
+        <v>128103703</v>
       </c>
       <c r="B104" t="n">
-        <v>98571</v>
+        <v>91452</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626319</v>
+        <v>626128</v>
       </c>
       <c r="R104" t="n">
-        <v>7217868</v>
+        <v>7218027</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11927,7 +11927,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103806</v>
+        <v>128103812</v>
       </c>
       <c r="B105" t="n">
         <v>98571</v>
@@ -11962,10 +11962,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626574</v>
+        <v>626319</v>
       </c>
       <c r="R105" t="n">
-        <v>7217449</v>
+        <v>7217868</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12024,53 +12024,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103719</v>
+        <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626269</v>
+        <v>626574</v>
       </c>
       <c r="R106" t="n">
-        <v>7217921</v>
+        <v>7217449</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12103,11 +12095,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12134,10 +12121,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128103703</v>
+        <v>128103719</v>
       </c>
       <c r="B107" t="n">
-        <v>91452</v>
+        <v>57685</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12145,34 +12132,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>626128</v>
+        <v>626269</v>
       </c>
       <c r="R107" t="n">
-        <v>7218027</v>
+        <v>7217921</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12205,6 +12200,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12231,32 +12231,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128103794</v>
+        <v>128103826</v>
       </c>
       <c r="B108" t="n">
-        <v>78840</v>
+        <v>98571</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>626239</v>
+        <v>626206</v>
       </c>
       <c r="R108" t="n">
-        <v>7217951</v>
+        <v>7218045</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12328,32 +12328,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128103830</v>
+        <v>128103794</v>
       </c>
       <c r="B109" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>626295</v>
+        <v>626239</v>
       </c>
       <c r="R109" t="n">
-        <v>7217850</v>
+        <v>7217951</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12425,7 +12425,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128103826</v>
+        <v>128103830</v>
       </c>
       <c r="B110" t="n">
         <v>98571</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>626206</v>
+        <v>626295</v>
       </c>
       <c r="R110" t="n">
-        <v>7218045</v>
+        <v>7217850</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103765</v>
+        <v>128103716</v>
       </c>
       <c r="B111" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,34 +12533,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R111" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12593,6 +12601,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12619,10 +12632,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103870</v>
+        <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78055</v>
+        <v>78841</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12630,21 +12643,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12654,10 +12667,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626270</v>
+        <v>626454</v>
       </c>
       <c r="R112" t="n">
-        <v>7217834</v>
+        <v>7217736</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12698,6 +12711,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12716,10 +12730,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103754</v>
+        <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>80188</v>
+        <v>78055</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12727,21 +12741,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12751,10 +12765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626325</v>
+        <v>626270</v>
       </c>
       <c r="R113" t="n">
-        <v>7217934</v>
+        <v>7217834</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12813,10 +12827,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103716</v>
+        <v>128103754</v>
       </c>
       <c r="B114" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12824,42 +12838,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626454</v>
+        <v>626325</v>
       </c>
       <c r="R114" t="n">
-        <v>7217736</v>
+        <v>7217934</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12892,11 +12898,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12923,10 +12924,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103744</v>
+        <v>128103765</v>
       </c>
       <c r="B115" t="n">
-        <v>78841</v>
+        <v>80188</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12934,21 +12935,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12958,10 +12959,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626454</v>
+        <v>626320</v>
       </c>
       <c r="R115" t="n">
-        <v>7217736</v>
+        <v>7217923</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13002,7 +13003,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13118,32 +13118,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103831</v>
+        <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>98571</v>
+        <v>80223</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626373</v>
+        <v>626282</v>
       </c>
       <c r="R117" t="n">
-        <v>7217883</v>
+        <v>7217980</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13215,32 +13215,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103828</v>
+        <v>128103871</v>
       </c>
       <c r="B118" t="n">
-        <v>98571</v>
+        <v>92736</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13250,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626202</v>
+        <v>626144</v>
       </c>
       <c r="R118" t="n">
-        <v>7217956</v>
+        <v>7217996</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13312,10 +13312,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103871</v>
+        <v>128103717</v>
       </c>
       <c r="B119" t="n">
-        <v>92736</v>
+        <v>57685</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13323,34 +13323,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626144</v>
+        <v>626217</v>
       </c>
       <c r="R119" t="n">
-        <v>7217996</v>
+        <v>7217965</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13383,6 +13391,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13409,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103866</v>
+        <v>128103831</v>
       </c>
       <c r="B120" t="n">
-        <v>80223</v>
+        <v>98571</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13444,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626282</v>
+        <v>626373</v>
       </c>
       <c r="R120" t="n">
-        <v>7217980</v>
+        <v>7217883</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13506,53 +13519,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103717</v>
+        <v>128103828</v>
       </c>
       <c r="B121" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626217</v>
+        <v>626202</v>
       </c>
       <c r="R121" t="n">
-        <v>7217965</v>
+        <v>7217956</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13585,11 +13590,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13713,32 +13713,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103740</v>
+        <v>128103782</v>
       </c>
       <c r="B123" t="n">
-        <v>91748</v>
+        <v>80224</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626128</v>
+        <v>626380</v>
       </c>
       <c r="R123" t="n">
-        <v>7218027</v>
+        <v>7217892</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13810,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103721</v>
+        <v>128103756</v>
       </c>
       <c r="B124" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,42 +13821,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626306</v>
+        <v>626277</v>
       </c>
       <c r="R124" t="n">
-        <v>7217910</v>
+        <v>7217976</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,11 +13881,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13920,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103746</v>
+        <v>128103772</v>
       </c>
       <c r="B125" t="n">
-        <v>78841</v>
+        <v>80188</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13931,21 +13918,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13955,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626290</v>
+        <v>626347</v>
       </c>
       <c r="R125" t="n">
-        <v>7217851</v>
+        <v>7217886</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13999,7 +13986,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14018,10 +14004,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103756</v>
+        <v>128103842</v>
       </c>
       <c r="B126" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14029,21 +14015,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14053,10 +14039,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626277</v>
+        <v>626317</v>
       </c>
       <c r="R126" t="n">
-        <v>7217976</v>
+        <v>7217935</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14115,10 +14101,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103772</v>
+        <v>128103740</v>
       </c>
       <c r="B127" t="n">
-        <v>80188</v>
+        <v>91748</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14126,21 +14112,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14150,10 +14136,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626347</v>
+        <v>626128</v>
       </c>
       <c r="R127" t="n">
-        <v>7217886</v>
+        <v>7218027</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14212,45 +14198,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103782</v>
+        <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>80224</v>
+        <v>57685</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626380</v>
+        <v>626306</v>
       </c>
       <c r="R128" t="n">
-        <v>7217892</v>
+        <v>7217910</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14283,6 +14277,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14309,32 +14308,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103842</v>
+        <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14344,10 +14343,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626317</v>
+        <v>626300</v>
       </c>
       <c r="R129" t="n">
-        <v>7217935</v>
+        <v>7217895</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14406,32 +14405,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103824</v>
+        <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>98571</v>
+        <v>78841</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14441,10 +14440,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626300</v>
+        <v>626290</v>
       </c>
       <c r="R130" t="n">
-        <v>7217895</v>
+        <v>7217851</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14485,6 +14484,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14503,7 +14503,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103811</v>
+        <v>128103827</v>
       </c>
       <c r="B131" t="n">
         <v>98571</v>
@@ -14538,10 +14538,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626311</v>
+        <v>626128</v>
       </c>
       <c r="R131" t="n">
-        <v>7217865</v>
+        <v>7218027</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14600,32 +14600,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103827</v>
+        <v>128103781</v>
       </c>
       <c r="B132" t="n">
-        <v>98571</v>
+        <v>80224</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626128</v>
+        <v>626239</v>
       </c>
       <c r="R132" t="n">
-        <v>7218027</v>
+        <v>7218007</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14697,48 +14697,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103787</v>
+        <v>128103867</v>
       </c>
       <c r="B133" t="n">
-        <v>91824</v>
+        <v>80223</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1505</v>
+        <v>6463</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626280</v>
+        <v>626346</v>
       </c>
       <c r="R133" t="n">
-        <v>7217822</v>
+        <v>7217883</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14779,7 +14776,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14798,45 +14794,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103696</v>
+        <v>128103787</v>
       </c>
       <c r="B134" t="n">
-        <v>91737</v>
+        <v>91824</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>71</v>
+        <v>1505</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626167</v>
+        <v>626280</v>
       </c>
       <c r="R134" t="n">
-        <v>7217957</v>
+        <v>7217822</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14877,6 +14876,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14895,32 +14895,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103781</v>
+        <v>128103696</v>
       </c>
       <c r="B135" t="n">
-        <v>80224</v>
+        <v>91737</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6464</v>
+        <v>71</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14930,10 +14930,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626239</v>
+        <v>626167</v>
       </c>
       <c r="R135" t="n">
-        <v>7218007</v>
+        <v>7217957</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14992,45 +14992,53 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103867</v>
+        <v>128103856</v>
       </c>
       <c r="B136" t="n">
-        <v>80223</v>
+        <v>57685</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626346</v>
+        <v>626323</v>
       </c>
       <c r="R136" t="n">
-        <v>7217883</v>
+        <v>7217908</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15063,6 +15071,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15089,53 +15102,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103856</v>
+        <v>128103811</v>
       </c>
       <c r="B137" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626323</v>
+        <v>626311</v>
       </c>
       <c r="R137" t="n">
-        <v>7217908</v>
+        <v>7217865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15168,11 +15173,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15199,32 +15199,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103837</v>
+        <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626194</v>
+        <v>626290</v>
       </c>
       <c r="R138" t="n">
-        <v>7218055</v>
+        <v>7217851</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103810</v>
+        <v>128103773</v>
       </c>
       <c r="B139" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626290</v>
+        <v>626370</v>
       </c>
       <c r="R139" t="n">
-        <v>7217851</v>
+        <v>7217900</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103773</v>
+        <v>128103769</v>
       </c>
       <c r="B140" t="n">
         <v>80188</v>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626370</v>
+        <v>626248</v>
       </c>
       <c r="R140" t="n">
-        <v>7217900</v>
+        <v>7218007</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,10 +15490,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103769</v>
+        <v>128103835</v>
       </c>
       <c r="B141" t="n">
-        <v>80188</v>
+        <v>91007</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15501,21 +15501,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>900</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626248</v>
+        <v>626354</v>
       </c>
       <c r="R141" t="n">
-        <v>7218007</v>
+        <v>7217769</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103835</v>
+        <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>91007</v>
+        <v>105609</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>900</v>
+        <v>221144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626354</v>
+        <v>626194</v>
       </c>
       <c r="R142" t="n">
-        <v>7217769</v>
+        <v>7218055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103857</v>
+        <v>128103843</v>
       </c>
       <c r="B143" t="n">
-        <v>91713</v>
+        <v>79083</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626178</v>
+        <v>626276</v>
       </c>
       <c r="R143" t="n">
-        <v>7217957</v>
+        <v>7217891</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,32 +15781,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103743</v>
+        <v>128103863</v>
       </c>
       <c r="B144" t="n">
-        <v>92734</v>
+        <v>80223</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626130</v>
+        <v>626248</v>
       </c>
       <c r="R144" t="n">
-        <v>7218000</v>
+        <v>7218007</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,32 +15878,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103843</v>
+        <v>128103857</v>
       </c>
       <c r="B145" t="n">
-        <v>79083</v>
+        <v>91713</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626276</v>
+        <v>626178</v>
       </c>
       <c r="R145" t="n">
-        <v>7217891</v>
+        <v>7217957</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15975,32 +15975,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103863</v>
+        <v>128103743</v>
       </c>
       <c r="B146" t="n">
-        <v>80223</v>
+        <v>92734</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>4361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626248</v>
+        <v>626130</v>
       </c>
       <c r="R146" t="n">
-        <v>7218007</v>
+        <v>7218000</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16266,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103704</v>
+        <v>128103839</v>
       </c>
       <c r="B149" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16277,21 +16277,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626182</v>
+        <v>626215</v>
       </c>
       <c r="R149" t="n">
-        <v>7218029</v>
+        <v>7218028</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,10 +16363,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103839</v>
+        <v>128103735</v>
       </c>
       <c r="B150" t="n">
-        <v>91470</v>
+        <v>57682</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16374,34 +16374,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626215</v>
+        <v>626159</v>
       </c>
       <c r="R150" t="n">
-        <v>7218028</v>
+        <v>7217940</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16434,6 +16442,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16460,10 +16473,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103735</v>
+        <v>128103704</v>
       </c>
       <c r="B151" t="n">
-        <v>57682</v>
+        <v>91452</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,42 +16484,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626159</v>
+        <v>626182</v>
       </c>
       <c r="R151" t="n">
-        <v>7217940</v>
+        <v>7218029</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16539,11 +16544,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16861,32 +16861,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128103737</v>
+        <v>128103694</v>
       </c>
       <c r="B155" t="n">
-        <v>92746</v>
+        <v>79702</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626278</v>
+        <v>626150</v>
       </c>
       <c r="R155" t="n">
-        <v>7217843</v>
+        <v>7217973</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103694</v>
+        <v>128103737</v>
       </c>
       <c r="B156" t="n">
-        <v>79702</v>
+        <v>92746</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626150</v>
+        <v>626278</v>
       </c>
       <c r="R156" t="n">
-        <v>7217973</v>
+        <v>7217843</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17249,10 +17249,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103774</v>
+        <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17260,21 +17260,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626377</v>
+        <v>626264</v>
       </c>
       <c r="R159" t="n">
-        <v>7217880</v>
+        <v>7217994</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17443,10 +17443,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103851</v>
+        <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17454,21 +17454,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626264</v>
+        <v>626377</v>
       </c>
       <c r="R161" t="n">
-        <v>7217994</v>
+        <v>7217880</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17734,10 +17734,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103783</v>
+        <v>128103823</v>
       </c>
       <c r="B164" t="n">
-        <v>91835</v>
+        <v>98571</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17745,21 +17745,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>298</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626271</v>
+        <v>626337</v>
       </c>
       <c r="R164" t="n">
-        <v>7217852</v>
+        <v>7217840</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,32 +17831,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103786</v>
+        <v>128103813</v>
       </c>
       <c r="B165" t="n">
-        <v>91925</v>
+        <v>98571</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626319</v>
+        <v>626370</v>
       </c>
       <c r="R165" t="n">
-        <v>7217868</v>
+        <v>7217900</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18135,32 +18135,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103823</v>
+        <v>128103786</v>
       </c>
       <c r="B168" t="n">
-        <v>98571</v>
+        <v>91925</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18170,10 +18170,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626337</v>
+        <v>626319</v>
       </c>
       <c r="R168" t="n">
-        <v>7217840</v>
+        <v>7217868</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18232,10 +18232,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103813</v>
+        <v>128103783</v>
       </c>
       <c r="B169" t="n">
-        <v>98571</v>
+        <v>91835</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18243,21 +18243,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626370</v>
+        <v>626271</v>
       </c>
       <c r="R169" t="n">
-        <v>7217900</v>
+        <v>7217852</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18523,32 +18523,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103852</v>
+        <v>128103825</v>
       </c>
       <c r="B172" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626320</v>
+        <v>626215</v>
       </c>
       <c r="R172" t="n">
-        <v>7217901</v>
+        <v>7218004</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,7 +18620,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103792</v>
+        <v>128103793</v>
       </c>
       <c r="B173" t="n">
         <v>78840</v>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626297</v>
+        <v>626317</v>
       </c>
       <c r="R173" t="n">
-        <v>7217856</v>
+        <v>7217867</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18814,10 +18814,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103793</v>
+        <v>128103852</v>
       </c>
       <c r="B175" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18825,21 +18825,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626317</v>
+        <v>626320</v>
       </c>
       <c r="R175" t="n">
-        <v>7217867</v>
+        <v>7217901</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18911,32 +18911,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103825</v>
+        <v>128103792</v>
       </c>
       <c r="B176" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626215</v>
+        <v>626297</v>
       </c>
       <c r="R176" t="n">
-        <v>7218004</v>
+        <v>7217856</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19202,32 +19202,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103845</v>
+        <v>128103727</v>
       </c>
       <c r="B179" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19237,10 +19237,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626363</v>
+        <v>626546</v>
       </c>
       <c r="R179" t="n">
-        <v>7217905</v>
+        <v>7217566</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19299,32 +19299,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103727</v>
+        <v>128103845</v>
       </c>
       <c r="B180" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626546</v>
+        <v>626363</v>
       </c>
       <c r="R180" t="n">
-        <v>7217566</v>
+        <v>7217905</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103859</v>
+        <v>128103759</v>
       </c>
       <c r="B183" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626133</v>
+        <v>626350</v>
       </c>
       <c r="R183" t="n">
-        <v>7217998</v>
+        <v>7217852</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103791</v>
+        <v>128103695</v>
       </c>
       <c r="B184" t="n">
-        <v>78840</v>
+        <v>79702</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19797,10 +19797,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103695</v>
+        <v>128103761</v>
       </c>
       <c r="B185" t="n">
-        <v>79702</v>
+        <v>80188</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19808,21 +19808,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626290</v>
+        <v>626398</v>
       </c>
       <c r="R185" t="n">
-        <v>7217851</v>
+        <v>7217759</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103761</v>
+        <v>128103791</v>
       </c>
       <c r="B186" t="n">
-        <v>80188</v>
+        <v>78840</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626398</v>
+        <v>626290</v>
       </c>
       <c r="R186" t="n">
-        <v>7217759</v>
+        <v>7217851</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20088,32 +20088,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103700</v>
+        <v>128103859</v>
       </c>
       <c r="B188" t="n">
-        <v>91737</v>
+        <v>92742</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626271</v>
+        <v>626133</v>
       </c>
       <c r="R188" t="n">
-        <v>7217852</v>
+        <v>7217998</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20185,32 +20185,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103759</v>
+        <v>128103700</v>
       </c>
       <c r="B189" t="n">
-        <v>80188</v>
+        <v>91737</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6458</v>
+        <v>71</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626350</v>
+        <v>626271</v>
       </c>
       <c r="R189" t="n">
         <v>7217852</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103745</v>
+        <v>128103784</v>
       </c>
       <c r="B98" t="n">
-        <v>78841</v>
+        <v>57789</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626149</v>
+        <v>626608</v>
       </c>
       <c r="R98" t="n">
-        <v>7217977</v>
+        <v>7217437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,7 +11321,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11340,32 +11339,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103784</v>
+        <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>57789</v>
+        <v>78841</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11375,10 +11374,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626608</v>
+        <v>626149</v>
       </c>
       <c r="R99" t="n">
-        <v>7217437</v>
+        <v>7217977</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11419,6 +11418,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103850</v>
+        <v>128103701</v>
       </c>
       <c r="B100" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626593</v>
+        <v>626222</v>
       </c>
       <c r="R100" t="n">
-        <v>7217442</v>
+        <v>7218014</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11508,11 +11508,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11539,10 +11534,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103757</v>
+        <v>128103850</v>
       </c>
       <c r="B101" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11550,21 +11545,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11574,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626239</v>
+        <v>626593</v>
       </c>
       <c r="R101" t="n">
-        <v>7218007</v>
+        <v>7217442</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11610,6 +11605,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11636,32 +11636,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103728</v>
+        <v>128103757</v>
       </c>
       <c r="B102" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626453</v>
+        <v>626239</v>
       </c>
       <c r="R102" t="n">
-        <v>7217719</v>
+        <v>7218007</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11733,32 +11733,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103701</v>
+        <v>128103728</v>
       </c>
       <c r="B103" t="n">
-        <v>91452</v>
+        <v>80217</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11768,10 +11768,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626222</v>
+        <v>626453</v>
       </c>
       <c r="R103" t="n">
-        <v>7218014</v>
+        <v>7217719</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12231,7 +12231,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128103826</v>
+        <v>128103830</v>
       </c>
       <c r="B108" t="n">
         <v>98571</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>626206</v>
+        <v>626295</v>
       </c>
       <c r="R108" t="n">
-        <v>7218045</v>
+        <v>7217850</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12328,32 +12328,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128103794</v>
+        <v>128103826</v>
       </c>
       <c r="B109" t="n">
-        <v>78840</v>
+        <v>98571</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>626239</v>
+        <v>626206</v>
       </c>
       <c r="R109" t="n">
-        <v>7217951</v>
+        <v>7218045</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12425,32 +12425,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128103830</v>
+        <v>128103794</v>
       </c>
       <c r="B110" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>626295</v>
+        <v>626239</v>
       </c>
       <c r="R110" t="n">
-        <v>7217850</v>
+        <v>7217951</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13422,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103831</v>
+        <v>128103733</v>
       </c>
       <c r="B120" t="n">
-        <v>98571</v>
+        <v>98592</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626373</v>
+        <v>626571</v>
       </c>
       <c r="R120" t="n">
-        <v>7217883</v>
+        <v>7217492</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,7 +13519,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103828</v>
+        <v>128103831</v>
       </c>
       <c r="B121" t="n">
         <v>98571</v>
@@ -13554,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626202</v>
+        <v>626373</v>
       </c>
       <c r="R121" t="n">
-        <v>7217956</v>
+        <v>7217883</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13616,32 +13616,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103733</v>
+        <v>128103828</v>
       </c>
       <c r="B122" t="n">
-        <v>98592</v>
+        <v>98571</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13651,10 +13651,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626571</v>
+        <v>626202</v>
       </c>
       <c r="R122" t="n">
-        <v>7217492</v>
+        <v>7217956</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13713,32 +13713,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103782</v>
+        <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>80224</v>
+        <v>91748</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>626380</v>
+        <v>626128</v>
       </c>
       <c r="R123" t="n">
-        <v>7217892</v>
+        <v>7218027</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13810,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103756</v>
+        <v>128103721</v>
       </c>
       <c r="B124" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,34 +13821,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626277</v>
+        <v>626306</v>
       </c>
       <c r="R124" t="n">
-        <v>7217976</v>
+        <v>7217910</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,6 +13889,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13907,32 +13920,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103772</v>
+        <v>128103824</v>
       </c>
       <c r="B125" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13955,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626347</v>
+        <v>626300</v>
       </c>
       <c r="R125" t="n">
-        <v>7217886</v>
+        <v>7217895</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14004,32 +14017,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103842</v>
+        <v>128103782</v>
       </c>
       <c r="B126" t="n">
-        <v>79083</v>
+        <v>80224</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14039,10 +14052,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626317</v>
+        <v>626380</v>
       </c>
       <c r="R126" t="n">
-        <v>7217935</v>
+        <v>7217892</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14101,10 +14114,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103740</v>
+        <v>128103756</v>
       </c>
       <c r="B127" t="n">
-        <v>91748</v>
+        <v>80188</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14112,21 +14125,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14136,10 +14149,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626128</v>
+        <v>626277</v>
       </c>
       <c r="R127" t="n">
-        <v>7218027</v>
+        <v>7217976</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14198,10 +14211,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103721</v>
+        <v>128103772</v>
       </c>
       <c r="B128" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14209,42 +14222,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626306</v>
+        <v>626347</v>
       </c>
       <c r="R128" t="n">
-        <v>7217910</v>
+        <v>7217886</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14277,11 +14282,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14308,32 +14308,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103824</v>
+        <v>128103842</v>
       </c>
       <c r="B129" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14343,10 +14343,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626300</v>
+        <v>626317</v>
       </c>
       <c r="R129" t="n">
-        <v>7217895</v>
+        <v>7217935</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16266,32 +16266,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103839</v>
+        <v>128103829</v>
       </c>
       <c r="B149" t="n">
-        <v>91470</v>
+        <v>98571</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626215</v>
+        <v>626217</v>
       </c>
       <c r="R149" t="n">
-        <v>7218028</v>
+        <v>7217956</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,53 +16363,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103735</v>
+        <v>128103807</v>
       </c>
       <c r="B150" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626159</v>
+        <v>626532</v>
       </c>
       <c r="R150" t="n">
-        <v>7217940</v>
+        <v>7217568</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16442,11 +16434,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16473,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103704</v>
+        <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>91452</v>
+        <v>57682</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16484,34 +16471,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626182</v>
+        <v>626159</v>
       </c>
       <c r="R151" t="n">
-        <v>7218029</v>
+        <v>7217940</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16544,6 +16539,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16570,32 +16570,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103829</v>
+        <v>128103839</v>
       </c>
       <c r="B152" t="n">
-        <v>98571</v>
+        <v>91470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626217</v>
+        <v>626215</v>
       </c>
       <c r="R152" t="n">
-        <v>7217956</v>
+        <v>7218028</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16667,32 +16667,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103807</v>
+        <v>128103704</v>
       </c>
       <c r="B153" t="n">
-        <v>98571</v>
+        <v>91452</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626532</v>
+        <v>626182</v>
       </c>
       <c r="R153" t="n">
-        <v>7217568</v>
+        <v>7218029</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B157" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R157" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B158" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R158" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17734,32 +17734,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103823</v>
+        <v>128103766</v>
       </c>
       <c r="B164" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626337</v>
+        <v>626308</v>
       </c>
       <c r="R164" t="n">
-        <v>7217840</v>
+        <v>7217938</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,32 +17831,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103813</v>
+        <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>98571</v>
+        <v>91925</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626370</v>
+        <v>626319</v>
       </c>
       <c r="R165" t="n">
-        <v>7217900</v>
+        <v>7217868</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,32 +17928,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103766</v>
+        <v>128103823</v>
       </c>
       <c r="B166" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626308</v>
+        <v>626337</v>
       </c>
       <c r="R166" t="n">
-        <v>7217938</v>
+        <v>7217840</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18025,53 +18025,45 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103736</v>
+        <v>128103813</v>
       </c>
       <c r="B167" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626194</v>
+        <v>626370</v>
       </c>
       <c r="R167" t="n">
-        <v>7217951</v>
+        <v>7217900</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18104,11 +18096,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18135,10 +18122,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103786</v>
+        <v>128103736</v>
       </c>
       <c r="B168" t="n">
-        <v>91925</v>
+        <v>57682</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18146,34 +18133,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626319</v>
+        <v>626194</v>
       </c>
       <c r="R168" t="n">
-        <v>7217868</v>
+        <v>7217951</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18206,6 +18201,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19991,32 +19991,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103739</v>
+        <v>128103859</v>
       </c>
       <c r="B187" t="n">
-        <v>80189</v>
+        <v>92742</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626582</v>
+        <v>626133</v>
       </c>
       <c r="R187" t="n">
-        <v>7217455</v>
+        <v>7217998</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,32 +20088,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103859</v>
+        <v>128103739</v>
       </c>
       <c r="B188" t="n">
-        <v>92742</v>
+        <v>80189</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626133</v>
+        <v>626582</v>
       </c>
       <c r="R188" t="n">
-        <v>7217998</v>
+        <v>7217455</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103836</v>
+        <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>91007</v>
+        <v>57793</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>900</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626328</v>
+        <v>626608</v>
       </c>
       <c r="R97" t="n">
-        <v>7217861</v>
+        <v>7217437</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103784</v>
+        <v>128103745</v>
       </c>
       <c r="B98" t="n">
-        <v>57789</v>
+        <v>78845</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626608</v>
+        <v>626149</v>
       </c>
       <c r="R98" t="n">
-        <v>7217437</v>
+        <v>7217977</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,6 +11321,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11339,10 +11340,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103745</v>
+        <v>128103836</v>
       </c>
       <c r="B99" t="n">
-        <v>78841</v>
+        <v>91019</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,21 +11351,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>900</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11374,10 +11375,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626149</v>
+        <v>626328</v>
       </c>
       <c r="R99" t="n">
-        <v>7217977</v>
+        <v>7217861</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11418,7 +11419,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103701</v>
+        <v>128103757</v>
       </c>
       <c r="B100" t="n">
-        <v>91452</v>
+        <v>80192</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626222</v>
+        <v>626239</v>
       </c>
       <c r="R100" t="n">
-        <v>7218014</v>
+        <v>7218007</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11534,32 +11534,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103850</v>
+        <v>128103728</v>
       </c>
       <c r="B101" t="n">
-        <v>79083</v>
+        <v>80221</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626593</v>
+        <v>626453</v>
       </c>
       <c r="R101" t="n">
-        <v>7217442</v>
+        <v>7217719</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11605,11 +11605,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11636,10 +11631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103757</v>
+        <v>128103701</v>
       </c>
       <c r="B102" t="n">
-        <v>80188</v>
+        <v>91464</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11647,21 +11642,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11671,10 +11666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626239</v>
+        <v>626222</v>
       </c>
       <c r="R102" t="n">
-        <v>7218007</v>
+        <v>7218014</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11733,32 +11728,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103728</v>
+        <v>128103850</v>
       </c>
       <c r="B103" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11768,10 +11763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626453</v>
+        <v>626593</v>
       </c>
       <c r="R103" t="n">
-        <v>7217719</v>
+        <v>7217442</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11804,6 +11799,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11830,10 +11830,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103703</v>
+        <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>91452</v>
+        <v>57689</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11841,34 +11841,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626128</v>
+        <v>626269</v>
       </c>
       <c r="R104" t="n">
-        <v>7218027</v>
+        <v>7217921</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11901,6 +11909,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11927,32 +11940,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103812</v>
+        <v>128103703</v>
       </c>
       <c r="B105" t="n">
-        <v>98571</v>
+        <v>91464</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11962,10 +11975,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626319</v>
+        <v>626128</v>
       </c>
       <c r="R105" t="n">
-        <v>7217868</v>
+        <v>7218027</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12024,10 +12037,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103806</v>
+        <v>128103812</v>
       </c>
       <c r="B106" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12059,10 +12072,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626574</v>
+        <v>626319</v>
       </c>
       <c r="R106" t="n">
-        <v>7217449</v>
+        <v>7217868</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12121,53 +12134,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128103719</v>
+        <v>128103806</v>
       </c>
       <c r="B107" t="n">
-        <v>57685</v>
+        <v>98585</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>626269</v>
+        <v>626574</v>
       </c>
       <c r="R107" t="n">
-        <v>7217921</v>
+        <v>7217449</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12200,11 +12205,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12234,7 +12234,7 @@
         <v>128103830</v>
       </c>
       <c r="B108" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>128103826</v>
       </c>
       <c r="B109" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>128103794</v>
       </c>
       <c r="B110" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103716</v>
+        <v>128103870</v>
       </c>
       <c r="B111" t="n">
-        <v>57685</v>
+        <v>78059</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,42 +12533,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626454</v>
+        <v>626270</v>
       </c>
       <c r="R111" t="n">
-        <v>7217736</v>
+        <v>7217834</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12601,11 +12593,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12632,10 +12619,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103744</v>
+        <v>128103754</v>
       </c>
       <c r="B112" t="n">
-        <v>78841</v>
+        <v>80192</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12643,21 +12630,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12667,10 +12654,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626454</v>
+        <v>626325</v>
       </c>
       <c r="R112" t="n">
-        <v>7217736</v>
+        <v>7217934</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12711,7 +12698,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12730,10 +12716,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103870</v>
+        <v>128103765</v>
       </c>
       <c r="B113" t="n">
-        <v>78055</v>
+        <v>80192</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12741,21 +12727,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12765,10 +12751,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626270</v>
+        <v>626320</v>
       </c>
       <c r="R113" t="n">
-        <v>7217834</v>
+        <v>7217923</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12827,10 +12813,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103754</v>
+        <v>128103716</v>
       </c>
       <c r="B114" t="n">
-        <v>80188</v>
+        <v>57689</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12838,34 +12824,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626325</v>
+        <v>626454</v>
       </c>
       <c r="R114" t="n">
-        <v>7217934</v>
+        <v>7217736</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12898,6 +12892,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12924,10 +12923,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103765</v>
+        <v>128103744</v>
       </c>
       <c r="B115" t="n">
-        <v>80188</v>
+        <v>78845</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12935,21 +12934,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12959,10 +12958,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R115" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13003,6 +13002,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13021,10 +13021,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103853</v>
+        <v>128103871</v>
       </c>
       <c r="B116" t="n">
-        <v>79083</v>
+        <v>92748</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13032,21 +13032,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626328</v>
+        <v>626144</v>
       </c>
       <c r="R116" t="n">
-        <v>7217861</v>
+        <v>7217996</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,27 +13118,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103866</v>
+        <v>128103853</v>
       </c>
       <c r="B117" t="n">
-        <v>80223</v>
+        <v>79087</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626282</v>
+        <v>626328</v>
       </c>
       <c r="R117" t="n">
-        <v>7217980</v>
+        <v>7217861</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13215,32 +13215,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103871</v>
+        <v>128103831</v>
       </c>
       <c r="B118" t="n">
-        <v>92736</v>
+        <v>98585</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13250,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626144</v>
+        <v>626373</v>
       </c>
       <c r="R118" t="n">
-        <v>7217996</v>
+        <v>7217883</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13312,53 +13312,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103717</v>
+        <v>128103828</v>
       </c>
       <c r="B119" t="n">
-        <v>57685</v>
+        <v>98585</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626217</v>
+        <v>626202</v>
       </c>
       <c r="R119" t="n">
-        <v>7217965</v>
+        <v>7217956</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13391,11 +13383,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13425,7 +13412,7 @@
         <v>128103733</v>
       </c>
       <c r="B120" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13519,32 +13506,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103831</v>
+        <v>128103866</v>
       </c>
       <c r="B121" t="n">
-        <v>98571</v>
+        <v>80227</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13554,10 +13541,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626373</v>
+        <v>626282</v>
       </c>
       <c r="R121" t="n">
-        <v>7217883</v>
+        <v>7217980</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13616,45 +13603,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103828</v>
+        <v>128103717</v>
       </c>
       <c r="B122" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626202</v>
+        <v>626217</v>
       </c>
       <c r="R122" t="n">
-        <v>7217956</v>
+        <v>7217965</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13687,6 +13682,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13716,7 +13716,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13810,10 +13810,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103721</v>
+        <v>128103842</v>
       </c>
       <c r="B124" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13821,42 +13821,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626306</v>
+        <v>626317</v>
       </c>
       <c r="R124" t="n">
-        <v>7217910</v>
+        <v>7217935</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,11 +13881,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13920,32 +13907,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103824</v>
+        <v>128103782</v>
       </c>
       <c r="B125" t="n">
-        <v>98571</v>
+        <v>80228</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13955,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626300</v>
+        <v>626380</v>
       </c>
       <c r="R125" t="n">
-        <v>7217895</v>
+        <v>7217892</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14017,32 +14004,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103782</v>
+        <v>128103756</v>
       </c>
       <c r="B126" t="n">
-        <v>80224</v>
+        <v>80192</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14052,10 +14039,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626380</v>
+        <v>626277</v>
       </c>
       <c r="R126" t="n">
-        <v>7217892</v>
+        <v>7217976</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14114,10 +14101,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103756</v>
+        <v>128103772</v>
       </c>
       <c r="B127" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14149,10 +14136,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626277</v>
+        <v>626347</v>
       </c>
       <c r="R127" t="n">
-        <v>7217976</v>
+        <v>7217886</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14211,10 +14198,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103772</v>
+        <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>80188</v>
+        <v>57689</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14222,34 +14209,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626347</v>
+        <v>626306</v>
       </c>
       <c r="R128" t="n">
-        <v>7217886</v>
+        <v>7217910</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14282,6 +14277,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14308,32 +14308,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103842</v>
+        <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>79083</v>
+        <v>98585</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14343,10 +14343,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626317</v>
+        <v>626300</v>
       </c>
       <c r="R129" t="n">
-        <v>7217935</v>
+        <v>7217895</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14408,7 +14408,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14503,10 +14503,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103827</v>
+        <v>128103787</v>
       </c>
       <c r="B131" t="n">
-        <v>98571</v>
+        <v>91836</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14514,34 +14514,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626128</v>
+        <v>626280</v>
       </c>
       <c r="R131" t="n">
-        <v>7218027</v>
+        <v>7217822</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14582,6 +14585,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14603,7 +14607,7 @@
         <v>128103781</v>
       </c>
       <c r="B132" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14700,7 +14704,7 @@
         <v>128103867</v>
       </c>
       <c r="B133" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14794,48 +14798,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103787</v>
+        <v>128103696</v>
       </c>
       <c r="B134" t="n">
-        <v>91824</v>
+        <v>91749</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1505</v>
+        <v>71</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626280</v>
+        <v>626167</v>
       </c>
       <c r="R134" t="n">
-        <v>7217822</v>
+        <v>7217957</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,7 +14877,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14895,45 +14895,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103696</v>
+        <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>91737</v>
+        <v>57689</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>71</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626167</v>
+        <v>626323</v>
       </c>
       <c r="R135" t="n">
-        <v>7217957</v>
+        <v>7217908</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14966,6 +14974,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14992,53 +15005,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103856</v>
+        <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>57685</v>
+        <v>98585</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626323</v>
+        <v>626311</v>
       </c>
       <c r="R136" t="n">
-        <v>7217908</v>
+        <v>7217865</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15071,11 +15076,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15102,10 +15102,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103811</v>
+        <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626311</v>
+        <v>626128</v>
       </c>
       <c r="R137" t="n">
-        <v>7217865</v>
+        <v>7218027</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15199,32 +15199,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103810</v>
+        <v>128103835</v>
       </c>
       <c r="B138" t="n">
-        <v>98571</v>
+        <v>91019</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>900</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626290</v>
+        <v>626354</v>
       </c>
       <c r="R138" t="n">
-        <v>7217851</v>
+        <v>7217769</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15299,7 +15299,7 @@
         <v>128103773</v>
       </c>
       <c r="B139" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>128103769</v>
       </c>
       <c r="B140" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103835</v>
+        <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>91007</v>
+        <v>98585</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>900</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626354</v>
+        <v>626290</v>
       </c>
       <c r="R141" t="n">
-        <v>7217769</v>
+        <v>7217851</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15590,7 +15590,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105609</v>
+        <v>105630</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15684,32 +15684,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128103843</v>
+        <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>79083</v>
+        <v>91725</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15719,10 +15719,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>626276</v>
+        <v>626178</v>
       </c>
       <c r="R143" t="n">
-        <v>7217891</v>
+        <v>7217957</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15781,32 +15781,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128103863</v>
+        <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>80223</v>
+        <v>92746</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>4361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>626248</v>
+        <v>626130</v>
       </c>
       <c r="R144" t="n">
-        <v>7218007</v>
+        <v>7218000</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,32 +15878,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128103857</v>
+        <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>91713</v>
+        <v>79087</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>626178</v>
+        <v>626276</v>
       </c>
       <c r="R145" t="n">
-        <v>7217957</v>
+        <v>7217891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15975,32 +15975,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128103743</v>
+        <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>92734</v>
+        <v>80227</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>626130</v>
+        <v>626248</v>
       </c>
       <c r="R146" t="n">
-        <v>7218000</v>
+        <v>7218007</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103753</v>
+        <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>80188</v>
+        <v>91482</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,21 +16083,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626465</v>
+        <v>626215</v>
       </c>
       <c r="R147" t="n">
-        <v>7217693</v>
+        <v>7218028</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,32 +16169,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103763</v>
+        <v>128103829</v>
       </c>
       <c r="B148" t="n">
-        <v>80188</v>
+        <v>98585</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626343</v>
+        <v>626217</v>
       </c>
       <c r="R148" t="n">
-        <v>7217927</v>
+        <v>7217956</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16266,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103829</v>
+        <v>128103807</v>
       </c>
       <c r="B149" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626217</v>
+        <v>626532</v>
       </c>
       <c r="R149" t="n">
-        <v>7217956</v>
+        <v>7217568</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,32 +16363,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103807</v>
+        <v>128103753</v>
       </c>
       <c r="B150" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626532</v>
+        <v>626465</v>
       </c>
       <c r="R150" t="n">
-        <v>7217568</v>
+        <v>7217693</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,10 +16460,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103735</v>
+        <v>128103763</v>
       </c>
       <c r="B151" t="n">
-        <v>57682</v>
+        <v>80192</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16471,42 +16471,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626159</v>
+        <v>626343</v>
       </c>
       <c r="R151" t="n">
-        <v>7217940</v>
+        <v>7217927</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16539,11 +16531,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16570,10 +16557,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103839</v>
+        <v>128103704</v>
       </c>
       <c r="B152" t="n">
-        <v>91470</v>
+        <v>91464</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16581,21 +16568,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16605,10 +16592,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626215</v>
+        <v>626182</v>
       </c>
       <c r="R152" t="n">
-        <v>7218028</v>
+        <v>7218029</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16667,10 +16654,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103704</v>
+        <v>128103735</v>
       </c>
       <c r="B153" t="n">
-        <v>91452</v>
+        <v>57686</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16678,34 +16665,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626182</v>
+        <v>626159</v>
       </c>
       <c r="R153" t="n">
-        <v>7218029</v>
+        <v>7217940</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16738,6 +16733,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16767,7 +16767,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91737</v>
+        <v>91749</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>128103694</v>
       </c>
       <c r="B155" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>128103737</v>
       </c>
       <c r="B156" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17055,32 +17055,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128103767</v>
+        <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>80188</v>
+        <v>92754</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>626268</v>
+        <v>626413</v>
       </c>
       <c r="R157" t="n">
-        <v>7217982</v>
+        <v>7217701</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17152,32 +17152,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128103858</v>
+        <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>92742</v>
+        <v>80192</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17187,10 +17187,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>626413</v>
+        <v>626268</v>
       </c>
       <c r="R158" t="n">
-        <v>7217701</v>
+        <v>7217982</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17252,7 +17252,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17734,10 +17734,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103766</v>
+        <v>128103786</v>
       </c>
       <c r="B164" t="n">
-        <v>80188</v>
+        <v>91937</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17745,21 +17745,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>5467</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626308</v>
+        <v>626319</v>
       </c>
       <c r="R164" t="n">
-        <v>7217938</v>
+        <v>7217868</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103786</v>
+        <v>128103766</v>
       </c>
       <c r="B165" t="n">
-        <v>91925</v>
+        <v>80192</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17842,21 +17842,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5467</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626319</v>
+        <v>626308</v>
       </c>
       <c r="R165" t="n">
-        <v>7217868</v>
+        <v>7217938</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17931,7 +17931,7 @@
         <v>128103823</v>
       </c>
       <c r="B166" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>128103813</v>
       </c>
       <c r="B167" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>128103736</v>
       </c>
       <c r="B168" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>128103783</v>
       </c>
       <c r="B169" t="n">
-        <v>91835</v>
+        <v>91847</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18329,32 +18329,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128103809</v>
+        <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>98571</v>
+        <v>57793</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>626232</v>
+        <v>626322</v>
       </c>
       <c r="R170" t="n">
-        <v>7217960</v>
+        <v>7217855</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18426,32 +18426,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128103785</v>
+        <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>57789</v>
+        <v>98585</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18461,10 +18461,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>626322</v>
+        <v>626232</v>
       </c>
       <c r="R171" t="n">
-        <v>7217855</v>
+        <v>7217960</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18523,32 +18523,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103825</v>
+        <v>128103852</v>
       </c>
       <c r="B172" t="n">
-        <v>98571</v>
+        <v>79087</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626215</v>
+        <v>626320</v>
       </c>
       <c r="R172" t="n">
-        <v>7218004</v>
+        <v>7217901</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,10 +18620,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103793</v>
+        <v>128103792</v>
       </c>
       <c r="B173" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626317</v>
+        <v>626297</v>
       </c>
       <c r="R173" t="n">
-        <v>7217867</v>
+        <v>7217856</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18720,7 +18720,7 @@
         <v>128103844</v>
       </c>
       <c r="B174" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18814,10 +18814,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103852</v>
+        <v>128103793</v>
       </c>
       <c r="B175" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18825,21 +18825,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626320</v>
+        <v>626317</v>
       </c>
       <c r="R175" t="n">
-        <v>7217901</v>
+        <v>7217867</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18911,32 +18911,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128103792</v>
+        <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>78840</v>
+        <v>98585</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>626297</v>
+        <v>626215</v>
       </c>
       <c r="R176" t="n">
-        <v>7217856</v>
+        <v>7218004</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19008,32 +19008,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128103758</v>
+        <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>80188</v>
+        <v>91429</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19043,10 +19043,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>626196</v>
+        <v>626320</v>
       </c>
       <c r="R177" t="n">
-        <v>7218053</v>
+        <v>7217864</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19105,32 +19105,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128103692</v>
+        <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>91417</v>
+        <v>80192</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19140,10 +19140,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>626320</v>
+        <v>626196</v>
       </c>
       <c r="R178" t="n">
-        <v>7217864</v>
+        <v>7218053</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19202,45 +19202,53 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103727</v>
+        <v>128103734</v>
       </c>
       <c r="B179" t="n">
-        <v>80217</v>
+        <v>57686</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626546</v>
+        <v>626084</v>
       </c>
       <c r="R179" t="n">
-        <v>7217566</v>
+        <v>7218019</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19273,6 +19281,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19299,10 +19312,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103845</v>
+        <v>128103729</v>
       </c>
       <c r="B180" t="n">
-        <v>79083</v>
+        <v>91414</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19310,21 +19323,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19334,10 +19347,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626363</v>
+        <v>626278</v>
       </c>
       <c r="R180" t="n">
-        <v>7217905</v>
+        <v>7217843</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19396,10 +19409,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103734</v>
+        <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19407,42 +19420,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626084</v>
+        <v>626363</v>
       </c>
       <c r="R181" t="n">
-        <v>7218019</v>
+        <v>7217905</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19475,11 +19480,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19506,32 +19506,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128103729</v>
+        <v>128103727</v>
       </c>
       <c r="B182" t="n">
-        <v>91402</v>
+        <v>80221</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19541,10 +19541,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>626278</v>
+        <v>626546</v>
       </c>
       <c r="R182" t="n">
-        <v>7217843</v>
+        <v>7217566</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19603,10 +19603,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103759</v>
+        <v>128103791</v>
       </c>
       <c r="B183" t="n">
-        <v>80188</v>
+        <v>78844</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19614,21 +19614,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626350</v>
+        <v>626290</v>
       </c>
       <c r="R183" t="n">
-        <v>7217852</v>
+        <v>7217851</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103695</v>
+        <v>128103759</v>
       </c>
       <c r="B184" t="n">
-        <v>79702</v>
+        <v>80192</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626290</v>
+        <v>626350</v>
       </c>
       <c r="R184" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,10 +19797,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103761</v>
+        <v>128103695</v>
       </c>
       <c r="B185" t="n">
-        <v>80188</v>
+        <v>79706</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19808,21 +19808,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626398</v>
+        <v>626290</v>
       </c>
       <c r="R185" t="n">
-        <v>7217759</v>
+        <v>7217851</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103791</v>
+        <v>128103761</v>
       </c>
       <c r="B186" t="n">
-        <v>78840</v>
+        <v>80192</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626290</v>
+        <v>626398</v>
       </c>
       <c r="R186" t="n">
-        <v>7217851</v>
+        <v>7217759</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,32 +19991,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103859</v>
+        <v>128103822</v>
       </c>
       <c r="B187" t="n">
-        <v>92742</v>
+        <v>98585</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626133</v>
+        <v>626528</v>
       </c>
       <c r="R187" t="n">
-        <v>7217998</v>
+        <v>7217613</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20091,7 +20091,7 @@
         <v>128103739</v>
       </c>
       <c r="B188" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>128103700</v>
       </c>
       <c r="B189" t="n">
-        <v>91737</v>
+        <v>91749</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20282,32 +20282,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128103822</v>
+        <v>128103859</v>
       </c>
       <c r="B190" t="n">
-        <v>98571</v>
+        <v>92754</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>626528</v>
+        <v>626133</v>
       </c>
       <c r="R190" t="n">
-        <v>7217613</v>
+        <v>7217998</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103784</v>
+        <v>128103836</v>
       </c>
       <c r="B97" t="n">
-        <v>57793</v>
+        <v>91019</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>900</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626608</v>
+        <v>626328</v>
       </c>
       <c r="R97" t="n">
-        <v>7217437</v>
+        <v>7217861</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103745</v>
+        <v>128103784</v>
       </c>
       <c r="B98" t="n">
-        <v>78845</v>
+        <v>57793</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626149</v>
+        <v>626608</v>
       </c>
       <c r="R98" t="n">
-        <v>7217977</v>
+        <v>7217437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,7 +11321,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11340,10 +11339,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>91019</v>
+        <v>78845</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11351,21 +11350,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11375,10 +11374,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R99" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11419,6 +11418,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11830,10 +11830,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103719</v>
+        <v>128103703</v>
       </c>
       <c r="B104" t="n">
-        <v>57689</v>
+        <v>91464</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11841,42 +11841,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626269</v>
+        <v>626128</v>
       </c>
       <c r="R104" t="n">
-        <v>7217921</v>
+        <v>7218027</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11909,11 +11901,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11940,10 +11927,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103703</v>
+        <v>128103719</v>
       </c>
       <c r="B105" t="n">
-        <v>91464</v>
+        <v>57689</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11951,34 +11938,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626128</v>
+        <v>626269</v>
       </c>
       <c r="R105" t="n">
-        <v>7218027</v>
+        <v>7217921</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12011,6 +12006,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12231,32 +12231,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128103830</v>
+        <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>98585</v>
+        <v>78844</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>626295</v>
+        <v>626239</v>
       </c>
       <c r="R108" t="n">
-        <v>7217850</v>
+        <v>7217951</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12328,7 +12328,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128103826</v>
+        <v>128103830</v>
       </c>
       <c r="B109" t="n">
         <v>98585</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>626206</v>
+        <v>626295</v>
       </c>
       <c r="R109" t="n">
-        <v>7218045</v>
+        <v>7217850</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12425,32 +12425,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128103794</v>
+        <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>78844</v>
+        <v>98585</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>626239</v>
+        <v>626206</v>
       </c>
       <c r="R110" t="n">
-        <v>7217951</v>
+        <v>7218045</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103871</v>
+        <v>128103733</v>
       </c>
       <c r="B116" t="n">
-        <v>92748</v>
+        <v>98606</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4362</v>
+        <v>221952</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626144</v>
+        <v>626571</v>
       </c>
       <c r="R116" t="n">
-        <v>7217996</v>
+        <v>7217492</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13215,32 +13215,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103831</v>
+        <v>128103866</v>
       </c>
       <c r="B118" t="n">
-        <v>98585</v>
+        <v>80227</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13250,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626373</v>
+        <v>626282</v>
       </c>
       <c r="R118" t="n">
-        <v>7217883</v>
+        <v>7217980</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13312,45 +13312,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103828</v>
+        <v>128103717</v>
       </c>
       <c r="B119" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626202</v>
+        <v>626217</v>
       </c>
       <c r="R119" t="n">
-        <v>7217956</v>
+        <v>7217965</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13383,6 +13391,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13409,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103733</v>
+        <v>128103831</v>
       </c>
       <c r="B120" t="n">
-        <v>98606</v>
+        <v>98585</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13444,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626571</v>
+        <v>626373</v>
       </c>
       <c r="R120" t="n">
-        <v>7217492</v>
+        <v>7217883</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13506,32 +13519,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103866</v>
+        <v>128103828</v>
       </c>
       <c r="B121" t="n">
-        <v>80227</v>
+        <v>98585</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13541,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626282</v>
+        <v>626202</v>
       </c>
       <c r="R121" t="n">
-        <v>7217980</v>
+        <v>7217956</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13603,10 +13616,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103717</v>
+        <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>57689</v>
+        <v>92748</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13614,42 +13627,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626217</v>
+        <v>626144</v>
       </c>
       <c r="R122" t="n">
-        <v>7217965</v>
+        <v>7217996</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13682,11 +13687,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13810,32 +13810,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103842</v>
+        <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>79087</v>
+        <v>80228</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13845,10 +13845,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626317</v>
+        <v>626380</v>
       </c>
       <c r="R124" t="n">
-        <v>7217935</v>
+        <v>7217892</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13907,32 +13907,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103782</v>
+        <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80228</v>
+        <v>80192</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626380</v>
+        <v>626277</v>
       </c>
       <c r="R125" t="n">
-        <v>7217892</v>
+        <v>7217976</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14004,7 +14004,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103756</v>
+        <v>128103772</v>
       </c>
       <c r="B126" t="n">
         <v>80192</v>
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626277</v>
+        <v>626347</v>
       </c>
       <c r="R126" t="n">
-        <v>7217976</v>
+        <v>7217886</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14101,10 +14101,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103772</v>
+        <v>128103721</v>
       </c>
       <c r="B127" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14112,34 +14112,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626347</v>
+        <v>626306</v>
       </c>
       <c r="R127" t="n">
-        <v>7217886</v>
+        <v>7217910</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14172,6 +14180,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14198,10 +14211,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103721</v>
+        <v>128103746</v>
       </c>
       <c r="B128" t="n">
-        <v>57689</v>
+        <v>78845</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14209,42 +14222,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626306</v>
+        <v>626290</v>
       </c>
       <c r="R128" t="n">
-        <v>7217910</v>
+        <v>7217851</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14279,17 +14284,13 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14308,32 +14309,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103824</v>
+        <v>128103842</v>
       </c>
       <c r="B129" t="n">
-        <v>98585</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14343,10 +14344,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626300</v>
+        <v>626317</v>
       </c>
       <c r="R129" t="n">
-        <v>7217895</v>
+        <v>7217935</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14405,32 +14406,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103746</v>
+        <v>128103824</v>
       </c>
       <c r="B130" t="n">
-        <v>78845</v>
+        <v>98585</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14440,10 +14441,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626290</v>
+        <v>626300</v>
       </c>
       <c r="R130" t="n">
-        <v>7217851</v>
+        <v>7217895</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14484,7 +14485,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14503,48 +14503,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103787</v>
+        <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91836</v>
+        <v>91749</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1505</v>
+        <v>71</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626280</v>
+        <v>626167</v>
       </c>
       <c r="R131" t="n">
-        <v>7217822</v>
+        <v>7217957</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14585,7 +14582,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14798,45 +14794,53 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103696</v>
+        <v>128103856</v>
       </c>
       <c r="B134" t="n">
-        <v>91749</v>
+        <v>57689</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>71</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626167</v>
+        <v>626323</v>
       </c>
       <c r="R134" t="n">
-        <v>7217957</v>
+        <v>7217908</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14869,6 +14873,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14895,53 +14904,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103856</v>
+        <v>128103811</v>
       </c>
       <c r="B135" t="n">
-        <v>57689</v>
+        <v>98585</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626323</v>
+        <v>626311</v>
       </c>
       <c r="R135" t="n">
-        <v>7217908</v>
+        <v>7217865</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14974,11 +14975,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15005,7 +15001,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103811</v>
+        <v>128103827</v>
       </c>
       <c r="B136" t="n">
         <v>98585</v>
@@ -15040,10 +15036,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626311</v>
+        <v>626128</v>
       </c>
       <c r="R136" t="n">
-        <v>7217865</v>
+        <v>7218027</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15102,10 +15098,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103827</v>
+        <v>128103787</v>
       </c>
       <c r="B137" t="n">
-        <v>98585</v>
+        <v>91836</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15113,34 +15109,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>1505</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626128</v>
+        <v>626280</v>
       </c>
       <c r="R137" t="n">
-        <v>7218027</v>
+        <v>7217822</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15181,6 +15180,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103773</v>
+        <v>128103810</v>
       </c>
       <c r="B139" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626370</v>
+        <v>626290</v>
       </c>
       <c r="R139" t="n">
-        <v>7217900</v>
+        <v>7217851</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103769</v>
+        <v>128103837</v>
       </c>
       <c r="B140" t="n">
-        <v>80192</v>
+        <v>105630</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626248</v>
+        <v>626194</v>
       </c>
       <c r="R140" t="n">
-        <v>7218007</v>
+        <v>7218055</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103810</v>
+        <v>128103773</v>
       </c>
       <c r="B141" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626290</v>
+        <v>626370</v>
       </c>
       <c r="R141" t="n">
-        <v>7217851</v>
+        <v>7217900</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103837</v>
+        <v>128103769</v>
       </c>
       <c r="B142" t="n">
-        <v>105630</v>
+        <v>80192</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626194</v>
+        <v>626248</v>
       </c>
       <c r="R142" t="n">
-        <v>7218055</v>
+        <v>7218007</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103839</v>
+        <v>128103704</v>
       </c>
       <c r="B147" t="n">
-        <v>91482</v>
+        <v>91464</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,21 +16083,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626215</v>
+        <v>626182</v>
       </c>
       <c r="R147" t="n">
-        <v>7218028</v>
+        <v>7218029</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,45 +16169,53 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103829</v>
+        <v>128103735</v>
       </c>
       <c r="B148" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626217</v>
+        <v>626159</v>
       </c>
       <c r="R148" t="n">
-        <v>7217956</v>
+        <v>7217940</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16240,6 +16248,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16266,32 +16279,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103807</v>
+        <v>128103839</v>
       </c>
       <c r="B149" t="n">
-        <v>98585</v>
+        <v>91482</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16301,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626532</v>
+        <v>626215</v>
       </c>
       <c r="R149" t="n">
-        <v>7217568</v>
+        <v>7218028</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16363,32 +16376,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103753</v>
+        <v>128103829</v>
       </c>
       <c r="B150" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16398,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626465</v>
+        <v>626217</v>
       </c>
       <c r="R150" t="n">
-        <v>7217693</v>
+        <v>7217956</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16460,32 +16473,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103763</v>
+        <v>128103807</v>
       </c>
       <c r="B151" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16495,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626343</v>
+        <v>626532</v>
       </c>
       <c r="R151" t="n">
-        <v>7217927</v>
+        <v>7217568</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16557,10 +16570,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103704</v>
+        <v>128103753</v>
       </c>
       <c r="B152" t="n">
-        <v>91464</v>
+        <v>80192</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16568,21 +16581,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16592,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626182</v>
+        <v>626465</v>
       </c>
       <c r="R152" t="n">
-        <v>7218029</v>
+        <v>7217693</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16654,10 +16667,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103735</v>
+        <v>128103763</v>
       </c>
       <c r="B153" t="n">
-        <v>57686</v>
+        <v>80192</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16665,42 +16678,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626159</v>
+        <v>626343</v>
       </c>
       <c r="R153" t="n">
-        <v>7217940</v>
+        <v>7217927</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16733,11 +16738,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16764,32 +16764,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128103699</v>
+        <v>128103694</v>
       </c>
       <c r="B154" t="n">
-        <v>91749</v>
+        <v>79706</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>626262</v>
+        <v>626150</v>
       </c>
       <c r="R154" t="n">
-        <v>7217920</v>
+        <v>7217973</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16861,32 +16861,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128103694</v>
+        <v>128103699</v>
       </c>
       <c r="B155" t="n">
-        <v>79706</v>
+        <v>91749</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626150</v>
+        <v>626262</v>
       </c>
       <c r="R155" t="n">
-        <v>7217973</v>
+        <v>7217920</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17249,10 +17249,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103851</v>
+        <v>128103770</v>
       </c>
       <c r="B159" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17260,21 +17260,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626264</v>
+        <v>626249</v>
       </c>
       <c r="R159" t="n">
-        <v>7217994</v>
+        <v>7218009</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17346,7 +17346,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103770</v>
+        <v>128103774</v>
       </c>
       <c r="B160" t="n">
         <v>80192</v>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626249</v>
+        <v>626377</v>
       </c>
       <c r="R160" t="n">
-        <v>7218009</v>
+        <v>7217880</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103774</v>
+        <v>128103768</v>
       </c>
       <c r="B161" t="n">
         <v>80192</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626377</v>
+        <v>626272</v>
       </c>
       <c r="R161" t="n">
-        <v>7217880</v>
+        <v>7217987</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,10 +17540,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103768</v>
+        <v>128103851</v>
       </c>
       <c r="B162" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17551,21 +17551,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626272</v>
+        <v>626264</v>
       </c>
       <c r="R162" t="n">
-        <v>7217987</v>
+        <v>7217994</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17734,10 +17734,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103786</v>
+        <v>128103736</v>
       </c>
       <c r="B164" t="n">
-        <v>91937</v>
+        <v>57686</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17745,34 +17745,42 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626319</v>
+        <v>626194</v>
       </c>
       <c r="R164" t="n">
-        <v>7217868</v>
+        <v>7217951</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17805,6 +17813,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17831,32 +17844,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103766</v>
+        <v>128103823</v>
       </c>
       <c r="B165" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17879,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626308</v>
+        <v>626337</v>
       </c>
       <c r="R165" t="n">
-        <v>7217938</v>
+        <v>7217840</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,7 +17941,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103823</v>
+        <v>128103813</v>
       </c>
       <c r="B166" t="n">
         <v>98585</v>
@@ -17963,10 +17976,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626337</v>
+        <v>626370</v>
       </c>
       <c r="R166" t="n">
-        <v>7217840</v>
+        <v>7217900</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18025,10 +18038,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103813</v>
+        <v>128103783</v>
       </c>
       <c r="B167" t="n">
-        <v>98585</v>
+        <v>91847</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18036,21 +18049,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18060,10 +18073,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626370</v>
+        <v>626271</v>
       </c>
       <c r="R167" t="n">
-        <v>7217900</v>
+        <v>7217852</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18122,10 +18135,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103736</v>
+        <v>128103786</v>
       </c>
       <c r="B168" t="n">
-        <v>57686</v>
+        <v>91937</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18133,42 +18146,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>5467</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626194</v>
+        <v>626319</v>
       </c>
       <c r="R168" t="n">
-        <v>7217951</v>
+        <v>7217868</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18201,11 +18206,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18232,32 +18232,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103783</v>
+        <v>128103766</v>
       </c>
       <c r="B169" t="n">
-        <v>91847</v>
+        <v>80192</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>298</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626271</v>
+        <v>626308</v>
       </c>
       <c r="R169" t="n">
-        <v>7217852</v>
+        <v>7217938</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19202,10 +19202,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128103734</v>
+        <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>57686</v>
+        <v>91414</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19213,42 +19213,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>626084</v>
+        <v>626278</v>
       </c>
       <c r="R179" t="n">
-        <v>7218019</v>
+        <v>7217843</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19281,11 +19273,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19312,10 +19299,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103729</v>
+        <v>128103845</v>
       </c>
       <c r="B180" t="n">
-        <v>91414</v>
+        <v>79087</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19323,21 +19310,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19347,10 +19334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626278</v>
+        <v>626363</v>
       </c>
       <c r="R180" t="n">
-        <v>7217843</v>
+        <v>7217905</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19409,10 +19396,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103845</v>
+        <v>128103734</v>
       </c>
       <c r="B181" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19420,34 +19407,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626363</v>
+        <v>626084</v>
       </c>
       <c r="R181" t="n">
-        <v>7217905</v>
+        <v>7218019</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19480,6 +19475,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD181" t="b">

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11145,32 +11145,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128103836</v>
+        <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>91019</v>
+        <v>57793</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>900</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>626328</v>
+        <v>626608</v>
       </c>
       <c r="R97" t="n">
-        <v>7217861</v>
+        <v>7217437</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11242,32 +11242,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103784</v>
+        <v>128103745</v>
       </c>
       <c r="B98" t="n">
-        <v>57793</v>
+        <v>78845</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626608</v>
+        <v>626149</v>
       </c>
       <c r="R98" t="n">
-        <v>7217437</v>
+        <v>7217977</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,6 +11321,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11339,10 +11340,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103745</v>
+        <v>128103836</v>
       </c>
       <c r="B99" t="n">
-        <v>78845</v>
+        <v>91019</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,21 +11351,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>900</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11374,10 +11375,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626149</v>
+        <v>626328</v>
       </c>
       <c r="R99" t="n">
-        <v>7217977</v>
+        <v>7217861</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11418,7 +11419,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11830,32 +11830,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103703</v>
+        <v>128103812</v>
       </c>
       <c r="B104" t="n">
-        <v>91464</v>
+        <v>98585</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626128</v>
+        <v>626319</v>
       </c>
       <c r="R104" t="n">
-        <v>7218027</v>
+        <v>7217868</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11927,53 +11927,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103719</v>
+        <v>128103806</v>
       </c>
       <c r="B105" t="n">
-        <v>57689</v>
+        <v>98585</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626269</v>
+        <v>626574</v>
       </c>
       <c r="R105" t="n">
-        <v>7217921</v>
+        <v>7217449</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12006,11 +11998,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12037,32 +12024,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103812</v>
+        <v>128103703</v>
       </c>
       <c r="B106" t="n">
-        <v>98585</v>
+        <v>91464</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12072,10 +12059,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626319</v>
+        <v>626128</v>
       </c>
       <c r="R106" t="n">
-        <v>7217868</v>
+        <v>7218027</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12134,45 +12121,53 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128103806</v>
+        <v>128103719</v>
       </c>
       <c r="B107" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>626574</v>
+        <v>626269</v>
       </c>
       <c r="R107" t="n">
-        <v>7217449</v>
+        <v>7217921</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12205,6 +12200,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12231,32 +12231,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128103794</v>
+        <v>128103830</v>
       </c>
       <c r="B108" t="n">
-        <v>78844</v>
+        <v>98585</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>626239</v>
+        <v>626295</v>
       </c>
       <c r="R108" t="n">
-        <v>7217951</v>
+        <v>7217850</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12328,7 +12328,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128103830</v>
+        <v>128103826</v>
       </c>
       <c r="B109" t="n">
         <v>98585</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>626295</v>
+        <v>626206</v>
       </c>
       <c r="R109" t="n">
-        <v>7217850</v>
+        <v>7218045</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12425,32 +12425,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128103826</v>
+        <v>128103794</v>
       </c>
       <c r="B110" t="n">
-        <v>98585</v>
+        <v>78844</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>626206</v>
+        <v>626239</v>
       </c>
       <c r="R110" t="n">
-        <v>7218045</v>
+        <v>7217951</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12813,10 +12813,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103716</v>
+        <v>128103744</v>
       </c>
       <c r="B114" t="n">
-        <v>57689</v>
+        <v>78845</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12824,32 +12824,24 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
@@ -12894,17 +12886,13 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12923,10 +12911,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103744</v>
+        <v>128103716</v>
       </c>
       <c r="B115" t="n">
-        <v>78845</v>
+        <v>57689</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12934,24 +12922,32 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
@@ -12996,13 +12992,17 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13021,32 +13021,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103733</v>
+        <v>128103871</v>
       </c>
       <c r="B116" t="n">
-        <v>98606</v>
+        <v>92748</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221952</v>
+        <v>4362</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626571</v>
+        <v>626144</v>
       </c>
       <c r="R116" t="n">
-        <v>7217492</v>
+        <v>7217996</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13215,32 +13215,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103866</v>
+        <v>128103831</v>
       </c>
       <c r="B118" t="n">
-        <v>80227</v>
+        <v>98585</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13250,10 +13250,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626282</v>
+        <v>626373</v>
       </c>
       <c r="R118" t="n">
-        <v>7217980</v>
+        <v>7217883</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13312,53 +13312,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103717</v>
+        <v>128103828</v>
       </c>
       <c r="B119" t="n">
-        <v>57689</v>
+        <v>98585</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626217</v>
+        <v>626202</v>
       </c>
       <c r="R119" t="n">
-        <v>7217965</v>
+        <v>7217956</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13391,11 +13383,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13422,32 +13409,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103831</v>
+        <v>128103733</v>
       </c>
       <c r="B120" t="n">
-        <v>98585</v>
+        <v>98606</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13457,10 +13444,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626373</v>
+        <v>626571</v>
       </c>
       <c r="R120" t="n">
-        <v>7217883</v>
+        <v>7217492</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13519,32 +13506,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103828</v>
+        <v>128103866</v>
       </c>
       <c r="B121" t="n">
-        <v>98585</v>
+        <v>80227</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13554,10 +13541,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626202</v>
+        <v>626282</v>
       </c>
       <c r="R121" t="n">
-        <v>7217956</v>
+        <v>7217980</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13616,10 +13603,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103871</v>
+        <v>128103717</v>
       </c>
       <c r="B122" t="n">
-        <v>92748</v>
+        <v>57689</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13627,34 +13614,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626144</v>
+        <v>626217</v>
       </c>
       <c r="R122" t="n">
-        <v>7217996</v>
+        <v>7217965</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13687,6 +13682,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13810,32 +13810,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103782</v>
+        <v>128103746</v>
       </c>
       <c r="B124" t="n">
-        <v>80228</v>
+        <v>78845</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13845,10 +13845,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626380</v>
+        <v>626290</v>
       </c>
       <c r="R124" t="n">
-        <v>7217892</v>
+        <v>7217851</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,6 +13889,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13907,10 +13908,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103756</v>
+        <v>128103842</v>
       </c>
       <c r="B125" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13918,21 +13919,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13942,10 +13943,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626277</v>
+        <v>626317</v>
       </c>
       <c r="R125" t="n">
-        <v>7217976</v>
+        <v>7217935</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14004,32 +14005,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103772</v>
+        <v>128103782</v>
       </c>
       <c r="B126" t="n">
-        <v>80192</v>
+        <v>80228</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14039,10 +14040,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626347</v>
+        <v>626380</v>
       </c>
       <c r="R126" t="n">
-        <v>7217886</v>
+        <v>7217892</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14101,10 +14102,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103721</v>
+        <v>128103756</v>
       </c>
       <c r="B127" t="n">
-        <v>57689</v>
+        <v>80192</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14112,42 +14113,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626306</v>
+        <v>626277</v>
       </c>
       <c r="R127" t="n">
-        <v>7217910</v>
+        <v>7217976</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14180,11 +14173,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14211,10 +14199,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103746</v>
+        <v>128103772</v>
       </c>
       <c r="B128" t="n">
-        <v>78845</v>
+        <v>80192</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14222,21 +14210,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14246,10 +14234,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626290</v>
+        <v>626347</v>
       </c>
       <c r="R128" t="n">
-        <v>7217851</v>
+        <v>7217886</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14290,7 +14278,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14309,10 +14296,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103842</v>
+        <v>128103721</v>
       </c>
       <c r="B129" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14320,34 +14307,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626317</v>
+        <v>626306</v>
       </c>
       <c r="R129" t="n">
-        <v>7217935</v>
+        <v>7217910</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14380,6 +14375,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14503,45 +14503,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103696</v>
+        <v>128103787</v>
       </c>
       <c r="B131" t="n">
-        <v>91749</v>
+        <v>91836</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>71</v>
+        <v>1505</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626167</v>
+        <v>626280</v>
       </c>
       <c r="R131" t="n">
-        <v>7217957</v>
+        <v>7217822</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14582,6 +14585,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14794,53 +14798,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103856</v>
+        <v>128103696</v>
       </c>
       <c r="B134" t="n">
-        <v>57689</v>
+        <v>91749</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>71</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626323</v>
+        <v>626167</v>
       </c>
       <c r="R134" t="n">
-        <v>7217908</v>
+        <v>7217957</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14873,11 +14869,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14904,45 +14895,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103811</v>
+        <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626311</v>
+        <v>626323</v>
       </c>
       <c r="R135" t="n">
-        <v>7217865</v>
+        <v>7217908</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14975,6 +14974,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15001,7 +15005,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103827</v>
+        <v>128103811</v>
       </c>
       <c r="B136" t="n">
         <v>98585</v>
@@ -15036,10 +15040,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626128</v>
+        <v>626311</v>
       </c>
       <c r="R136" t="n">
-        <v>7218027</v>
+        <v>7217865</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15098,10 +15102,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103787</v>
+        <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>91836</v>
+        <v>98585</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15109,37 +15113,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626280</v>
+        <v>626128</v>
       </c>
       <c r="R137" t="n">
-        <v>7217822</v>
+        <v>7218027</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15180,7 +15181,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -15296,32 +15296,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103810</v>
+        <v>128103773</v>
       </c>
       <c r="B139" t="n">
-        <v>98585</v>
+        <v>80192</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626290</v>
+        <v>626370</v>
       </c>
       <c r="R139" t="n">
-        <v>7217851</v>
+        <v>7217900</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,32 +15393,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103837</v>
+        <v>128103769</v>
       </c>
       <c r="B140" t="n">
-        <v>105630</v>
+        <v>80192</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626194</v>
+        <v>626248</v>
       </c>
       <c r="R140" t="n">
-        <v>7218055</v>
+        <v>7218007</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103773</v>
+        <v>128103810</v>
       </c>
       <c r="B141" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626370</v>
+        <v>626290</v>
       </c>
       <c r="R141" t="n">
-        <v>7217900</v>
+        <v>7217851</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15587,32 +15587,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128103769</v>
+        <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>80192</v>
+        <v>105630</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>626248</v>
+        <v>626194</v>
       </c>
       <c r="R142" t="n">
-        <v>7218007</v>
+        <v>7218055</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16861,32 +16861,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128103699</v>
+        <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>91749</v>
+        <v>92758</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>71</v>
+        <v>4365</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16896,10 +16896,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>626262</v>
+        <v>626278</v>
       </c>
       <c r="R155" t="n">
-        <v>7217920</v>
+        <v>7217843</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103737</v>
+        <v>128103699</v>
       </c>
       <c r="B156" t="n">
-        <v>92758</v>
+        <v>91749</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4365</v>
+        <v>71</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626278</v>
+        <v>626262</v>
       </c>
       <c r="R156" t="n">
-        <v>7217843</v>
+        <v>7217920</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17249,10 +17249,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128103770</v>
+        <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17260,21 +17260,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>626249</v>
+        <v>626264</v>
       </c>
       <c r="R159" t="n">
-        <v>7218009</v>
+        <v>7217994</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17346,7 +17346,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128103774</v>
+        <v>128103770</v>
       </c>
       <c r="B160" t="n">
         <v>80192</v>
@@ -17381,10 +17381,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>626377</v>
+        <v>626249</v>
       </c>
       <c r="R160" t="n">
-        <v>7217880</v>
+        <v>7218009</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17443,7 +17443,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128103768</v>
+        <v>128103774</v>
       </c>
       <c r="B161" t="n">
         <v>80192</v>
@@ -17478,10 +17478,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>626272</v>
+        <v>626377</v>
       </c>
       <c r="R161" t="n">
-        <v>7217987</v>
+        <v>7217880</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17540,10 +17540,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128103851</v>
+        <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17551,21 +17551,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>626264</v>
+        <v>626272</v>
       </c>
       <c r="R162" t="n">
-        <v>7217994</v>
+        <v>7217987</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19396,53 +19396,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103734</v>
+        <v>128103727</v>
       </c>
       <c r="B181" t="n">
-        <v>57686</v>
+        <v>80221</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626084</v>
+        <v>626546</v>
       </c>
       <c r="R181" t="n">
-        <v>7218019</v>
+        <v>7217566</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19475,11 +19467,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19506,45 +19493,53 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128103727</v>
+        <v>128103734</v>
       </c>
       <c r="B182" t="n">
-        <v>80221</v>
+        <v>57686</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>626546</v>
+        <v>626084</v>
       </c>
       <c r="R182" t="n">
-        <v>7217566</v>
+        <v>7218019</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19577,6 +19572,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD182" t="b">

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11242,10 +11242,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128103745</v>
+        <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>78845</v>
+        <v>91021</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11253,21 +11253,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>900</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>626149</v>
+        <v>626328</v>
       </c>
       <c r="R98" t="n">
-        <v>7217977</v>
+        <v>7217861</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11321,7 +11321,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11340,10 +11339,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128103836</v>
+        <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>91019</v>
+        <v>78847</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11351,21 +11350,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>900</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11375,10 +11374,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>626328</v>
+        <v>626149</v>
       </c>
       <c r="R99" t="n">
-        <v>7217861</v>
+        <v>7217977</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11419,6 +11418,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11437,10 +11437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128103757</v>
+        <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11448,21 +11448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>626239</v>
+        <v>626593</v>
       </c>
       <c r="R100" t="n">
-        <v>7218007</v>
+        <v>7217442</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11508,6 +11508,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11534,32 +11539,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128103728</v>
+        <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80221</v>
+        <v>80194</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11569,10 +11574,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>626453</v>
+        <v>626239</v>
       </c>
       <c r="R101" t="n">
-        <v>7217719</v>
+        <v>7218007</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11631,32 +11636,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128103701</v>
+        <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>91464</v>
+        <v>80223</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11666,10 +11671,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>626222</v>
+        <v>626453</v>
       </c>
       <c r="R102" t="n">
-        <v>7218014</v>
+        <v>7217719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11728,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128103850</v>
+        <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>79087</v>
+        <v>91466</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11739,21 +11744,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11763,10 +11768,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>626593</v>
+        <v>626222</v>
       </c>
       <c r="R103" t="n">
-        <v>7217442</v>
+        <v>7218014</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11799,11 +11804,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Med apothecier bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11830,45 +11830,53 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128103812</v>
+        <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>626319</v>
+        <v>626269</v>
       </c>
       <c r="R104" t="n">
-        <v>7217868</v>
+        <v>7217921</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11901,6 +11909,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11927,10 +11940,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128103806</v>
+        <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11962,10 +11975,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>626574</v>
+        <v>626319</v>
       </c>
       <c r="R105" t="n">
-        <v>7217449</v>
+        <v>7217868</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12024,32 +12037,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128103703</v>
+        <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>91464</v>
+        <v>98591</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12059,10 +12072,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>626128</v>
+        <v>626574</v>
       </c>
       <c r="R106" t="n">
-        <v>7218027</v>
+        <v>7217449</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12121,10 +12134,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128103719</v>
+        <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>57689</v>
+        <v>91466</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12132,42 +12145,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>626269</v>
+        <v>626128</v>
       </c>
       <c r="R107" t="n">
-        <v>7217921</v>
+        <v>7218027</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12200,11 +12205,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12231,32 +12231,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128103830</v>
+        <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>98585</v>
+        <v>78846</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>626295</v>
+        <v>626239</v>
       </c>
       <c r="R108" t="n">
-        <v>7217850</v>
+        <v>7217951</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12328,10 +12328,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128103826</v>
+        <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>626206</v>
+        <v>626295</v>
       </c>
       <c r="R109" t="n">
-        <v>7218045</v>
+        <v>7217850</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12425,32 +12425,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128103794</v>
+        <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>78844</v>
+        <v>98591</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>626239</v>
+        <v>626206</v>
       </c>
       <c r="R110" t="n">
-        <v>7217951</v>
+        <v>7218045</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103870</v>
+        <v>128103765</v>
       </c>
       <c r="B111" t="n">
-        <v>78059</v>
+        <v>80194</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626270</v>
+        <v>626320</v>
       </c>
       <c r="R111" t="n">
-        <v>7217834</v>
+        <v>7217923</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103754</v>
+        <v>128103870</v>
       </c>
       <c r="B112" t="n">
-        <v>80192</v>
+        <v>78061</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626325</v>
+        <v>626270</v>
       </c>
       <c r="R112" t="n">
-        <v>7217934</v>
+        <v>7217834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12716,10 +12716,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103765</v>
+        <v>128103754</v>
       </c>
       <c r="B113" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12751,10 +12751,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626320</v>
+        <v>626325</v>
       </c>
       <c r="R113" t="n">
-        <v>7217923</v>
+        <v>7217934</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12813,10 +12813,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103744</v>
+        <v>128103716</v>
       </c>
       <c r="B114" t="n">
-        <v>78845</v>
+        <v>57689</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12824,24 +12824,32 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
@@ -12886,13 +12894,17 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12911,10 +12923,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103716</v>
+        <v>128103744</v>
       </c>
       <c r="B115" t="n">
-        <v>57689</v>
+        <v>78847</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12922,32 +12934,24 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
@@ -12992,17 +12996,13 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13021,10 +13021,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103871</v>
+        <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>92748</v>
+        <v>79089</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13032,21 +13032,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>626144</v>
+        <v>626328</v>
       </c>
       <c r="R116" t="n">
-        <v>7217996</v>
+        <v>7217861</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13118,27 +13118,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128103853</v>
+        <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>79087</v>
+        <v>80229</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>626328</v>
+        <v>626282</v>
       </c>
       <c r="R117" t="n">
-        <v>7217861</v>
+        <v>7217980</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13215,45 +13215,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103831</v>
+        <v>128103717</v>
       </c>
       <c r="B118" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>626373</v>
+        <v>626217</v>
       </c>
       <c r="R118" t="n">
-        <v>7217883</v>
+        <v>7217965</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13286,6 +13294,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13312,10 +13325,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128103828</v>
+        <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13347,10 +13360,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>626202</v>
+        <v>626373</v>
       </c>
       <c r="R119" t="n">
-        <v>7217956</v>
+        <v>7217883</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13409,32 +13422,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103733</v>
+        <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98606</v>
+        <v>98591</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13444,10 +13457,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>626571</v>
+        <v>626202</v>
       </c>
       <c r="R120" t="n">
-        <v>7217492</v>
+        <v>7217956</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13506,10 +13519,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103866</v>
+        <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>80227</v>
+        <v>98612</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13517,21 +13530,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13541,10 +13554,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>626282</v>
+        <v>626571</v>
       </c>
       <c r="R121" t="n">
-        <v>7217980</v>
+        <v>7217492</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13603,10 +13616,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103717</v>
+        <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>57689</v>
+        <v>92750</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13614,42 +13627,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>626217</v>
+        <v>626144</v>
       </c>
       <c r="R122" t="n">
-        <v>7217965</v>
+        <v>7217996</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13682,11 +13687,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13716,7 +13716,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13810,32 +13810,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128103746</v>
+        <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>78845</v>
+        <v>80230</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13845,10 +13845,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>626290</v>
+        <v>626380</v>
       </c>
       <c r="R124" t="n">
-        <v>7217851</v>
+        <v>7217892</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13889,7 +13889,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13908,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128103842</v>
+        <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13919,21 +13918,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13943,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>626317</v>
+        <v>626277</v>
       </c>
       <c r="R125" t="n">
-        <v>7217935</v>
+        <v>7217976</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14005,32 +14004,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128103782</v>
+        <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80228</v>
+        <v>80194</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14040,10 +14039,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>626380</v>
+        <v>626347</v>
       </c>
       <c r="R126" t="n">
-        <v>7217892</v>
+        <v>7217886</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14102,10 +14101,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128103756</v>
+        <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>80192</v>
+        <v>79089</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14113,21 +14112,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14137,10 +14136,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>626277</v>
+        <v>626317</v>
       </c>
       <c r="R127" t="n">
-        <v>7217976</v>
+        <v>7217935</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14199,10 +14198,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128103772</v>
+        <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14210,34 +14209,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>626347</v>
+        <v>626306</v>
       </c>
       <c r="R128" t="n">
-        <v>7217886</v>
+        <v>7217910</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14270,6 +14277,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14296,53 +14308,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128103721</v>
+        <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>626306</v>
+        <v>626300</v>
       </c>
       <c r="R129" t="n">
-        <v>7217910</v>
+        <v>7217895</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14375,11 +14379,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14406,32 +14405,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128103824</v>
+        <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>98585</v>
+        <v>78847</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14441,10 +14440,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>626300</v>
+        <v>626290</v>
       </c>
       <c r="R130" t="n">
-        <v>7217895</v>
+        <v>7217851</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14485,6 +14484,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14503,10 +14503,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103787</v>
+        <v>128103827</v>
       </c>
       <c r="B131" t="n">
-        <v>91836</v>
+        <v>98591</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14514,37 +14514,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1505</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626280</v>
+        <v>626128</v>
       </c>
       <c r="R131" t="n">
-        <v>7217822</v>
+        <v>7218027</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14585,7 +14582,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14604,32 +14600,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103781</v>
+        <v>128103696</v>
       </c>
       <c r="B132" t="n">
-        <v>80228</v>
+        <v>91751</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>71</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14639,10 +14635,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626239</v>
+        <v>626167</v>
       </c>
       <c r="R132" t="n">
-        <v>7218007</v>
+        <v>7217957</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14701,45 +14697,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103867</v>
+        <v>128103787</v>
       </c>
       <c r="B133" t="n">
-        <v>80227</v>
+        <v>91838</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6463</v>
+        <v>1505</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626346</v>
+        <v>626280</v>
       </c>
       <c r="R133" t="n">
-        <v>7217883</v>
+        <v>7217822</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14780,6 +14779,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14798,32 +14798,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103696</v>
+        <v>128103781</v>
       </c>
       <c r="B134" t="n">
-        <v>91749</v>
+        <v>80230</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>71</v>
+        <v>6464</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14833,10 +14833,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626167</v>
+        <v>626239</v>
       </c>
       <c r="R134" t="n">
-        <v>7217957</v>
+        <v>7218007</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14895,53 +14895,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103856</v>
+        <v>128103867</v>
       </c>
       <c r="B135" t="n">
-        <v>57689</v>
+        <v>80229</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626323</v>
+        <v>626346</v>
       </c>
       <c r="R135" t="n">
-        <v>7217908</v>
+        <v>7217883</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14974,11 +14966,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15005,45 +14992,53 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103811</v>
+        <v>128103856</v>
       </c>
       <c r="B136" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626311</v>
+        <v>626323</v>
       </c>
       <c r="R136" t="n">
-        <v>7217865</v>
+        <v>7217908</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15076,6 +15071,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15102,10 +15102,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103827</v>
+        <v>128103811</v>
       </c>
       <c r="B137" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626128</v>
+        <v>626311</v>
       </c>
       <c r="R137" t="n">
-        <v>7218027</v>
+        <v>7217865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15199,32 +15199,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128103835</v>
+        <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>91019</v>
+        <v>98591</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>900</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gröntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Kavinia alboviridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Morgan) Gilb. &amp; Budington</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>626354</v>
+        <v>626290</v>
       </c>
       <c r="R138" t="n">
-        <v>7217769</v>
+        <v>7217851</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15296,10 +15296,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103773</v>
+        <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>80192</v>
+        <v>91021</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15307,21 +15307,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>900</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gröntagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Kavinia alboviridis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Morgan) Gilb. &amp; Budington</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15331,10 +15331,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>626370</v>
+        <v>626354</v>
       </c>
       <c r="R139" t="n">
-        <v>7217900</v>
+        <v>7217769</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15393,10 +15393,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128103769</v>
+        <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>626248</v>
+        <v>626370</v>
       </c>
       <c r="R140" t="n">
-        <v>7218007</v>
+        <v>7217900</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15490,32 +15490,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128103810</v>
+        <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>626290</v>
+        <v>626248</v>
       </c>
       <c r="R141" t="n">
-        <v>7217851</v>
+        <v>7218007</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15590,7 +15590,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105630</v>
+        <v>105651</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91725</v>
+        <v>91727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16072,10 +16072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128103704</v>
+        <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91464</v>
+        <v>91484</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16083,21 +16083,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>626182</v>
+        <v>626215</v>
       </c>
       <c r="R147" t="n">
-        <v>7218029</v>
+        <v>7218028</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16169,10 +16169,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128103735</v>
+        <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>57686</v>
+        <v>91466</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16180,42 +16180,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>626159</v>
+        <v>626182</v>
       </c>
       <c r="R148" t="n">
-        <v>7217940</v>
+        <v>7218029</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16248,11 +16240,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16279,10 +16266,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128103839</v>
+        <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>91482</v>
+        <v>80194</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16290,21 +16277,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16314,10 +16301,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>626215</v>
+        <v>626465</v>
       </c>
       <c r="R149" t="n">
-        <v>7218028</v>
+        <v>7217693</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16376,32 +16363,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128103829</v>
+        <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>98585</v>
+        <v>80194</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16411,10 +16398,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>626217</v>
+        <v>626343</v>
       </c>
       <c r="R150" t="n">
-        <v>7217956</v>
+        <v>7217927</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16473,45 +16460,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128103807</v>
+        <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>98585</v>
+        <v>57686</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>626532</v>
+        <v>626159</v>
       </c>
       <c r="R151" t="n">
-        <v>7217568</v>
+        <v>7217940</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16544,6 +16539,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16570,32 +16570,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128103753</v>
+        <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>80192</v>
+        <v>98591</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>626465</v>
+        <v>626217</v>
       </c>
       <c r="R152" t="n">
-        <v>7217693</v>
+        <v>7217956</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16667,32 +16667,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128103763</v>
+        <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>80192</v>
+        <v>98591</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>626343</v>
+        <v>626532</v>
       </c>
       <c r="R153" t="n">
-        <v>7217927</v>
+        <v>7217568</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16764,32 +16764,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128103694</v>
+        <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>79706</v>
+        <v>91751</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16799,10 +16799,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>626150</v>
+        <v>626262</v>
       </c>
       <c r="R154" t="n">
-        <v>7217973</v>
+        <v>7217920</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16864,7 +16864,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16958,32 +16958,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128103699</v>
+        <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>91749</v>
+        <v>79708</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16993,10 +16993,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>626262</v>
+        <v>626150</v>
       </c>
       <c r="R156" t="n">
-        <v>7217920</v>
+        <v>7217973</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17058,7 +17058,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17734,53 +17734,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103736</v>
+        <v>128103813</v>
       </c>
       <c r="B164" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626194</v>
+        <v>626370</v>
       </c>
       <c r="R164" t="n">
-        <v>7217951</v>
+        <v>7217900</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17813,11 +17805,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17844,10 +17831,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103823</v>
+        <v>128103783</v>
       </c>
       <c r="B165" t="n">
-        <v>98585</v>
+        <v>91849</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17855,21 +17842,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17879,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626337</v>
+        <v>626271</v>
       </c>
       <c r="R165" t="n">
-        <v>7217840</v>
+        <v>7217852</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17941,32 +17928,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103813</v>
+        <v>128103786</v>
       </c>
       <c r="B166" t="n">
-        <v>98585</v>
+        <v>91939</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17976,10 +17963,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626370</v>
+        <v>626319</v>
       </c>
       <c r="R166" t="n">
-        <v>7217900</v>
+        <v>7217868</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18038,32 +18025,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103783</v>
+        <v>128103766</v>
       </c>
       <c r="B167" t="n">
-        <v>91847</v>
+        <v>80194</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>298</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18073,10 +18060,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626271</v>
+        <v>626308</v>
       </c>
       <c r="R167" t="n">
-        <v>7217852</v>
+        <v>7217938</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18135,10 +18122,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103786</v>
+        <v>128103736</v>
       </c>
       <c r="B168" t="n">
-        <v>91937</v>
+        <v>57686</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18146,34 +18133,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626319</v>
+        <v>626194</v>
       </c>
       <c r="R168" t="n">
-        <v>7217868</v>
+        <v>7217951</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18206,6 +18201,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18232,32 +18232,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103766</v>
+        <v>128103823</v>
       </c>
       <c r="B169" t="n">
-        <v>80192</v>
+        <v>98591</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626308</v>
+        <v>626337</v>
       </c>
       <c r="R169" t="n">
-        <v>7217938</v>
+        <v>7217840</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18429,7 +18429,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18523,10 +18523,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128103852</v>
+        <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18534,21 +18534,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>626320</v>
+        <v>626317</v>
       </c>
       <c r="R172" t="n">
-        <v>7217901</v>
+        <v>7217867</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18620,10 +18620,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128103792</v>
+        <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18631,21 +18631,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>626297</v>
+        <v>626263</v>
       </c>
       <c r="R173" t="n">
-        <v>7217856</v>
+        <v>7217877</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18717,10 +18717,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128103844</v>
+        <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18752,10 +18752,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>626263</v>
+        <v>626320</v>
       </c>
       <c r="R174" t="n">
-        <v>7217877</v>
+        <v>7217901</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18814,10 +18814,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128103793</v>
+        <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>626317</v>
+        <v>626297</v>
       </c>
       <c r="R175" t="n">
-        <v>7217867</v>
+        <v>7217856</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18914,7 +18914,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91414</v>
+        <v>91416</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19299,32 +19299,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128103845</v>
+        <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>79087</v>
+        <v>80223</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>626363</v>
+        <v>626546</v>
       </c>
       <c r="R180" t="n">
-        <v>7217905</v>
+        <v>7217566</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19396,32 +19396,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128103727</v>
+        <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>80221</v>
+        <v>79089</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19431,10 +19431,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>626546</v>
+        <v>626363</v>
       </c>
       <c r="R181" t="n">
-        <v>7217566</v>
+        <v>7217905</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103791</v>
+        <v>128103700</v>
       </c>
       <c r="B183" t="n">
-        <v>78844</v>
+        <v>91751</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>71</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626290</v>
+        <v>626271</v>
       </c>
       <c r="R183" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103759</v>
+        <v>128103739</v>
       </c>
       <c r="B184" t="n">
-        <v>80192</v>
+        <v>80195</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626350</v>
+        <v>626582</v>
       </c>
       <c r="R184" t="n">
-        <v>7217852</v>
+        <v>7217455</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,10 +19797,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103695</v>
+        <v>128103759</v>
       </c>
       <c r="B185" t="n">
-        <v>79706</v>
+        <v>80194</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19808,21 +19808,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626290</v>
+        <v>626350</v>
       </c>
       <c r="R185" t="n">
-        <v>7217851</v>
+        <v>7217852</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103761</v>
+        <v>128103695</v>
       </c>
       <c r="B186" t="n">
-        <v>80192</v>
+        <v>79708</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626398</v>
+        <v>626290</v>
       </c>
       <c r="R186" t="n">
-        <v>7217759</v>
+        <v>7217851</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,32 +19991,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103822</v>
+        <v>128103859</v>
       </c>
       <c r="B187" t="n">
-        <v>98585</v>
+        <v>92756</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626528</v>
+        <v>626133</v>
       </c>
       <c r="R187" t="n">
-        <v>7217613</v>
+        <v>7217998</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,10 +20088,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103739</v>
+        <v>128103761</v>
       </c>
       <c r="B188" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20099,21 +20099,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626582</v>
+        <v>626398</v>
       </c>
       <c r="R188" t="n">
-        <v>7217455</v>
+        <v>7217759</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20185,32 +20185,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128103700</v>
+        <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>91749</v>
+        <v>78846</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>71</v>
+        <v>6446</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>626271</v>
+        <v>626290</v>
       </c>
       <c r="R189" t="n">
-        <v>7217852</v>
+        <v>7217851</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20282,32 +20282,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128103859</v>
+        <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>92754</v>
+        <v>98591</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>626133</v>
+        <v>626528</v>
       </c>
       <c r="R190" t="n">
-        <v>7217998</v>
+        <v>7217613</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -12522,10 +12522,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103765</v>
+        <v>128103716</v>
       </c>
       <c r="B111" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12533,34 +12533,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>626320</v>
+        <v>626454</v>
       </c>
       <c r="R111" t="n">
-        <v>7217923</v>
+        <v>7217736</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12593,6 +12601,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12619,10 +12632,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103870</v>
+        <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78061</v>
+        <v>78847</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12630,21 +12643,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12654,10 +12667,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>626270</v>
+        <v>626454</v>
       </c>
       <c r="R112" t="n">
-        <v>7217834</v>
+        <v>7217736</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12698,6 +12711,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12716,10 +12730,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103754</v>
+        <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>80194</v>
+        <v>78061</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12727,21 +12741,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12751,10 +12765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>626325</v>
+        <v>626270</v>
       </c>
       <c r="R113" t="n">
-        <v>7217934</v>
+        <v>7217834</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12813,10 +12827,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128103716</v>
+        <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12824,42 +12838,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>626454</v>
+        <v>626320</v>
       </c>
       <c r="R114" t="n">
-        <v>7217736</v>
+        <v>7217923</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12892,11 +12898,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12923,10 +12924,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103744</v>
+        <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>78847</v>
+        <v>80194</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12934,21 +12935,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12958,10 +12959,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>626454</v>
+        <v>626325</v>
       </c>
       <c r="R115" t="n">
-        <v>7217736</v>
+        <v>7217934</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13002,7 +13003,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -14503,32 +14503,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128103827</v>
+        <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>98591</v>
+        <v>91751</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>71</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14538,10 +14538,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>626128</v>
+        <v>626167</v>
       </c>
       <c r="R131" t="n">
-        <v>7218027</v>
+        <v>7217957</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14600,45 +14600,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128103696</v>
+        <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91751</v>
+        <v>91838</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>71</v>
+        <v>1505</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>626167</v>
+        <v>626280</v>
       </c>
       <c r="R132" t="n">
-        <v>7217957</v>
+        <v>7217822</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14679,6 +14682,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14697,48 +14701,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103787</v>
+        <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>91838</v>
+        <v>80230</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1505</v>
+        <v>6464</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>626280</v>
+        <v>626239</v>
       </c>
       <c r="R133" t="n">
-        <v>7217822</v>
+        <v>7218007</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14779,7 +14780,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14798,10 +14798,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128103781</v>
+        <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14809,21 +14809,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14833,10 +14833,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>626239</v>
+        <v>626346</v>
       </c>
       <c r="R134" t="n">
-        <v>7218007</v>
+        <v>7217883</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14895,45 +14895,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128103867</v>
+        <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>80229</v>
+        <v>57689</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>626346</v>
+        <v>626323</v>
       </c>
       <c r="R135" t="n">
-        <v>7217883</v>
+        <v>7217908</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14966,6 +14974,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14992,53 +15005,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128103856</v>
+        <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>626323</v>
+        <v>626311</v>
       </c>
       <c r="R136" t="n">
-        <v>7217908</v>
+        <v>7217865</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15071,11 +15076,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15102,7 +15102,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128103811</v>
+        <v>128103827</v>
       </c>
       <c r="B137" t="n">
         <v>98591</v>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>626311</v>
+        <v>626128</v>
       </c>
       <c r="R137" t="n">
-        <v>7217865</v>
+        <v>7218027</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17734,10 +17734,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128103813</v>
+        <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>98591</v>
+        <v>91849</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17745,21 +17745,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Byssomerulius albostramineus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Torrend) Hjortstam</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>626370</v>
+        <v>626271</v>
       </c>
       <c r="R164" t="n">
-        <v>7217900</v>
+        <v>7217852</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17831,32 +17831,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128103783</v>
+        <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91849</v>
+        <v>91939</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>298</v>
+        <v>5467</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Laxgröppa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17866,10 +17866,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>626271</v>
+        <v>626319</v>
       </c>
       <c r="R165" t="n">
-        <v>7217852</v>
+        <v>7217868</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17928,10 +17928,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128103786</v>
+        <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>91939</v>
+        <v>57686</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17939,34 +17939,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>626319</v>
+        <v>626194</v>
       </c>
       <c r="R166" t="n">
-        <v>7217868</v>
+        <v>7217951</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17999,6 +18007,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18025,32 +18038,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128103766</v>
+        <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18060,10 +18073,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>626308</v>
+        <v>626337</v>
       </c>
       <c r="R167" t="n">
-        <v>7217938</v>
+        <v>7217840</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18122,10 +18135,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128103736</v>
+        <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>57686</v>
+        <v>80194</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18133,42 +18146,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Burmyrhobben, Ly lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>626194</v>
+        <v>626308</v>
       </c>
       <c r="R168" t="n">
-        <v>7217951</v>
+        <v>7217938</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18201,11 +18206,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18232,7 +18232,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128103823</v>
+        <v>128103813</v>
       </c>
       <c r="B169" t="n">
         <v>98591</v>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>626337</v>
+        <v>626370</v>
       </c>
       <c r="R169" t="n">
-        <v>7217840</v>
+        <v>7217900</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19603,32 +19603,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128103700</v>
+        <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>91751</v>
+        <v>92756</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19638,10 +19638,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>626271</v>
+        <v>626133</v>
       </c>
       <c r="R183" t="n">
-        <v>7217852</v>
+        <v>7217998</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128103739</v>
+        <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80195</v>
+        <v>80194</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19711,21 +19711,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>626582</v>
+        <v>626398</v>
       </c>
       <c r="R184" t="n">
-        <v>7217455</v>
+        <v>7217759</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19797,32 +19797,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128103759</v>
+        <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>80194</v>
+        <v>91751</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>71</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>626350</v>
+        <v>626271</v>
       </c>
       <c r="R185" t="n">
         <v>7217852</v>
@@ -19894,10 +19894,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128103695</v>
+        <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>79708</v>
+        <v>80195</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19905,21 +19905,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>626290</v>
+        <v>626582</v>
       </c>
       <c r="R186" t="n">
-        <v>7217851</v>
+        <v>7217455</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19991,32 +19991,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128103859</v>
+        <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>626133</v>
+        <v>626350</v>
       </c>
       <c r="R187" t="n">
-        <v>7217998</v>
+        <v>7217852</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20088,10 +20088,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128103761</v>
+        <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>80194</v>
+        <v>79708</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20099,21 +20099,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>626398</v>
+        <v>626290</v>
       </c>
       <c r="R188" t="n">
-        <v>7217759</v>
+        <v>7217851</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11148,7 +11148,7 @@
         <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11238,14 +11238,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr"/>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91021</v>
+        <v>91059</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11335,14 +11339,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY98" t="inlineStr"/>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78847</v>
+        <v>78878</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11433,14 +11441,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY99" t="inlineStr"/>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11535,14 +11547,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY100" t="inlineStr"/>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11632,14 +11648,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY101" t="inlineStr"/>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80223</v>
+        <v>80254</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11729,14 +11749,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY102" t="inlineStr"/>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11826,14 +11850,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY103" t="inlineStr"/>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11936,14 +11964,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY104" t="inlineStr"/>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12033,14 +12065,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY105" t="inlineStr"/>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12130,14 +12166,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY106" t="inlineStr"/>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12227,14 +12267,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY107" t="inlineStr"/>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78846</v>
+        <v>78877</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12324,14 +12368,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12421,14 +12469,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY109" t="inlineStr"/>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12518,14 +12570,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY110" t="inlineStr"/>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>128103716</v>
       </c>
       <c r="B111" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12628,14 +12684,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY111" t="inlineStr"/>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78847</v>
+        <v>78878</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12726,14 +12786,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY112" t="inlineStr"/>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78061</v>
+        <v>78092</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12823,14 +12887,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY113" t="inlineStr"/>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12920,14 +12988,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY114" t="inlineStr"/>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13017,14 +13089,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY115" t="inlineStr"/>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13114,14 +13190,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY116" t="inlineStr"/>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80229</v>
+        <v>80260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13211,14 +13291,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY117" t="inlineStr"/>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
         <v>128103717</v>
       </c>
       <c r="B118" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13321,14 +13405,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY118" t="inlineStr"/>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13418,14 +13506,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY119" t="inlineStr"/>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13515,14 +13607,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY120" t="inlineStr"/>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98612</v>
+        <v>98653</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13612,14 +13708,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY121" t="inlineStr"/>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92750</v>
+        <v>92788</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13709,14 +13809,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY122" t="inlineStr"/>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91762</v>
+        <v>91800</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13806,14 +13910,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY123" t="inlineStr"/>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13903,14 +14011,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY124" t="inlineStr"/>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14000,14 +14112,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY125" t="inlineStr"/>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14097,14 +14213,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY126" t="inlineStr"/>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14194,14 +14314,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY127" t="inlineStr"/>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14304,14 +14428,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY128" t="inlineStr"/>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14401,14 +14529,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY129" t="inlineStr"/>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78847</v>
+        <v>78878</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14499,14 +14631,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY130" t="inlineStr"/>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91751</v>
+        <v>91789</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14596,14 +14732,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY131" t="inlineStr"/>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91838</v>
+        <v>91876</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14697,14 +14837,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY132" t="inlineStr"/>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80230</v>
+        <v>80261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14794,14 +14938,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY133" t="inlineStr"/>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80229</v>
+        <v>80260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14891,14 +15039,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY134" t="inlineStr"/>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
         <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15001,14 +15153,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15098,14 +15254,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY136" t="inlineStr"/>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15195,14 +15355,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY137" t="inlineStr"/>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15292,14 +15456,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY138" t="inlineStr"/>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91021</v>
+        <v>91059</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15389,14 +15557,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY139" t="inlineStr"/>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15486,14 +15658,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY140" t="inlineStr"/>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15583,14 +15759,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105651</v>
+        <v>105695</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15680,14 +15860,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr"/>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91727</v>
+        <v>91765</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15777,14 +15961,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY143" t="inlineStr"/>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92748</v>
+        <v>92786</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15874,14 +16062,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY144" t="inlineStr"/>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15971,14 +16163,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80229</v>
+        <v>80260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16068,14 +16264,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91484</v>
+        <v>91522</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16165,14 +16365,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY147" t="inlineStr"/>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16262,14 +16466,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY148" t="inlineStr"/>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16359,14 +16567,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY149" t="inlineStr"/>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16456,14 +16668,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr"/>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
         <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16566,14 +16782,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16663,14 +16883,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16760,14 +16984,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY153" t="inlineStr"/>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91751</v>
+        <v>91789</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16857,14 +17085,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY154" t="inlineStr"/>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92760</v>
+        <v>92798</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16954,14 +17186,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY155" t="inlineStr"/>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79708</v>
+        <v>79739</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17051,14 +17287,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY156" t="inlineStr"/>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92756</v>
+        <v>92794</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17148,14 +17388,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY157" t="inlineStr"/>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17245,14 +17489,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY158" t="inlineStr"/>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17342,14 +17590,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY159" t="inlineStr"/>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17439,14 +17691,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17536,14 +17792,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY161" t="inlineStr"/>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17633,14 +17893,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr"/>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17730,14 +17994,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr"/>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91849</v>
+        <v>91887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17827,14 +18095,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr"/>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91939</v>
+        <v>91977</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17924,14 +18196,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY165" t="inlineStr"/>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
         <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18034,14 +18310,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY166" t="inlineStr"/>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18131,14 +18411,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY167" t="inlineStr"/>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18228,14 +18512,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY168" t="inlineStr"/>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18325,14 +18613,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY169" t="inlineStr"/>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
         <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18422,14 +18714,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY170" t="inlineStr"/>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18519,14 +18815,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr"/>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78846</v>
+        <v>78877</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18616,14 +18916,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY172" t="inlineStr"/>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18713,14 +19017,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr"/>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18810,14 +19118,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY174" t="inlineStr"/>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78846</v>
+        <v>78877</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18907,14 +19219,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY175" t="inlineStr"/>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19004,14 +19320,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY176" t="inlineStr"/>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91431</v>
+        <v>91469</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19101,14 +19421,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY177" t="inlineStr"/>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19198,14 +19522,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY178" t="inlineStr"/>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91416</v>
+        <v>91454</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19295,14 +19623,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY179" t="inlineStr"/>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80223</v>
+        <v>80254</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19392,14 +19724,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY180" t="inlineStr"/>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19489,14 +19825,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY181" t="inlineStr"/>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
         <v>128103734</v>
       </c>
       <c r="B182" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19599,14 +19939,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY182" t="inlineStr"/>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92756</v>
+        <v>92794</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19696,14 +20040,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY183" t="inlineStr"/>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19793,14 +20141,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY184" t="inlineStr"/>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91751</v>
+        <v>91789</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19890,14 +20242,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY185" t="inlineStr"/>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80195</v>
+        <v>80226</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19987,14 +20343,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY186" t="inlineStr"/>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20084,14 +20444,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY187" t="inlineStr"/>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79708</v>
+        <v>79739</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20181,14 +20545,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY188" t="inlineStr"/>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78846</v>
+        <v>78877</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20278,14 +20646,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY189" t="inlineStr"/>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20375,7 +20747,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY190" t="inlineStr"/>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11148,7 +11148,7 @@
         <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91059</v>
+        <v>91063</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>128103716</v>
       </c>
       <c r="B111" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78092</v>
+        <v>78096</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>128103717</v>
       </c>
       <c r="B118" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91789</v>
+        <v>91793</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91876</v>
+        <v>91880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91059</v>
+        <v>91063</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91765</v>
+        <v>91769</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91789</v>
+        <v>91793</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91887</v>
+        <v>91891</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91977</v>
+        <v>91981</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>128103734</v>
       </c>
       <c r="B182" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91789</v>
+        <v>91793</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11148,7 +11148,7 @@
         <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91063</v>
+        <v>91068</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>128103716</v>
       </c>
       <c r="B111" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78096</v>
+        <v>78037</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>128103717</v>
       </c>
       <c r="B118" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91793</v>
+        <v>91798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91880</v>
+        <v>91885</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91063</v>
+        <v>91068</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91769</v>
+        <v>91774</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91793</v>
+        <v>91798</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91891</v>
+        <v>91896</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91981</v>
+        <v>91986</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>128103734</v>
       </c>
       <c r="B182" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91793</v>
+        <v>91798</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91075</v>
+        <v>91078</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91795</v>
+        <v>91798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91893</v>
+        <v>91896</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91075</v>
+        <v>91078</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91795</v>
+        <v>91798</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91904</v>
+        <v>91907</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91994</v>
+        <v>91997</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91795</v>
+        <v>91798</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91078</v>
+        <v>91081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78042</v>
+        <v>78043</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91798</v>
+        <v>91801</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91896</v>
+        <v>91899</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91078</v>
+        <v>91081</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91798</v>
+        <v>91801</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91907</v>
+        <v>91910</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>91997</v>
+        <v>92000</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91798</v>
+        <v>91801</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11148,7 +11148,7 @@
         <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91081</v>
+        <v>91085</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>128103716</v>
       </c>
       <c r="B111" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>128103717</v>
       </c>
       <c r="B118" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91801</v>
+        <v>91808</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91899</v>
+        <v>91906</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91081</v>
+        <v>91085</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91801</v>
+        <v>91808</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91910</v>
+        <v>91917</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92000</v>
+        <v>92007</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>128103734</v>
       </c>
       <c r="B182" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91801</v>
+        <v>91808</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91085</v>
+        <v>91092</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91906</v>
+        <v>91913</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91085</v>
+        <v>91092</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91917</v>
+        <v>91924</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92007</v>
+        <v>92014</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11148,7 +11148,7 @@
         <v>128103784</v>
       </c>
       <c r="B97" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91092</v>
+        <v>91094</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>128103719</v>
       </c>
       <c r="B104" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>128103716</v>
       </c>
       <c r="B111" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78047</v>
+        <v>78049</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>128103717</v>
       </c>
       <c r="B118" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>128103721</v>
       </c>
       <c r="B128" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91815</v>
+        <v>91817</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91913</v>
+        <v>91915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>128103856</v>
       </c>
       <c r="B135" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91092</v>
+        <v>91094</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>128103735</v>
       </c>
       <c r="B151" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91815</v>
+        <v>91817</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92014</v>
+        <v>92016</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>128103736</v>
       </c>
       <c r="B166" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>128103785</v>
       </c>
       <c r="B170" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>128103734</v>
       </c>
       <c r="B182" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91815</v>
+        <v>91817</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91094</v>
+        <v>91095</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91817</v>
+        <v>91827</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91915</v>
+        <v>91924</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91094</v>
+        <v>91095</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91817</v>
+        <v>91827</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91926</v>
+        <v>91961</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18022,12 +18022,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Byssomerulius albostramineus</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Torrend) Hjortstam</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18106,7 +18106,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92016</v>
+        <v>92022</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91817</v>
+        <v>91827</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91827</v>
+        <v>91828</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91924</v>
+        <v>91925</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16292,14 +16292,10 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -16793,7 +16789,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16894,7 +16890,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16991,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91827</v>
+        <v>91828</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17096,7 +17092,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17298,7 +17294,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17904,7 +17900,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18005,7 +18001,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18106,7 +18102,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18321,7 +18317,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18523,7 +18519,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18725,7 +18721,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19230,7 +19226,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19950,7 +19946,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20152,7 +20148,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91827</v>
+        <v>91828</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20657,7 +20653,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91095</v>
+        <v>91098</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78049</v>
+        <v>78051</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91828</v>
+        <v>91831</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91925</v>
+        <v>91928</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91095</v>
+        <v>91098</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91828</v>
+        <v>91831</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92023</v>
+        <v>92026</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91828</v>
+        <v>91831</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91098</v>
+        <v>91100</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>128103745</v>
       </c>
       <c r="B99" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>128103850</v>
       </c>
       <c r="B100" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>128103757</v>
       </c>
       <c r="B101" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128103728</v>
       </c>
       <c r="B102" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>128103794</v>
       </c>
       <c r="B108" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>128103744</v>
       </c>
       <c r="B112" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>128103870</v>
       </c>
       <c r="B113" t="n">
-        <v>78051</v>
+        <v>78052</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>128103765</v>
       </c>
       <c r="B114" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>128103754</v>
       </c>
       <c r="B115" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>128103853</v>
       </c>
       <c r="B116" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>128103866</v>
       </c>
       <c r="B117" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>128103782</v>
       </c>
       <c r="B124" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>128103756</v>
       </c>
       <c r="B125" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>128103772</v>
       </c>
       <c r="B126" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>128103842</v>
       </c>
       <c r="B127" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>128103746</v>
       </c>
       <c r="B130" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91831</v>
+        <v>91833</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91928</v>
+        <v>91930</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>128103781</v>
       </c>
       <c r="B133" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>128103867</v>
       </c>
       <c r="B134" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91098</v>
+        <v>91100</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>128103773</v>
       </c>
       <c r="B140" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>128103769</v>
       </c>
       <c r="B141" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>128103843</v>
       </c>
       <c r="B145" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>128103863</v>
       </c>
       <c r="B146" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>128103753</v>
       </c>
       <c r="B149" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>128103763</v>
       </c>
       <c r="B150" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91831</v>
+        <v>91833</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>128103694</v>
       </c>
       <c r="B156" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>128103767</v>
       </c>
       <c r="B158" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>128103851</v>
       </c>
       <c r="B159" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>128103770</v>
       </c>
       <c r="B160" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>128103774</v>
       </c>
       <c r="B161" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>128103768</v>
       </c>
       <c r="B162" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91965</v>
+        <v>91967</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92026</v>
+        <v>92028</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>128103766</v>
       </c>
       <c r="B168" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>128103793</v>
       </c>
       <c r="B172" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>128103844</v>
       </c>
       <c r="B173" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>128103852</v>
       </c>
       <c r="B174" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>128103792</v>
       </c>
       <c r="B175" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>128103758</v>
       </c>
       <c r="B178" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>128103727</v>
       </c>
       <c r="B180" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>128103845</v>
       </c>
       <c r="B181" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>128103761</v>
       </c>
       <c r="B184" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91831</v>
+        <v>91833</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>128103739</v>
       </c>
       <c r="B186" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>128103759</v>
       </c>
       <c r="B187" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>128103695</v>
       </c>
       <c r="B188" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>128103791</v>
       </c>
       <c r="B189" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -11249,7 +11249,7 @@
         <v>128103836</v>
       </c>
       <c r="B98" t="n">
-        <v>91100</v>
+        <v>91104</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>128103701</v>
       </c>
       <c r="B103" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>128103812</v>
       </c>
       <c r="B105" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>128103806</v>
       </c>
       <c r="B106" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>128103703</v>
       </c>
       <c r="B107" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>128103830</v>
       </c>
       <c r="B109" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>128103826</v>
       </c>
       <c r="B110" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>128103831</v>
       </c>
       <c r="B119" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>128103828</v>
       </c>
       <c r="B120" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>128103733</v>
       </c>
       <c r="B121" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>128103871</v>
       </c>
       <c r="B122" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>128103740</v>
       </c>
       <c r="B123" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>128103824</v>
       </c>
       <c r="B129" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>128103696</v>
       </c>
       <c r="B131" t="n">
-        <v>91833</v>
+        <v>91837</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>128103787</v>
       </c>
       <c r="B132" t="n">
-        <v>91930</v>
+        <v>91934</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128103811</v>
       </c>
       <c r="B136" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>128103827</v>
       </c>
       <c r="B137" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>128103810</v>
       </c>
       <c r="B138" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>128103835</v>
       </c>
       <c r="B139" t="n">
-        <v>91100</v>
+        <v>91104</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>128103837</v>
       </c>
       <c r="B142" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>128103857</v>
       </c>
       <c r="B143" t="n">
-        <v>91818</v>
+        <v>91822</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>128103743</v>
       </c>
       <c r="B144" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>128103839</v>
       </c>
       <c r="B147" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>128103704</v>
       </c>
       <c r="B148" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>128103829</v>
       </c>
       <c r="B152" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>128103807</v>
       </c>
       <c r="B153" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>128103699</v>
       </c>
       <c r="B154" t="n">
-        <v>91833</v>
+        <v>91837</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>128103737</v>
       </c>
       <c r="B155" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>128103858</v>
       </c>
       <c r="B157" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>128103808</v>
       </c>
       <c r="B163" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>128103783</v>
       </c>
       <c r="B164" t="n">
-        <v>91967</v>
+        <v>91971</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>128103786</v>
       </c>
       <c r="B165" t="n">
-        <v>92028</v>
+        <v>92032</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>128103823</v>
       </c>
       <c r="B167" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>128103813</v>
       </c>
       <c r="B169" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>128103809</v>
       </c>
       <c r="B171" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>128103825</v>
       </c>
       <c r="B176" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>128103692</v>
       </c>
       <c r="B177" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>128103729</v>
       </c>
       <c r="B179" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>128103859</v>
       </c>
       <c r="B183" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>128103700</v>
       </c>
       <c r="B185" t="n">
-        <v>91833</v>
+        <v>91837</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>128103822</v>
       </c>
       <c r="B190" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY190"/>
+  <dimension ref="A1:AY207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20749,6 +20749,1678 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>134317509</v>
+      </c>
+      <c r="B191" t="n">
+        <v>99180</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>626184</v>
+      </c>
+      <c r="R191" t="n">
+        <v>7218057</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>134317552</v>
+      </c>
+      <c r="B192" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>626324</v>
+      </c>
+      <c r="R192" t="n">
+        <v>7217928</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>134317451</v>
+      </c>
+      <c r="B193" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>626203</v>
+      </c>
+      <c r="R193" t="n">
+        <v>7218075</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>134317492</v>
+      </c>
+      <c r="B194" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>626231</v>
+      </c>
+      <c r="R194" t="n">
+        <v>7218032</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>134317458</v>
+      </c>
+      <c r="B195" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>626149</v>
+      </c>
+      <c r="R195" t="n">
+        <v>7217993</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>134317460</v>
+      </c>
+      <c r="B196" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>626307</v>
+      </c>
+      <c r="R196" t="n">
+        <v>7217942</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>134317486</v>
+      </c>
+      <c r="B197" t="n">
+        <v>80479</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>626132</v>
+      </c>
+      <c r="R197" t="n">
+        <v>7217883</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>134317531</v>
+      </c>
+      <c r="B198" t="n">
+        <v>79025</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>353</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>626172</v>
+      </c>
+      <c r="R198" t="n">
+        <v>7217960</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>134317487</v>
+      </c>
+      <c r="B199" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>626132</v>
+      </c>
+      <c r="R199" t="n">
+        <v>7217883</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>134317530</v>
+      </c>
+      <c r="B200" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>626575</v>
+      </c>
+      <c r="R200" t="n">
+        <v>7217473</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>134317477</v>
+      </c>
+      <c r="B201" t="n">
+        <v>80368</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>626242</v>
+      </c>
+      <c r="R201" t="n">
+        <v>7217975</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>134317493</v>
+      </c>
+      <c r="B202" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>626147</v>
+      </c>
+      <c r="R202" t="n">
+        <v>7217919</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>134317508</v>
+      </c>
+      <c r="B203" t="n">
+        <v>99180</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>626239</v>
+      </c>
+      <c r="R203" t="n">
+        <v>7217985</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>134317441</v>
+      </c>
+      <c r="B204" t="n">
+        <v>79949</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>626096</v>
+      </c>
+      <c r="R204" t="n">
+        <v>7217858</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>134317495</v>
+      </c>
+      <c r="B205" t="n">
+        <v>80474</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>626188</v>
+      </c>
+      <c r="R205" t="n">
+        <v>7218062</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>134317553</v>
+      </c>
+      <c r="B206" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>626324</v>
+      </c>
+      <c r="R206" t="n">
+        <v>7217928</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>134317469</v>
+      </c>
+      <c r="B207" t="n">
+        <v>99202</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>626140</v>
+      </c>
+      <c r="R207" t="n">
+        <v>7217899</v>
+      </c>
+      <c r="S207" t="n">
+        <v>10</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -21047,10 +21047,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>134317458</v>
+        <v>134317492</v>
       </c>
       <c r="B194" t="n">
-        <v>58461</v>
+        <v>80474</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21058,43 +21058,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>626149</v>
+        <v>626231</v>
       </c>
       <c r="R194" t="n">
-        <v>7217993</v>
+        <v>7218032</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21153,10 +21144,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>134317492</v>
+        <v>134317458</v>
       </c>
       <c r="B195" t="n">
-        <v>80474</v>
+        <v>58461</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21164,34 +21155,43 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>626231</v>
+        <v>626149</v>
       </c>
       <c r="R195" t="n">
-        <v>7218032</v>
+        <v>7217993</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21550,32 +21550,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134317487</v>
+        <v>134317530</v>
       </c>
       <c r="B199" t="n">
-        <v>80474</v>
+        <v>99098</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21585,10 +21585,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>626132</v>
+        <v>626575</v>
       </c>
       <c r="R199" t="n">
-        <v>7217883</v>
+        <v>7217473</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21647,32 +21647,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134317530</v>
+        <v>134317487</v>
       </c>
       <c r="B200" t="n">
-        <v>99098</v>
+        <v>80474</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21682,10 +21682,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>626575</v>
+        <v>626132</v>
       </c>
       <c r="R200" t="n">
-        <v>7217473</v>
+        <v>7217883</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21744,32 +21744,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>134317477</v>
+        <v>134317493</v>
       </c>
       <c r="B201" t="n">
-        <v>80368</v>
+        <v>80474</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21779,10 +21779,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>626242</v>
+        <v>626147</v>
       </c>
       <c r="R201" t="n">
-        <v>7217975</v>
+        <v>7217919</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21841,32 +21841,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>134317493</v>
+        <v>134317477</v>
       </c>
       <c r="B202" t="n">
-        <v>80474</v>
+        <v>80368</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21876,10 +21876,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>626147</v>
+        <v>626242</v>
       </c>
       <c r="R202" t="n">
-        <v>7217919</v>
+        <v>7217975</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22035,10 +22035,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>134317441</v>
+        <v>134317495</v>
       </c>
       <c r="B204" t="n">
-        <v>79949</v>
+        <v>80474</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22046,21 +22046,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22070,10 +22070,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>626096</v>
+        <v>626188</v>
       </c>
       <c r="R204" t="n">
-        <v>7217858</v>
+        <v>7218062</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22132,10 +22132,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>134317495</v>
+        <v>134317441</v>
       </c>
       <c r="B205" t="n">
-        <v>80474</v>
+        <v>79949</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22143,21 +22143,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22167,10 +22167,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>626188</v>
+        <v>626096</v>
       </c>
       <c r="R205" t="n">
-        <v>7218062</v>
+        <v>7217858</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>

--- a/artfynd/A 36585-2025 artfynd.xlsx
+++ b/artfynd/A 36585-2025 artfynd.xlsx
@@ -20754,7 +20754,7 @@
         <v>134317509</v>
       </c>
       <c r="B191" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>134317552</v>
       </c>
       <c r="B192" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>134317492</v>
       </c>
       <c r="B194" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>134317486</v>
       </c>
       <c r="B197" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>134317531</v>
       </c>
       <c r="B198" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21550,32 +21550,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>134317530</v>
+        <v>134317487</v>
       </c>
       <c r="B199" t="n">
-        <v>99098</v>
+        <v>80481</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21585,10 +21585,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>626575</v>
+        <v>626132</v>
       </c>
       <c r="R199" t="n">
-        <v>7217473</v>
+        <v>7217883</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21647,32 +21647,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>134317487</v>
+        <v>134317530</v>
       </c>
       <c r="B200" t="n">
-        <v>80474</v>
+        <v>99105</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21682,10 +21682,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>626132</v>
+        <v>626575</v>
       </c>
       <c r="R200" t="n">
-        <v>7217883</v>
+        <v>7217473</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21744,32 +21744,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>134317493</v>
+        <v>134317477</v>
       </c>
       <c r="B201" t="n">
-        <v>80474</v>
+        <v>80375</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21779,10 +21779,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>626147</v>
+        <v>626242</v>
       </c>
       <c r="R201" t="n">
-        <v>7217919</v>
+        <v>7217975</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21841,32 +21841,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>134317477</v>
+        <v>134317493</v>
       </c>
       <c r="B202" t="n">
-        <v>80368</v>
+        <v>80481</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21876,10 +21876,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>626242</v>
+        <v>626147</v>
       </c>
       <c r="R202" t="n">
-        <v>7217975</v>
+        <v>7217919</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21941,7 +21941,7 @@
         <v>134317508</v>
       </c>
       <c r="B203" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22035,10 +22035,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>134317495</v>
+        <v>134317441</v>
       </c>
       <c r="B204" t="n">
-        <v>80474</v>
+        <v>79956</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22046,21 +22046,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22070,10 +22070,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>626188</v>
+        <v>626096</v>
       </c>
       <c r="R204" t="n">
-        <v>7218062</v>
+        <v>7217858</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22132,10 +22132,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>134317441</v>
+        <v>134317495</v>
       </c>
       <c r="B205" t="n">
-        <v>79949</v>
+        <v>80481</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22143,21 +22143,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22167,10 +22167,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>626096</v>
+        <v>626188</v>
       </c>
       <c r="R205" t="n">
-        <v>7217858</v>
+        <v>7218062</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22232,7 +22232,7 @@
         <v>134317553</v>
       </c>
       <c r="B206" t="n">
-        <v>80485</v>
+        <v>80492</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>134317469</v>
       </c>
       <c r="B207" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
